--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -13715,7 +13715,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>569</x:v>
@@ -13855,7 +13855,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>83860</x:v>
+        <x:v>167720</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>569</x:v>
@@ -14555,7 +14555,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>585</x:v>
@@ -14660,7 +14660,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>569</x:v>
@@ -14905,7 +14905,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>569</x:v>
@@ -15500,7 +15500,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>569</x:v>
@@ -15605,7 +15605,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>569</x:v>
@@ -15675,7 +15675,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>569</x:v>
@@ -15780,7 +15780,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>569</x:v>
@@ -16060,7 +16060,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>585</x:v>
@@ -16410,7 +16410,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>569</x:v>
@@ -16445,7 +16445,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>9866096</x:v>
+        <x:v>15034832</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>585</x:v>
@@ -17025,7 +17025,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>569</x:v>
@@ -17153,7 +17153,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>83860</x:v>
+        <x:v>167720</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>569</x:v>
@@ -17793,7 +17793,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>585</x:v>
@@ -17889,7 +17889,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>569</x:v>
@@ -18113,7 +18113,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>524948</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>569</x:v>
@@ -18625,7 +18625,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>569</x:v>
@@ -18721,7 +18721,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>569</x:v>
@@ -18785,7 +18785,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>587501</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>569</x:v>
@@ -18849,7 +18849,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>569</x:v>
@@ -19105,7 +19105,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>585</x:v>
@@ -19425,7 +19425,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>569</x:v>
@@ -19457,7 +19457,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>9866096</x:v>
+        <x:v>15034832</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>585</x:v>
@@ -19889,7 +19889,7 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>569</x:v>
@@ -19933,7 +19933,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>666234</x:v>
+        <x:v>750094</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>569</x:v>
@@ -20142,7 +20142,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>585</x:v>
@@ -20175,7 +20175,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>569</x:v>
@@ -20241,7 +20241,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>524948</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>569</x:v>
@@ -20417,7 +20417,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>569</x:v>
@@ -20450,7 +20450,7 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>569</x:v>
@@ -20472,7 +20472,7 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>587501</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>569</x:v>
@@ -20494,7 +20494,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>569</x:v>
@@ -20582,7 +20582,7 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>585</x:v>
@@ -20692,7 +20692,7 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>569</x:v>
@@ -20703,7 +20703,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>9985740</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>585</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35810,10 +35810,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35825,7 +35825,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35836,10 +35836,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35851,7 +35851,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -58933,10 +58933,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2544</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2545</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2129</x:v>
@@ -58957,7 +58957,7 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2551</x:v>
@@ -58968,10 +58968,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2544</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2545</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2129</x:v>
@@ -58992,7 +58992,7 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2551</x:v>
@@ -60648,10 +60648,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2544</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2545</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2672</x:v>
@@ -60672,7 +60672,7 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>15034832</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2567</x:v>
@@ -60683,10 +60683,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2544</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2545</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2672</x:v>
@@ -60707,7 +60707,7 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>119644</x:v>
+        <x:v>15034832</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2567</x:v>
@@ -61356,10 +61356,10 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>2544</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2545</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>1979</x:v>
@@ -61380,7 +61380,7 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>167720</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2551</x:v>
@@ -61388,10 +61388,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2544</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2545</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>1979</x:v>
@@ -61412,7 +61412,7 @@
         <x:v>2575</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>582374</x:v>
+        <x:v>167720</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2551</x:v>
@@ -63724,10 +63724,10 @@
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2544</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2545</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2672</x:v>
@@ -63748,7 +63748,7 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>15034832</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2567</x:v>
@@ -63756,10 +63756,10 @@
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2544</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2545</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2672</x:v>
@@ -63780,7 +63780,7 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>119644</x:v>
+        <x:v>15034832</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2567</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35810,10 +35810,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35825,7 +35825,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35836,10 +35836,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35851,7 +35851,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35810,10 +35810,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35825,7 +35825,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35836,10 +35836,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35851,7 +35851,7 @@
         <x:v>2080</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -3123,7 +3123,7 @@
     <x:t>C00573949</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSH GOTTHEIMER FOR CONGRESS</x:t>
+    <x:t>JOSH FOR JERSEY</x:t>
   </x:si>
   <x:si>
     <x:t>GOTTHEIMER, JOSH</x:t>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7830,6 +7830,21 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
     <x:t>S4AZ00139</x:t>
   </x:si>
   <x:si>
@@ -7942,9 +7957,6 @@
   </x:si>
   <x:si>
     <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX22283</x:t>
@@ -8192,8 +8204,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K96" totalsRowShown="0">
-  <x:autoFilter ref="A1:K96"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K97" totalsRowShown="0">
+  <x:autoFilter ref="A1:K97"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8212,8 +8224,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J94" totalsRowShown="0">
-  <x:autoFilter ref="A1:J94"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J95" totalsRowShown="0">
+  <x:autoFilter ref="A1:J95"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8231,8 +8243,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C90" totalsRowShown="0">
-  <x:autoFilter ref="A1:C90"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C91" totalsRowShown="0">
+  <x:autoFilter ref="A1:C91"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -35752,10 +35764,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35767,7 +35779,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35778,10 +35790,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35793,7 +35805,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -57605,7 +57617,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K96"/>
+  <x:dimension ref="A1:K97"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58639,66 +58651,66 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K30" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2549</x:v>
@@ -58709,16 +58721,16 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2553</x:v>
@@ -58727,19 +58739,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K32" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -58750,10 +58762,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2553</x:v>
@@ -58765,45 +58777,45 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K33" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -58820,10 +58832,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2546</x:v>
@@ -58832,13 +58844,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -58849,16 +58861,16 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2546</x:v>
@@ -58867,13 +58879,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -58884,10 +58896,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2127</x:v>
@@ -58908,7 +58920,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -58925,10 +58937,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -58937,13 +58949,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -58954,37 +58966,37 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K39" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -59013,42 +59025,42 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K40" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -59059,31 +59071,31 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -59100,10 +59112,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2553</x:v>
@@ -59112,13 +59124,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -59129,16 +59141,16 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2553</x:v>
@@ -59147,13 +59159,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -59164,31 +59176,31 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -59199,31 +59211,31 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -59234,37 +59246,37 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K47" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -59275,31 +59287,31 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K48" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -59310,10 +59322,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2546</x:v>
@@ -59322,13 +59334,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -59339,19 +59351,19 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
         <x:v>2547</x:v>
@@ -59360,10 +59372,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -59374,101 +59386,101 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K51" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K52" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -59479,31 +59491,31 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -59514,31 +59526,31 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -59555,25 +59567,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -59584,16 +59596,16 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2546</x:v>
@@ -59602,19 +59614,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K57" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -59625,10 +59637,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2546</x:v>
@@ -59637,48 +59649,48 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K58" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -59695,31 +59707,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K60" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -59730,31 +59742,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -59765,10 +59777,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2553</x:v>
@@ -59777,19 +59789,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -59800,10 +59812,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2553</x:v>
@@ -59815,16 +59827,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K63" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -59835,25 +59847,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -59870,66 +59882,66 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K65" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -59940,25 +59952,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
@@ -59969,31 +59981,31 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -60004,31 +60016,31 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -60045,10 +60057,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2553</x:v>
@@ -60057,51 +60069,51 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K70" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>20483</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K71" s="1">
         <x:v>2026</x:v>
@@ -60109,16 +60121,16 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2546</x:v>
@@ -60127,19 +60139,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -60150,10 +60162,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2546</x:v>
@@ -60162,19 +60174,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -60185,10 +60197,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2546</x:v>
@@ -60197,19 +60209,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -60220,28 +60232,28 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K75" s="1">
         <x:v>2024</x:v>
@@ -60249,34 +60261,34 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K76" s="1">
         <x:v>2024</x:v>
@@ -60284,101 +60296,101 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>91847</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2549</x:v>
@@ -60389,31 +60401,31 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2549</x:v>
@@ -60424,34 +60436,34 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K81" s="1">
         <x:v>2024</x:v>
@@ -60459,34 +60471,34 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K82" s="1">
         <x:v>2024</x:v>
@@ -60500,10 +60512,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2553</x:v>
@@ -60512,13 +60524,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2549</x:v>
@@ -60529,16 +60541,16 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2553</x:v>
@@ -60547,51 +60559,51 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K84" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K85" s="1">
         <x:v>2026</x:v>
@@ -60605,10 +60617,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2546</x:v>
@@ -60640,45 +60652,45 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>106947</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2546</x:v>
@@ -60687,13 +60699,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2549</x:v>
@@ -60704,16 +60716,16 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2546</x:v>
@@ -60722,13 +60734,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2549</x:v>
@@ -60739,31 +60751,31 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -60774,31 +60786,31 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>110148</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -60809,10 +60821,10 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2482</x:v>
@@ -60833,7 +60845,7 @@
         <x:v>2597</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -60844,31 +60856,31 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
@@ -60879,10 +60891,10 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2680</x:v>
@@ -60894,16 +60906,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2549</x:v>
@@ -60914,31 +60926,31 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2549</x:v>
@@ -60955,10 +60967,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
@@ -60970,15 +60982,50 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K96" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:11">
+      <x:c r="A97" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
+        <x:v>2686</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
+        <x:v>2687</x:v>
+      </x:c>
+      <x:c r="E97" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F97" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G97" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H97" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="I97" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J97" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K97" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -60998,7 +61045,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J94"/>
+  <x:dimension ref="A1:J95"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61944,31 +61991,31 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2549</x:v>
@@ -61976,31 +62023,31 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2549</x:v>
@@ -62008,16 +62055,16 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2553</x:v>
@@ -62026,13 +62073,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
@@ -62046,10 +62093,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2553</x:v>
@@ -62061,10 +62108,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
@@ -62072,31 +62119,31 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -62110,10 +62157,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2546</x:v>
@@ -62122,13 +62169,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -62142,10 +62189,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2546</x:v>
@@ -62154,13 +62201,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -62168,10 +62215,10 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2127</x:v>
@@ -62192,7 +62239,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -62200,16 +62247,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -62218,13 +62265,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -62232,31 +62279,31 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -62264,31 +62311,31 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -62296,31 +62343,31 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -62334,10 +62381,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2553</x:v>
@@ -62346,13 +62393,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -62360,16 +62407,16 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2553</x:v>
@@ -62378,13 +62425,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -62392,31 +62439,31 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -62424,31 +62471,31 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -62456,31 +62503,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -62494,25 +62541,25 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -62526,10 +62573,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>2546</x:v>
@@ -62538,13 +62585,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -62552,19 +62599,19 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
         <x:v>2547</x:v>
@@ -62573,10 +62620,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -62584,31 +62631,31 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -62616,31 +62663,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -62648,31 +62695,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -62680,31 +62727,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -62712,31 +62759,31 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -62750,25 +62797,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -62776,16 +62823,16 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2546</x:v>
@@ -62794,13 +62841,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -62814,10 +62861,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2546</x:v>
@@ -62826,13 +62873,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -62840,31 +62887,31 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -62878,25 +62925,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -62910,25 +62957,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -62942,10 +62989,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2553</x:v>
@@ -62954,13 +63001,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -62974,25 +63021,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
@@ -63006,25 +63053,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -63032,31 +63079,31 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -63070,25 +63117,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
@@ -63096,31 +63143,31 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
@@ -63128,31 +63175,31 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
@@ -63166,10 +63213,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2553</x:v>
@@ -63178,13 +63225,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -63192,48 +63239,48 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>20483</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2546</x:v>
@@ -63242,16 +63289,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:10">
@@ -63262,10 +63309,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2546</x:v>
@@ -63274,16 +63321,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:10">
@@ -63294,10 +63341,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2546</x:v>
@@ -63306,16 +63353,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:10">
@@ -63326,89 +63373,89 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>91847</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -63416,31 +63463,31 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2549</x:v>
@@ -63448,31 +63495,31 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
@@ -63480,31 +63527,31 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2549</x:v>
@@ -63512,66 +63559,66 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:10">
@@ -63582,10 +63629,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2553</x:v>
@@ -63594,13 +63641,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2549</x:v>
@@ -63608,16 +63655,16 @@
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2553</x:v>
@@ -63626,13 +63673,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2549</x:v>
@@ -63640,48 +63687,48 @@
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2546</x:v>
@@ -63696,7 +63743,7 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2565</x:v>
@@ -63704,48 +63751,48 @@
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2546</x:v>
@@ -63754,13 +63801,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2549</x:v>
@@ -63768,16 +63815,16 @@
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
@@ -63786,13 +63833,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2549</x:v>
@@ -63800,31 +63847,31 @@
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2549</x:v>
@@ -63832,31 +63879,31 @@
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>110148</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2549</x:v>
@@ -63864,10 +63911,10 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>2482</x:v>
@@ -63888,7 +63935,7 @@
         <x:v>2597</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -63896,31 +63943,31 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -63928,10 +63975,10 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2680</x:v>
@@ -63943,16 +63990,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -63960,31 +64007,31 @@
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
@@ -63998,10 +64045,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2546</x:v>
@@ -64013,12 +64060,44 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="I94" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J94" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:10">
+      <x:c r="A95" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
+        <x:v>2686</x:v>
+      </x:c>
+      <x:c r="D95" s="1" t="s">
+        <x:v>2687</x:v>
+      </x:c>
+      <x:c r="E95" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F95" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G95" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H95" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="I95" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J94" s="1" t="s">
+      <x:c r="J95" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>
@@ -64038,7 +64117,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C90"/>
+  <x:dimension ref="A1:C91"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -64357,10 +64436,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>2549</x:v>
@@ -64368,10 +64447,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>2549</x:v>
@@ -64379,10 +64458,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>2549</x:v>
@@ -64390,10 +64469,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2549</x:v>
@@ -64401,10 +64480,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2549</x:v>
@@ -64412,10 +64491,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2549</x:v>
@@ -64423,10 +64502,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2549</x:v>
@@ -64434,10 +64513,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2549</x:v>
@@ -64445,10 +64524,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2549</x:v>
@@ -64456,10 +64535,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2549</x:v>
@@ -64467,10 +64546,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2549</x:v>
@@ -64478,10 +64557,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2549</x:v>
@@ -64489,10 +64568,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2549</x:v>
@@ -64500,10 +64579,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2549</x:v>
@@ -64511,10 +64590,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2549</x:v>
@@ -64522,10 +64601,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2549</x:v>
@@ -64533,10 +64612,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2549</x:v>
@@ -64544,10 +64623,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2549</x:v>
@@ -64555,10 +64634,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2549</x:v>
@@ -64566,10 +64645,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2549</x:v>
@@ -64577,10 +64656,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2549</x:v>
@@ -64588,10 +64667,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2549</x:v>
@@ -64599,10 +64678,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2549</x:v>
@@ -64610,10 +64689,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2549</x:v>
@@ -64621,10 +64700,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2549</x:v>
@@ -64632,10 +64711,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2549</x:v>
@@ -64643,10 +64722,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2549</x:v>
@@ -64654,10 +64733,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2549</x:v>
@@ -64665,10 +64744,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2549</x:v>
@@ -64676,10 +64755,10 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>
@@ -64687,10 +64766,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2549</x:v>
@@ -64698,10 +64777,10 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2549</x:v>
@@ -64709,10 +64788,10 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2549</x:v>
@@ -64720,10 +64799,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2549</x:v>
@@ -64731,10 +64810,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2549</x:v>
@@ -64742,10 +64821,10 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2549</x:v>
@@ -64753,10 +64832,10 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2549</x:v>
@@ -64764,10 +64843,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2549</x:v>
@@ -64775,76 +64854,76 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>20483</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>91847</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2549</x:v>
@@ -64852,10 +64931,10 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2549</x:v>
@@ -64863,10 +64942,10 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2549</x:v>
@@ -64874,10 +64953,10 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2549</x:v>
@@ -64885,32 +64964,32 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2549</x:v>
@@ -64918,10 +64997,10 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2549</x:v>
@@ -64929,32 +65008,32 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>106947</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2549</x:v>
@@ -64962,10 +65041,10 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2549</x:v>
@@ -64973,10 +65052,10 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2549</x:v>
@@ -64984,10 +65063,10 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>173232</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2549</x:v>
@@ -64995,10 +65074,10 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>10000</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2549</x:v>
@@ -65009,7 +65088,7 @@
         <x:v>2681</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2549</x:v>
@@ -65017,10 +65096,10 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2549</x:v>
@@ -65028,12 +65107,23 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="B90" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C90" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:3">
+      <x:c r="A91" s="1" t="s">
+        <x:v>2687</x:v>
+      </x:c>
+      <x:c r="B91" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C90" s="1" t="s">
+      <x:c r="C91" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7773,6 +7773,12 @@
     <x:t>CISCOMANI, JUAN</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA13070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
     <x:t>04</x:t>
   </x:si>
   <x:si>
@@ -7957,6 +7963,12 @@
   </x:si>
   <x:si>
     <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX22283</x:t>
@@ -8204,8 +8216,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K97" totalsRowShown="0">
-  <x:autoFilter ref="A1:K97"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K100" totalsRowShown="0">
+  <x:autoFilter ref="A1:K100"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8224,8 +8236,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J95" totalsRowShown="0">
-  <x:autoFilter ref="A1:J95"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J98" totalsRowShown="0">
+  <x:autoFilter ref="A1:J98"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8243,8 +8255,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C91" totalsRowShown="0">
-  <x:autoFilter ref="A1:C91"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C94" totalsRowShown="0">
+  <x:autoFilter ref="A1:C94"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -26022,7 +26034,7 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>3500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="H672" s="1" t="s">
         <x:v>20</x:v>
@@ -30338,7 +30350,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="G838" s="1">
-        <x:v>1000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H838" s="1" t="s">
         <x:v>20</x:v>
@@ -35764,10 +35776,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35779,7 +35791,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35790,10 +35802,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35805,7 +35817,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -40537,7 +40549,7 @@
         <x:v>2216</x:v>
       </x:c>
       <x:c r="H389" s="1">
-        <x:v>2500</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="390" spans="1:8">
@@ -46023,7 +46035,7 @@
         <x:v>2393</x:v>
       </x:c>
       <x:c r="H600" s="1">
-        <x:v>3500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:8">
@@ -54166,7 +54178,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C296" s="1">
-        <x:v>8200</x:v>
+        <x:v>12200</x:v>
       </x:c>
     </x:row>
     <x:row r="297" spans="1:3">
@@ -56047,7 +56059,7 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>7050</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:3">
@@ -57617,7 +57629,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K97"/>
+  <x:dimension ref="A1:K100"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58161,66 +58173,66 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2018</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>211281</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K16" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>973501</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2549</x:v>
@@ -58231,31 +58243,31 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>2035</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>2044</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>1700</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I18" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
@@ -58266,16 +58278,16 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2553</x:v>
@@ -58284,13 +58296,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
@@ -58301,34 +58313,34 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K20" s="1">
         <x:v>2024</x:v>
@@ -58336,10 +58348,10 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2591</x:v>
@@ -58354,16 +58366,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K21" s="1">
         <x:v>2024</x:v>
@@ -58395,7 +58407,7 @@
         <x:v>2576</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2549</x:v>
@@ -58418,19 +58430,19 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2549</x:v>
@@ -58441,16 +58453,16 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2553</x:v>
@@ -58459,13 +58471,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -58476,16 +58488,16 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2553</x:v>
@@ -58494,13 +58506,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -58511,31 +58523,31 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -58546,37 +58558,37 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K27" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -58587,10 +58599,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2553</x:v>
@@ -58599,86 +58611,86 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K28" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K29" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>2603</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>2604</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>2605</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>2606</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K30" s="1">
         <x:v>2026</x:v>
@@ -58686,66 +58698,66 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>2608</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K31" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
@@ -58756,16 +58768,16 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2553</x:v>
@@ -58774,19 +58786,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K33" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -58797,10 +58809,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>2613</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>2553</x:v>
@@ -58812,45 +58824,45 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K34" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2616</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2617</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -58867,10 +58879,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2546</x:v>
@@ -58879,13 +58891,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -58896,16 +58908,16 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2546</x:v>
@@ -58914,13 +58926,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -58966,16 +58978,16 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2546</x:v>
@@ -58984,13 +58996,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -59001,37 +59013,37 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K40" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -59057,45 +59069,45 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K41" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -59106,31 +59118,31 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -59147,10 +59159,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2553</x:v>
@@ -59159,13 +59171,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -59176,16 +59188,16 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2553</x:v>
@@ -59194,13 +59206,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -59211,31 +59223,31 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -59246,31 +59258,31 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -59281,37 +59293,37 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K48" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -59322,31 +59334,31 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K49" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -59357,10 +59369,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2546</x:v>
@@ -59369,13 +59381,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -59386,19 +59398,19 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2547</x:v>
@@ -59407,10 +59419,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -59421,101 +59433,101 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H52" s="1" t="s">
         <x:v>2630</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H52" s="1" t="s">
-        <x:v>2625</x:v>
-      </x:c>
       <x:c r="I52" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K52" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2631</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K53" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -59526,31 +59538,31 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -59561,31 +59573,31 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -59602,25 +59614,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -59631,16 +59643,16 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2546</x:v>
@@ -59649,19 +59661,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K58" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -59672,10 +59684,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>2636</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>2637</x:v>
-      </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>1296</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2546</x:v>
@@ -59684,48 +59696,48 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K59" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -59751,22 +59763,22 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -59786,22 +59798,22 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -59824,19 +59836,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K63" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -59847,10 +59859,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2553</x:v>
@@ -59862,16 +59874,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K64" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -59882,25 +59894,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
@@ -59917,80 +59929,80 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>2648</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>2649</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>1891</x:v>
-      </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>116161</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2553</x:v>
@@ -59999,33 +60011,33 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>999284</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2546</x:v>
@@ -60034,13 +60046,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>209387</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -60051,16 +60063,16 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2553</x:v>
@@ -60069,13 +60081,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
         <x:v>2548</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>257695</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
@@ -60086,10 +60098,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2654</x:v>
@@ -60098,33 +60110,33 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>558813</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K71" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2656</x:v>
@@ -60133,74 +60145,74 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
         <x:v>2659</x:v>
       </x:c>
-      <x:c r="D73" s="1" t="s">
-        <x:v>2660</x:v>
-      </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
         <x:v>2661</x:v>
-      </x:c>
-      <x:c r="D74" s="1" t="s">
-        <x:v>2662</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2546</x:v>
@@ -60209,13 +60221,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>817066</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2565</x:v>
@@ -60232,10 +60244,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2546</x:v>
@@ -60244,13 +60256,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>88256</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -60267,45 +60279,45 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>10041119</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="K76" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2546</x:v>
@@ -60314,13 +60326,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>1491280</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
@@ -60331,51 +60343,51 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
         <x:v>2546</x:v>
@@ -60384,13 +60396,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2549</x:v>
@@ -60401,104 +60413,104 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>10046680</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>817169</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1531015</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K82" s="1">
         <x:v>2024</x:v>
@@ -60506,31 +60518,31 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2549</x:v>
@@ -60547,25 +60559,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2549</x:v>
@@ -60582,31 +60594,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -60617,74 +60629,74 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
+        <x:v>1312</x:v>
+      </x:c>
+      <x:c r="E86" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F86" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G86" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H86" s="1" t="s">
         <x:v>2675</x:v>
       </x:c>
-      <x:c r="E86" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F86" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G86" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H86" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I86" s="1">
-        <x:v>9866096</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>119644</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2676</x:v>
@@ -60693,25 +60705,25 @@
         <x:v>2677</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>106947</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -60722,31 +60734,31 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>902176</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K89" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
@@ -60766,51 +60778,51 @@
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1010142</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -60821,16 +60833,16 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2546</x:v>
@@ -60842,10 +60854,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>110148</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -60856,16 +60868,16 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2546</x:v>
@@ -60874,13 +60886,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>63084</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
@@ -60891,31 +60903,31 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>10000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2549</x:v>
@@ -60926,31 +60938,31 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1306863</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2549</x:v>
@@ -60961,16 +60973,16 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
@@ -60979,13 +60991,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>889852</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
@@ -60996,36 +61008,141 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
+        <x:v>2684</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
+        <x:v>2685</x:v>
+      </x:c>
+      <x:c r="E97" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F97" s="1" t="s">
         <x:v>2686</x:v>
       </x:c>
-      <x:c r="D97" s="1" t="s">
+      <x:c r="G97" s="1" t="s">
         <x:v>2687</x:v>
       </x:c>
-      <x:c r="E97" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F97" s="1" t="s">
-        <x:v>2547</x:v>
-      </x:c>
-      <x:c r="G97" s="1" t="s">
-        <x:v>172</x:v>
-      </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>1012792</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K97" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:11">
+      <x:c r="A98" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B98" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
+        <x:v>2688</x:v>
+      </x:c>
+      <x:c r="D98" s="1" t="s">
+        <x:v>2689</x:v>
+      </x:c>
+      <x:c r="E98" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F98" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G98" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H98" s="1" t="s">
+        <x:v>2652</x:v>
+      </x:c>
+      <x:c r="I98" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J98" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K98" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:11">
+      <x:c r="A99" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B99" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D99" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="E99" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F99" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G99" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H99" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="I99" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J99" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K99" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:11">
+      <x:c r="A100" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
+        <x:v>2690</x:v>
+      </x:c>
+      <x:c r="D100" s="1" t="s">
+        <x:v>2691</x:v>
+      </x:c>
+      <x:c r="E100" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F100" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G100" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H100" s="1" t="s">
+        <x:v>2662</x:v>
+      </x:c>
+      <x:c r="I100" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J100" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K100" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61045,7 +61162,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J95"/>
+  <x:dimension ref="A1:J98"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61543,31 +61660,31 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2018</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>211281</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61575,31 +61692,31 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>973501</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2549</x:v>
@@ -61607,31 +61724,31 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>2035</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
         <x:v>2587</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>2044</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>1700</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I18" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
@@ -61639,16 +61756,16 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2553</x:v>
@@ -61657,13 +61774,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
@@ -61671,42 +61788,42 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2591</x:v>
@@ -61721,16 +61838,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
@@ -61759,7 +61876,7 @@
         <x:v>2576</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2549</x:v>
@@ -61779,19 +61896,19 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2549</x:v>
@@ -61799,16 +61916,16 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2553</x:v>
@@ -61817,13 +61934,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -61831,16 +61948,16 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2553</x:v>
@@ -61849,13 +61966,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -61863,31 +61980,31 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -61895,31 +62012,31 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
@@ -61933,10 +62050,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2553</x:v>
@@ -61945,13 +62062,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
@@ -61959,95 +62076,95 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>2603</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>2604</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>2605</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>2606</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>2608</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2549</x:v>
@@ -62055,31 +62172,31 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
@@ -62087,16 +62204,16 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2553</x:v>
@@ -62105,13 +62222,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
@@ -62125,10 +62242,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>2613</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>2553</x:v>
@@ -62140,10 +62257,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -62151,31 +62268,31 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2616</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2617</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -62189,10 +62306,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2546</x:v>
@@ -62201,13 +62318,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -62221,10 +62338,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2546</x:v>
@@ -62233,13 +62350,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -62285,10 +62402,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2546</x:v>
@@ -62297,13 +62414,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -62311,31 +62428,31 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -62343,31 +62460,31 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -62375,31 +62492,31 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -62413,10 +62530,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2553</x:v>
@@ -62425,13 +62542,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -62439,16 +62556,16 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2553</x:v>
@@ -62457,13 +62574,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -62471,31 +62588,31 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -62503,31 +62620,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -62535,31 +62652,31 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -62573,25 +62690,25 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -62605,10 +62722,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2546</x:v>
@@ -62617,13 +62734,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -62631,19 +62748,19 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
         <x:v>2547</x:v>
@@ -62652,10 +62769,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -62663,31 +62780,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H51" s="1" t="s">
         <x:v>2630</x:v>
       </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H51" s="1" t="s">
-        <x:v>2625</x:v>
-      </x:c>
       <x:c r="I51" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -62695,31 +62812,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2631</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -62727,31 +62844,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -62759,31 +62876,31 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -62791,31 +62908,31 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -62829,25 +62946,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -62855,16 +62972,16 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2546</x:v>
@@ -62873,13 +62990,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -62893,10 +63010,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>2636</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>2637</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>1296</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2546</x:v>
@@ -62905,13 +63022,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -62919,31 +63036,31 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -62966,16 +63083,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -62998,16 +63115,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -63033,13 +63150,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
@@ -63053,25 +63170,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -63085,25 +63202,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -63111,31 +63228,31 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>2648</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>2649</x:v>
       </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>1891</x:v>
-      </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>116161</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
@@ -63143,16 +63260,16 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2553</x:v>
@@ -63161,13 +63278,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>999284</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
@@ -63175,16 +63292,16 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>2546</x:v>
@@ -63193,13 +63310,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>209387</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
@@ -63207,16 +63324,16 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2553</x:v>
@@ -63225,13 +63342,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
         <x:v>2548</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>257695</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -63239,10 +63356,10 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2654</x:v>
@@ -63251,19 +63368,19 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>558813</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -63271,10 +63388,10 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2656</x:v>
@@ -63283,51 +63400,51 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>2659</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>2660</x:v>
-      </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
@@ -63335,16 +63452,16 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
         <x:v>2661</x:v>
-      </x:c>
-      <x:c r="D72" s="1" t="s">
-        <x:v>2662</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2546</x:v>
@@ -63353,13 +63470,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>817066</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2565</x:v>
@@ -63373,10 +63490,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2546</x:v>
@@ -63385,13 +63502,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>88256</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
@@ -63405,25 +63522,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>10041119</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2565</x:v>
@@ -63431,16 +63548,16 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2546</x:v>
@@ -63449,13 +63566,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>1491280</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -63463,48 +63580,48 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2546</x:v>
@@ -63513,13 +63630,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
@@ -63527,31 +63644,31 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>10046680</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2549</x:v>
@@ -63559,31 +63676,31 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>817169</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2549</x:v>
@@ -63591,63 +63708,63 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1531015</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2549</x:v>
@@ -63661,25 +63778,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2549</x:v>
@@ -63693,60 +63810,60 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
+        <x:v>1312</x:v>
+      </x:c>
+      <x:c r="E84" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F84" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G84" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H84" s="1" t="s">
         <x:v>2675</x:v>
       </x:c>
-      <x:c r="E84" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F84" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G84" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H84" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I84" s="1">
-        <x:v>119644</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:10">
@@ -63757,36 +63874,36 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>9866096</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2676</x:v>
@@ -63795,19 +63912,19 @@
         <x:v>2677</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>106947</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2549</x:v>
@@ -63821,28 +63938,28 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>902176</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:10">
@@ -63862,48 +63979,48 @@
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1010142</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2549</x:v>
@@ -63911,16 +64028,16 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2546</x:v>
@@ -63932,10 +64049,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>110148</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -63943,16 +64060,16 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2546</x:v>
@@ -63961,13 +64078,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>63084</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -63975,31 +64092,31 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>10000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -64007,31 +64124,31 @@
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1306863</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
@@ -64039,16 +64156,16 @@
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2546</x:v>
@@ -64057,13 +64174,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>889852</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2549</x:v>
@@ -64071,33 +64188,129 @@
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
+        <x:v>2588</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
+        <x:v>2589</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
+        <x:v>2684</x:v>
+      </x:c>
+      <x:c r="D95" s="1" t="s">
+        <x:v>2685</x:v>
+      </x:c>
+      <x:c r="E95" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F95" s="1" t="s">
+        <x:v>2686</x:v>
+      </x:c>
+      <x:c r="G95" s="1" t="s">
+        <x:v>2687</x:v>
+      </x:c>
+      <x:c r="H95" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="I95" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J95" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:10">
+      <x:c r="A96" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B96" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
+        <x:v>2688</x:v>
+      </x:c>
+      <x:c r="D96" s="1" t="s">
+        <x:v>2689</x:v>
+      </x:c>
+      <x:c r="E96" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F96" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G96" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H96" s="1" t="s">
+        <x:v>2652</x:v>
+      </x:c>
+      <x:c r="I96" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J96" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:10">
+      <x:c r="A97" s="1" t="s">
         <x:v>2542</x:v>
       </x:c>
-      <x:c r="B95" s="1" t="s">
+      <x:c r="B97" s="1" t="s">
         <x:v>2543</x:v>
       </x:c>
-      <x:c r="C95" s="1" t="s">
-        <x:v>2686</x:v>
-      </x:c>
-      <x:c r="D95" s="1" t="s">
-        <x:v>2687</x:v>
-      </x:c>
-      <x:c r="E95" s="1" t="s">
+      <x:c r="C97" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="E97" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
-      <x:c r="F95" s="1" t="s">
+      <x:c r="F97" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
-      <x:c r="G95" s="1" t="s">
+      <x:c r="G97" s="1" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H95" s="1" t="s">
-        <x:v>2658</x:v>
-      </x:c>
-      <x:c r="I95" s="1">
+      <x:c r="H97" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="I97" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J97" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:10">
+      <x:c r="A98" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B98" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
+        <x:v>2690</x:v>
+      </x:c>
+      <x:c r="D98" s="1" t="s">
+        <x:v>2691</x:v>
+      </x:c>
+      <x:c r="E98" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F98" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G98" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H98" s="1" t="s">
+        <x:v>2662</x:v>
+      </x:c>
+      <x:c r="I98" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J95" s="1" t="s">
+      <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>
@@ -64117,7 +64330,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C91"/>
+  <x:dimension ref="A1:C94"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -64282,10 +64495,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>211281</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>
@@ -64293,10 +64506,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>973501</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64304,10 +64517,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2549</x:v>
@@ -64315,10 +64528,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2549</x:v>
@@ -64326,13 +64539,13 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -64340,10 +64553,10 @@
         <x:v>2592</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -64351,7 +64564,7 @@
         <x:v>2594</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2549</x:v>
@@ -64362,7 +64575,7 @@
         <x:v>2596</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2549</x:v>
@@ -64370,10 +64583,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2549</x:v>
@@ -64381,10 +64594,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2549</x:v>
@@ -64392,10 +64605,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2549</x:v>
@@ -64403,10 +64616,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2549</x:v>
@@ -64414,10 +64627,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2549</x:v>
@@ -64425,32 +64638,32 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>2549</x:v>
@@ -64458,10 +64671,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>2549</x:v>
@@ -64469,10 +64682,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2549</x:v>
@@ -64480,10 +64693,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2549</x:v>
@@ -64491,10 +64704,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2549</x:v>
@@ -64502,10 +64715,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2549</x:v>
@@ -64513,10 +64726,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2549</x:v>
@@ -64524,10 +64737,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2549</x:v>
@@ -64535,10 +64748,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2549</x:v>
@@ -64546,10 +64759,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2549</x:v>
@@ -64557,10 +64770,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2549</x:v>
@@ -64568,10 +64781,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2549</x:v>
@@ -64579,10 +64792,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2549</x:v>
@@ -64590,10 +64803,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2549</x:v>
@@ -64601,10 +64814,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2549</x:v>
@@ -64612,10 +64825,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2549</x:v>
@@ -64623,10 +64836,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2549</x:v>
@@ -64634,10 +64847,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2549</x:v>
@@ -64645,10 +64858,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2549</x:v>
@@ -64656,10 +64869,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2549</x:v>
@@ -64667,10 +64880,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2549</x:v>
@@ -64678,10 +64891,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2549</x:v>
@@ -64689,10 +64902,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2549</x:v>
@@ -64700,10 +64913,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2549</x:v>
@@ -64711,10 +64924,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2549</x:v>
@@ -64722,10 +64935,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>1564215</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2549</x:v>
@@ -64733,10 +64946,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>215063</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2549</x:v>
@@ -64744,10 +64957,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2549</x:v>
@@ -64758,7 +64971,7 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>
@@ -64769,7 +64982,7 @@
         <x:v>2643</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2549</x:v>
@@ -64780,7 +64993,7 @@
         <x:v>2645</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2549</x:v>
@@ -64788,10 +65001,10 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2549</x:v>
@@ -64799,10 +65012,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2549</x:v>
@@ -64810,10 +65023,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>116161</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2549</x:v>
@@ -64821,10 +65034,10 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>999284</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2549</x:v>
@@ -64832,10 +65045,10 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>209387</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2549</x:v>
@@ -64843,10 +65056,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>257695</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2549</x:v>
@@ -64857,7 +65070,7 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>558813</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2549</x:v>
@@ -64868,18 +65081,18 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2549</x:v>
@@ -64887,10 +65100,10 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>817066</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2565</x:v>
@@ -64898,10 +65111,10 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>88256</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2549</x:v>
@@ -64909,10 +65122,10 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>10041119</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2565</x:v>
@@ -64920,10 +65133,10 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>1491280</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2549</x:v>
@@ -64931,21 +65144,21 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2549</x:v>
@@ -64953,10 +65166,10 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>10046680</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2549</x:v>
@@ -64964,10 +65177,10 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>817169</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2549</x:v>
@@ -64975,21 +65188,21 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>1531015</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2549</x:v>
@@ -64997,10 +65210,10 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2549</x:v>
@@ -65008,32 +65221,32 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>9985740</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>106947</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2549</x:v>
@@ -65041,10 +65254,10 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>902176</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2549</x:v>
@@ -65055,18 +65268,18 @@
         <x:v>2679</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>1010142</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2549</x:v>
@@ -65074,10 +65287,10 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>173232</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2549</x:v>
@@ -65085,10 +65298,10 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>10000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2549</x:v>
@@ -65096,10 +65309,10 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2549</x:v>
@@ -65107,10 +65320,10 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>889852</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>2549</x:v>
@@ -65118,12 +65331,45 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B91" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:3">
+      <x:c r="A92" s="1" t="s">
+        <x:v>2689</x:v>
+      </x:c>
+      <x:c r="B92" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:3">
+      <x:c r="A93" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="B93" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:3">
+      <x:c r="A94" s="1" t="s">
+        <x:v>2691</x:v>
+      </x:c>
+      <x:c r="B94" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C91" s="1" t="s">
+      <x:c r="C94" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35776,10 +35776,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35791,7 +35791,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35802,10 +35802,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35817,7 +35817,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35776,10 +35776,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35791,7 +35791,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35802,10 +35802,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35817,7 +35817,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -58197,7 +58197,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61684,7 +61684,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64498,7 +64498,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -58197,7 +58197,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61684,7 +61684,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64498,7 +64498,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -58197,7 +58197,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61684,7 +61684,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64498,7 +64498,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35776,10 +35776,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35791,7 +35791,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35802,10 +35802,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35817,7 +35817,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -58197,7 +58197,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61684,7 +61684,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64498,7 +64498,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7782,6 +7782,18 @@
     <x:t>04</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
@@ -7836,12 +7848,6 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -7920,6 +7926,12 @@
     <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H4AZ08124</x:t>
   </x:si>
   <x:si>
@@ -7947,6 +7959,12 @@
     <x:t>MESSMER, MARK MR.</x:t>
   </x:si>
   <x:si>
+    <x:t>S6LA00540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6AL00476</x:t>
   </x:si>
   <x:si>
@@ -7999,6 +8017,12 @@
   </x:si>
   <x:si>
     <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6TX00388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
   <x:si>
     <x:t>H6VA11074</x:t>
@@ -8216,8 +8240,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K100" totalsRowShown="0">
-  <x:autoFilter ref="A1:K100"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K105" totalsRowShown="0">
+  <x:autoFilter ref="A1:K105"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8236,8 +8260,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J98" totalsRowShown="0">
-  <x:autoFilter ref="A1:J98"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J103" totalsRowShown="0">
+  <x:autoFilter ref="A1:J103"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8255,8 +8279,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C94" totalsRowShown="0">
-  <x:autoFilter ref="A1:C94"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C98" totalsRowShown="0">
+  <x:autoFilter ref="A1:C98"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57629,7 +57653,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K100"/>
+  <x:dimension ref="A1:K105"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58243,66 +58267,66 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K18" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2044</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
@@ -58313,16 +58337,16 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2553</x:v>
@@ -58331,13 +58355,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2549</x:v>
@@ -58348,34 +58372,34 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K21" s="1">
         <x:v>2024</x:v>
@@ -58383,16 +58407,16 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>2546</x:v>
@@ -58401,16 +58425,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K22" s="1">
         <x:v>2024</x:v>
@@ -58424,10 +58448,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2546</x:v>
@@ -58442,7 +58466,7 @@
         <x:v>2576</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2549</x:v>
@@ -58459,25 +58483,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -58488,16 +58512,16 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2553</x:v>
@@ -58506,13 +58530,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -58523,16 +58547,16 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2553</x:v>
@@ -58541,13 +58565,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -58558,31 +58582,31 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
@@ -58593,37 +58617,37 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K28" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -58634,10 +58658,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2553</x:v>
@@ -58646,86 +58670,86 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K29" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K30" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>2606</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
         <x:v>2607</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>2608</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K31" s="1">
         <x:v>2026</x:v>
@@ -58733,66 +58757,66 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>2610</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K32" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
@@ -58803,16 +58827,16 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>2553</x:v>
@@ -58821,19 +58845,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K34" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -58844,10 +58868,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2615</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2616</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2553</x:v>
@@ -58859,45 +58883,45 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K35" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2617</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>2618</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>2619</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -58914,10 +58938,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2546</x:v>
@@ -58926,13 +58950,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -58949,10 +58973,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -58961,13 +58985,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -58978,10 +59002,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2127</x:v>
@@ -59002,7 +59026,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -59013,16 +59037,16 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2546</x:v>
@@ -59031,13 +59055,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -59048,37 +59072,37 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K41" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -59104,45 +59128,45 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K42" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -59153,31 +59177,31 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -59194,10 +59218,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2553</x:v>
@@ -59206,13 +59230,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -59223,16 +59247,16 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>2553</x:v>
@@ -59241,13 +59265,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -59258,31 +59282,31 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -59293,31 +59317,31 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -59328,37 +59352,37 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K49" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -59369,31 +59393,31 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K50" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -59404,10 +59428,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2546</x:v>
@@ -59416,13 +59440,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -59433,19 +59457,19 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2547</x:v>
@@ -59454,10 +59478,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -59468,136 +59492,136 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H53" s="1" t="s">
         <x:v>2632</x:v>
       </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H53" s="1" t="s">
-        <x:v>2627</x:v>
-      </x:c>
       <x:c r="I53" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K53" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2633</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K54" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K55" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -59608,31 +59632,31 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -59643,31 +59667,31 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -59678,51 +59702,51 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>1564215</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K59" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2546</x:v>
@@ -59731,13 +59755,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>215063</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -59748,10 +59772,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2640</x:v>
@@ -59760,60 +59784,60 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>504020</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>10049014</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -59836,13 +59860,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -59853,10 +59877,10 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2646</x:v>
@@ -59868,16 +59892,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>161896</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -59888,37 +59912,37 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>506553</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K65" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -59929,10 +59953,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2553</x:v>
@@ -59941,54 +59965,54 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>40134929</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>850000</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -59999,10 +60023,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2553</x:v>
@@ -60011,13 +60035,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>282526</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -60028,19 +60052,19 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
+        <x:v>2652</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
         <x:v>2653</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>1891</x:v>
-      </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2547</x:v>
@@ -60049,10 +60073,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>116161</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -60063,31 +60087,31 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>999284</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
@@ -60098,10 +60122,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2654</x:v>
@@ -60110,25 +60134,25 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>209387</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K71" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -60151,103 +60175,103 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>257695</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>558813</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>20483</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2546</x:v>
@@ -60256,13 +60280,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>1927706</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -60273,107 +60297,107 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>817066</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K76" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>88256</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>1077</x:v>
-      </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>10041119</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -60396,86 +60420,86 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1491280</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K79" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2379</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>350000</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>91847</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K81" s="1">
         <x:v>2026</x:v>
@@ -60489,10 +60513,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2546</x:v>
@@ -60501,13 +60525,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1987660</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2549</x:v>
@@ -60518,16 +60542,16 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2546</x:v>
@@ -60536,16 +60560,16 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>10046680</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K83" s="1">
         <x:v>2024</x:v>
@@ -60553,16 +60577,16 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2546</x:v>
@@ -60571,13 +60595,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>817169</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2549</x:v>
@@ -60588,16 +60612,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2553</x:v>
@@ -60606,54 +60630,54 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1531015</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>2791716</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -60664,25 +60688,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>764206</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2549</x:v>
@@ -60693,37 +60717,37 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1543316</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -60734,95 +60758,95 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>9866096</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K89" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>119644</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>106947</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -60839,25 +60863,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>902176</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -60868,121 +60892,121 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>1860445</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>110148</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K95" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
@@ -60991,13 +61015,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>63084</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
@@ -61008,31 +61032,31 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>10000</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
@@ -61043,31 +61067,31 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
@@ -61078,31 +61102,31 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>889852</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2549</x:v>
@@ -61119,10 +61143,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2546</x:v>
@@ -61131,18 +61155,193 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>1012792</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K100" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:11">
+      <x:c r="A101" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>2482</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F101" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G101" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H101" s="1" t="s">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="I101" s="1">
+        <x:v>63084</x:v>
+      </x:c>
+      <x:c r="J101" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K101" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:11">
+      <x:c r="A102" s="1" t="s">
+        <x:v>2592</x:v>
+      </x:c>
+      <x:c r="B102" s="1" t="s">
+        <x:v>2593</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
+        <x:v>2692</x:v>
+      </x:c>
+      <x:c r="D102" s="1" t="s">
+        <x:v>2693</x:v>
+      </x:c>
+      <x:c r="E102" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F102" s="1" t="s">
+        <x:v>2694</x:v>
+      </x:c>
+      <x:c r="G102" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="H102" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="I102" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J102" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K102" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:11">
+      <x:c r="A103" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>2696</x:v>
+      </x:c>
+      <x:c r="D103" s="1" t="s">
+        <x:v>2697</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F103" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G103" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H103" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="I103" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J103" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K103" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:11">
+      <x:c r="A104" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D104" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="E104" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F104" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G104" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H104" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="I104" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J104" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K104" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:11">
+      <x:c r="A105" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B105" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C105" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D105" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F105" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H105" s="1" t="s">
+        <x:v>2670</x:v>
+      </x:c>
+      <x:c r="I105" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J105" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K105" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61162,7 +61361,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J98"/>
+  <x:dimension ref="A1:J103"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61436,10 +61635,10 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>1977</x:v>
@@ -61460,7 +61659,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2549</x:v>
@@ -61468,10 +61667,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>1977</x:v>
@@ -61492,7 +61691,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2549</x:v>
@@ -61724,31 +61923,31 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
@@ -61756,31 +61955,31 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2044</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
@@ -61788,16 +61987,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2553</x:v>
@@ -61806,13 +62005,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2549</x:v>
@@ -61820,48 +62019,48 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>2546</x:v>
@@ -61870,16 +62069,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
@@ -61890,10 +62089,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2546</x:v>
@@ -61908,7 +62107,7 @@
         <x:v>2576</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2549</x:v>
@@ -61922,25 +62121,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -61948,16 +62147,16 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2553</x:v>
@@ -61966,13 +62165,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -61980,16 +62179,16 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2553</x:v>
@@ -61998,13 +62197,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -62012,31 +62211,31 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
@@ -62044,31 +62243,31 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
@@ -62082,10 +62281,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2553</x:v>
@@ -62094,13 +62293,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2549</x:v>
@@ -62108,95 +62307,95 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>2606</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
         <x:v>2607</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>2608</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>2610</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>811</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2549</x:v>
@@ -62204,31 +62403,31 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
@@ -62236,16 +62435,16 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>2553</x:v>
@@ -62254,13 +62453,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -62274,10 +62473,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2615</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2616</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2553</x:v>
@@ -62289,10 +62488,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -62300,31 +62499,31 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2617</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>2618</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>2619</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -62338,10 +62537,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2546</x:v>
@@ -62350,13 +62549,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -62364,16 +62563,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -62382,13 +62581,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -62428,16 +62627,16 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2546</x:v>
@@ -62446,13 +62645,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -62460,31 +62659,31 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -62492,31 +62691,31 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -62524,31 +62723,31 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
         <x:v>2586</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -62562,10 +62761,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2553</x:v>
@@ -62574,13 +62773,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -62588,16 +62787,16 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2553</x:v>
@@ -62606,13 +62805,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -62620,31 +62819,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -62652,31 +62851,31 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -62684,31 +62883,31 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -62722,25 +62921,25 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -62754,10 +62953,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2546</x:v>
@@ -62766,13 +62965,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -62780,19 +62979,19 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2547</x:v>
@@ -62801,10 +63000,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -62812,31 +63011,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
+        <x:v>1909</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H52" s="1" t="s">
         <x:v>2632</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>2546</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H52" s="1" t="s">
-        <x:v>2627</x:v>
-      </x:c>
       <x:c r="I52" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -62844,31 +63043,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2633</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -62876,31 +63075,31 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -62908,31 +63107,31 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -62940,31 +63139,31 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -62972,31 +63171,31 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -63004,31 +63203,31 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>1564215</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -63036,16 +63235,16 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2546</x:v>
@@ -63054,13 +63253,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>215063</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -63068,10 +63267,10 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2640</x:v>
@@ -63080,19 +63279,19 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>504020</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -63100,31 +63299,31 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>10049014</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -63150,13 +63349,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
@@ -63164,10 +63363,10 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2646</x:v>
@@ -63179,16 +63378,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>668449</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -63202,10 +63401,10 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2553</x:v>
@@ -63214,13 +63413,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>40134929</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -63228,10 +63427,10 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2648</x:v>
@@ -63246,13 +63445,13 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
@@ -63278,13 +63477,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>282526</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
@@ -63292,19 +63491,19 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>2652</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>2653</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>1891</x:v>
-      </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2547</x:v>
@@ -63313,10 +63512,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>116161</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
@@ -63324,31 +63523,31 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>999284</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -63356,10 +63555,10 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2654</x:v>
@@ -63368,19 +63567,19 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>209387</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -63406,13 +63605,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>257695</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
@@ -63420,31 +63619,31 @@
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>558813</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
@@ -63452,48 +63651,48 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>20483</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2546</x:v>
@@ -63502,13 +63701,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>1927706</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
@@ -63516,63 +63715,63 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>817066</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>88256</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -63580,34 +63779,34 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
-      <x:c r="D76" s="1" t="s">
-        <x:v>1077</x:v>
-      </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>10041119</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:10">
@@ -63630,45 +63829,45 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>1491280</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2379</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>350000</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2549</x:v>
@@ -63676,34 +63875,34 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>91847</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:10">
@@ -63714,10 +63913,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2546</x:v>
@@ -63726,13 +63925,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1987660</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2549</x:v>
@@ -63740,16 +63939,16 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2546</x:v>
@@ -63758,30 +63957,30 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>10046680</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2546</x:v>
@@ -63790,13 +63989,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>817169</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2549</x:v>
@@ -63804,16 +64003,16 @@
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2553</x:v>
@@ -63822,45 +64021,45 @@
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>1531015</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>2791716</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2549</x:v>
@@ -63874,25 +64073,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>764206</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2549</x:v>
@@ -63900,31 +64099,31 @@
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>1543316</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2549</x:v>
@@ -63938,57 +64137,57 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>9866096</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2554</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>119644</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2565</x:v>
@@ -63996,31 +64195,31 @@
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>106947</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2549</x:v>
@@ -64034,25 +64233,25 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>902176</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -64060,31 +64259,31 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -64092,80 +64291,80 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>1860445</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>110148</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2546</x:v>
@@ -64174,13 +64373,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>63084</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2549</x:v>
@@ -64188,31 +64387,31 @@
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>10000</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2549</x:v>
@@ -64220,31 +64419,31 @@
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
@@ -64252,31 +64451,31 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>889852</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
@@ -64284,16 +64483,16 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2546</x:v>
@@ -64302,15 +64501,175 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H98" s="1" t="s">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="I98" s="1">
+        <x:v>63084</x:v>
+      </x:c>
+      <x:c r="J98" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:10">
+      <x:c r="A99" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B99" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
+        <x:v>2482</x:v>
+      </x:c>
+      <x:c r="D99" s="1" t="s">
+        <x:v>1782</x:v>
+      </x:c>
+      <x:c r="E99" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F99" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G99" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H99" s="1" t="s">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="I99" s="1">
+        <x:v>110148</x:v>
+      </x:c>
+      <x:c r="J99" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:10">
+      <x:c r="A100" s="1" t="s">
+        <x:v>2592</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
+        <x:v>2593</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
+        <x:v>2692</x:v>
+      </x:c>
+      <x:c r="D100" s="1" t="s">
+        <x:v>2693</x:v>
+      </x:c>
+      <x:c r="E100" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F100" s="1" t="s">
+        <x:v>2694</x:v>
+      </x:c>
+      <x:c r="G100" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="H100" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="I100" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J100" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:10">
+      <x:c r="A101" s="1" t="s">
+        <x:v>2566</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
+        <x:v>2567</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>2696</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
+        <x:v>2697</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="F101" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G101" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H101" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="I101" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J101" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:10">
+      <x:c r="A102" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B102" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D102" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="E102" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F102" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G102" s="1" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H98" s="1" t="s">
-        <x:v>2662</x:v>
-      </x:c>
-      <x:c r="I98" s="1">
+      <x:c r="H102" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="I102" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J102" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:10">
+      <x:c r="A103" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D103" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F103" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G103" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H103" s="1" t="s">
+        <x:v>2670</x:v>
+      </x:c>
+      <x:c r="I103" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J98" s="1" t="s">
+      <x:c r="J103" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>
@@ -64330,7 +64689,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C94"/>
+  <x:dimension ref="A1:C98"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -64517,10 +64876,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2549</x:v>
@@ -64528,10 +64887,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2549</x:v>
@@ -64539,10 +64898,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2549</x:v>
@@ -64550,32 +64909,32 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2549</x:v>
@@ -64583,10 +64942,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2549</x:v>
@@ -64594,10 +64953,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2549</x:v>
@@ -64605,10 +64964,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2549</x:v>
@@ -64616,10 +64975,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2549</x:v>
@@ -64627,10 +64986,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2549</x:v>
@@ -64638,10 +64997,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2549</x:v>
@@ -64649,32 +65008,32 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>2549</x:v>
@@ -64682,10 +65041,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2549</x:v>
@@ -64693,10 +65052,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2549</x:v>
@@ -64704,10 +65063,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2549</x:v>
@@ -64715,10 +65074,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2549</x:v>
@@ -64726,10 +65085,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2549</x:v>
@@ -64737,10 +65096,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2549</x:v>
@@ -64748,10 +65107,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2549</x:v>
@@ -64759,10 +65118,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2549</x:v>
@@ -64770,10 +65129,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2549</x:v>
@@ -64781,10 +65140,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2549</x:v>
@@ -64792,10 +65151,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2549</x:v>
@@ -64803,10 +65162,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2549</x:v>
@@ -64814,10 +65173,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2549</x:v>
@@ -64825,10 +65184,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2549</x:v>
@@ -64836,10 +65195,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2549</x:v>
@@ -64847,10 +65206,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2549</x:v>
@@ -64858,10 +65217,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2549</x:v>
@@ -64869,10 +65228,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2549</x:v>
@@ -64880,10 +65239,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2549</x:v>
@@ -64891,10 +65250,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2549</x:v>
@@ -64902,10 +65261,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2549</x:v>
@@ -64913,10 +65272,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2549</x:v>
@@ -64924,10 +65283,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2549</x:v>
@@ -64935,10 +65294,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2549</x:v>
@@ -64946,10 +65305,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>1564215</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2549</x:v>
@@ -64957,10 +65316,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>215063</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2549</x:v>
@@ -64971,7 +65330,7 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>504020</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>
@@ -64979,10 +65338,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>10049014</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2549</x:v>
@@ -64993,7 +65352,7 @@
         <x:v>2645</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2549</x:v>
@@ -65004,7 +65363,7 @@
         <x:v>2647</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>668449</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2549</x:v>
@@ -65012,10 +65371,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>40134929</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2549</x:v>
@@ -65023,10 +65382,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>850000</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2549</x:v>
@@ -65034,10 +65393,10 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>282526</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2549</x:v>
@@ -65045,10 +65404,10 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>116161</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2549</x:v>
@@ -65056,10 +65415,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>999284</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2549</x:v>
@@ -65067,10 +65426,10 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>209387</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2549</x:v>
@@ -65078,10 +65437,10 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>257695</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2549</x:v>
@@ -65089,10 +65448,10 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>558813</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2549</x:v>
@@ -65103,18 +65462,18 @@
         <x:v>2661</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>20483</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>1927706</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2549</x:v>
@@ -65122,21 +65481,21 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>817066</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>88256</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2549</x:v>
@@ -65144,10 +65503,10 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>10041119</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2565</x:v>
@@ -65155,10 +65514,10 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>1491280</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2549</x:v>
@@ -65166,21 +65525,21 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>91847</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2549</x:v>
@@ -65188,21 +65547,21 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>1987660</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2549</x:v>
@@ -65210,10 +65569,10 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>817169</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2549</x:v>
@@ -65221,21 +65580,21 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>1531015</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>2549</x:v>
@@ -65243,10 +65602,10 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>764206</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2549</x:v>
@@ -65254,10 +65613,10 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>1543316</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2549</x:v>
@@ -65265,10 +65624,10 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2565</x:v>
@@ -65276,10 +65635,10 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>106947</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2549</x:v>
@@ -65287,10 +65646,10 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>902176</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2549</x:v>
@@ -65298,10 +65657,10 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2549</x:v>
@@ -65309,21 +65668,21 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>1860445</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>173232</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>2549</x:v>
@@ -65331,10 +65690,10 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>10000</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>2549</x:v>
@@ -65342,10 +65701,10 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2549</x:v>
@@ -65353,10 +65712,10 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>889852</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>2549</x:v>
@@ -65364,12 +65723,56 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="B94" s="1">
+        <x:v>173232</x:v>
+      </x:c>
+      <x:c r="C94" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:3">
+      <x:c r="A95" s="1" t="s">
+        <x:v>2693</x:v>
+      </x:c>
+      <x:c r="B95" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:3">
+      <x:c r="A96" s="1" t="s">
+        <x:v>2697</x:v>
+      </x:c>
+      <x:c r="B96" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:3">
+      <x:c r="A97" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="B97" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:3">
+      <x:c r="A98" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="B98" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C94" s="1" t="s">
+      <x:c r="C98" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8240,8 +8240,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K105" totalsRowShown="0">
-  <x:autoFilter ref="A1:K105"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K106" totalsRowShown="0">
+  <x:autoFilter ref="A1:K106"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8260,8 +8260,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J103" totalsRowShown="0">
-  <x:autoFilter ref="A1:J103"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J104" totalsRowShown="0">
+  <x:autoFilter ref="A1:J104"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8279,8 +8279,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C98" totalsRowShown="0">
-  <x:autoFilter ref="A1:C98"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C99" totalsRowShown="0">
+  <x:autoFilter ref="A1:C99"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57653,7 +57653,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K105"/>
+  <x:dimension ref="A1:K106"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -60723,60 +60723,60 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2420</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2549</x:v>
@@ -60787,34 +60787,34 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K90" s="1">
         <x:v>2024</x:v>
@@ -60822,34 +60822,34 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K91" s="1">
         <x:v>2024</x:v>
@@ -60863,10 +60863,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2553</x:v>
@@ -60875,13 +60875,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -60892,16 +60892,16 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2553</x:v>
@@ -60910,51 +60910,51 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K94" s="1">
         <x:v>2026</x:v>
@@ -60962,10 +60962,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2686</x:v>
@@ -60986,7 +60986,7 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2565</x:v>
@@ -60997,51 +60997,51 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="K96" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2546</x:v>
@@ -61050,13 +61050,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
@@ -61067,16 +61067,16 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2546</x:v>
@@ -61085,13 +61085,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
@@ -61102,31 +61102,31 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2549</x:v>
@@ -61137,31 +61137,31 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>110148</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2549</x:v>
@@ -61172,10 +61172,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>2482</x:v>
@@ -61196,7 +61196,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2549</x:v>
@@ -61207,31 +61207,31 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2549</x:v>
@@ -61242,31 +61242,31 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2549</x:v>
@@ -61277,31 +61277,31 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2549</x:v>
@@ -61318,10 +61318,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
         <x:v>2546</x:v>
@@ -61333,15 +61333,50 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K105" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:11">
+      <x:c r="A106" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B106" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C106" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D106" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E106" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F106" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G106" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H106" s="1" t="s">
+        <x:v>2670</x:v>
+      </x:c>
+      <x:c r="I106" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J106" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K106" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61361,7 +61396,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J103"/>
+  <x:dimension ref="A1:J104"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -62595,10 +62630,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2127</x:v>
@@ -62619,7 +62654,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -62627,10 +62662,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2127</x:v>
@@ -62651,7 +62686,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -64105,57 +64140,57 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2420</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2549</x:v>
@@ -64163,66 +64198,66 @@
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:10">
@@ -64233,10 +64268,10 @@
         <x:v>2567</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2553</x:v>
@@ -64245,13 +64280,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -64259,16 +64294,16 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2553</x:v>
@@ -64277,13 +64312,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -64291,34 +64326,34 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:10">
@@ -64361,42 +64396,42 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>106947</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2546</x:v>
@@ -64405,13 +64440,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2549</x:v>
@@ -64419,16 +64454,16 @@
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
@@ -64437,13 +64472,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
@@ -64451,31 +64486,31 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
@@ -64483,31 +64518,31 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>63084</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
@@ -64547,31 +64582,31 @@
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2549</x:v>
@@ -64579,31 +64614,31 @@
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2549</x:v>
@@ -64611,31 +64646,31 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2549</x:v>
@@ -64649,10 +64684,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2546</x:v>
@@ -64664,12 +64699,44 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="I103" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J103" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:10">
+      <x:c r="A104" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D104" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E104" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F104" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G104" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H104" s="1" t="s">
         <x:v>2670</x:v>
       </x:c>
-      <x:c r="I103" s="1">
+      <x:c r="I104" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J103" s="1" t="s">
+      <x:c r="J104" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>
@@ -64689,7 +64756,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C98"/>
+  <x:dimension ref="A1:C99"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -65602,21 +65669,21 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2549</x:v>
@@ -65624,32 +65691,32 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2549</x:v>
@@ -65657,10 +65724,10 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2549</x:v>
@@ -65668,32 +65735,32 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>106947</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2565</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>2549</x:v>
@@ -65701,10 +65768,10 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2549</x:v>
@@ -65712,10 +65779,10 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>2549</x:v>
@@ -65723,10 +65790,10 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>173232</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2549</x:v>
@@ -65734,10 +65801,10 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>10000</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2549</x:v>
@@ -65745,10 +65812,10 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2549</x:v>
@@ -65756,10 +65823,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2549</x:v>
@@ -65767,12 +65834,23 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="B98" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:3">
+      <x:c r="A99" s="1" t="s">
         <x:v>2699</x:v>
       </x:c>
-      <x:c r="B98" s="1">
+      <x:c r="B99" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C98" s="1" t="s">
+      <x:c r="C99" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -58221,7 +58221,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61918,7 +61918,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64924,7 +64924,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -58221,7 +58221,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61918,7 +61918,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64924,7 +64924,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35800,10 +35800,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35815,7 +35815,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35826,10 +35826,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35841,7 +35841,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35826,10 +35826,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35841,7 +35841,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35852,10 +35852,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35867,7 +35867,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35826,10 +35826,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35841,7 +35841,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35852,10 +35852,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35867,7 +35867,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -58273,7 +58273,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -59848,7 +59848,7 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -61970,7 +61970,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -63378,7 +63378,7 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -64976,7 +64976,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>
@@ -65449,7 +65449,7 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35826,10 +35826,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35841,7 +35841,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35852,10 +35852,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35867,7 +35867,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -58273,7 +58273,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -61970,7 +61970,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -64976,7 +64976,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8240,8 +8240,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K106" totalsRowShown="0">
-  <x:autoFilter ref="A1:K106"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K107" totalsRowShown="0">
+  <x:autoFilter ref="A1:K107"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -35826,10 +35826,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
         <x:v>636</x:v>
@@ -35841,7 +35841,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H206" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:8">
@@ -35852,10 +35852,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D207" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E207" s="1" t="s">
         <x:v>636</x:v>
@@ -35867,7 +35867,7 @@
         <x:v>2078</x:v>
       </x:c>
       <x:c r="H207" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:8">
@@ -57705,7 +57705,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K106"/>
+  <x:dimension ref="A1:K107"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58273,7 +58273,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -59054,10 +59054,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2127</x:v>
@@ -59078,7 +59078,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -59089,10 +59089,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2127</x:v>
@@ -59113,7 +59113,7 @@
         <x:v>2579</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2549</x:v>
@@ -59848,7 +59848,7 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -61014,10 +61014,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2686</x:v>
@@ -61038,7 +61038,7 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>119644</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2565</x:v>
@@ -61049,10 +61049,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2686</x:v>
@@ -61073,7 +61073,7 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2565</x:v>
@@ -61248,21 +61248,21 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>110148</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
         <x:v>2482</x:v>
@@ -61283,7 +61283,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2549</x:v>
@@ -61294,31 +61294,31 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2549</x:v>
@@ -61329,31 +61329,31 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2549</x:v>
@@ -61364,31 +61364,31 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2549</x:v>
@@ -61405,10 +61405,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
         <x:v>2546</x:v>
@@ -61420,15 +61420,50 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K106" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:11">
+      <x:c r="A107" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B107" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C107" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D107" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E107" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F107" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G107" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H107" s="1" t="s">
+        <x:v>2670</x:v>
+      </x:c>
+      <x:c r="I107" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J107" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K107" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61970,7 +62005,7 @@
         <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -63378,7 +63413,7 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -64626,7 +64661,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>110148</x:v>
+        <x:v>161023</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2549</x:v>
@@ -64976,7 +65011,7 @@
         <x:v>2585</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>
@@ -65449,7 +65484,7 @@
         <x:v>2641</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>
@@ -65856,7 +65891,7 @@
         <x:v>1782</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>173232</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2549</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7677,12 +7677,15 @@
     <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
+    <x:t>REP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
     <x:t>S4IN00196</x:t>
   </x:si>
   <x:si>
-    <x:t>REP</x:t>
-  </x:si>
-  <x:si>
     <x:t>Senate</x:t>
   </x:si>
   <x:si>
@@ -7777,9 +7780,6 @@
   </x:si>
   <x:si>
     <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
   </x:si>
   <x:si>
     <x:t>C00915181</x:t>
@@ -8240,8 +8240,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K107" totalsRowShown="0">
-  <x:autoFilter ref="A1:K107"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K108" totalsRowShown="0">
+  <x:autoFilter ref="A1:K108"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8260,8 +8260,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J104" totalsRowShown="0">
-  <x:autoFilter ref="A1:J104"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J105" totalsRowShown="0">
+  <x:autoFilter ref="A1:J105"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8279,8 +8279,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C99" totalsRowShown="0">
-  <x:autoFilter ref="A1:C99"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C100" totalsRowShown="0">
+  <x:autoFilter ref="A1:C100"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57705,7 +57705,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K107"/>
+  <x:dimension ref="A1:K108"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -57800,31 +57800,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>1931</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>1934</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I3" s="1">
-        <x:v>3009467</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K3" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -57835,25 +57835,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>2554</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>1934</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>2547</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="s">
-        <x:v>2557</x:v>
-      </x:c>
       <x:c r="I4" s="1">
-        <x:v>106708</x:v>
+        <x:v>3009467</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2549</x:v>
@@ -57864,139 +57864,139 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>557012</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K5" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K6" s="1">
-        <x:v>2022</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>2078023</x:v>
+        <x:v>248811</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K7" s="1">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K8" s="1">
         <x:v>2024</x:v>
@@ -58004,45 +58004,45 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>1977</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>83860</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K9" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>1977</x:v>
@@ -58060,30 +58060,30 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K10" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>1977</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>2546</x:v>
@@ -58092,16 +58092,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>2024</x:v>
@@ -58109,16 +58109,16 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1988</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2546</x:v>
@@ -58127,16 +58127,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K12" s="1">
         <x:v>2024</x:v>
@@ -58144,31 +58144,31 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2549</x:v>
@@ -58179,31 +58179,31 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2549</x:v>
@@ -58214,19 +58214,19 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>2581</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>2582</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>2583</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2547</x:v>
@@ -58235,10 +58235,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2549</x:v>
@@ -58249,171 +58249,171 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>2585</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2704261</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K16" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2018</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>211281</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K17" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I18" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K18" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K19" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2044</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2549</x:v>
@@ -58424,31 +58424,31 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2549</x:v>
@@ -58459,34 +58459,34 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K22" s="1">
         <x:v>2024</x:v>
@@ -58494,16 +58494,16 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2546</x:v>
@@ -58512,16 +58512,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K23" s="1">
         <x:v>2024</x:v>
@@ -58529,16 +58529,16 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2546</x:v>
@@ -58550,10 +58550,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -58564,31 +58564,31 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -58599,31 +58599,31 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -58634,31 +58634,31 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
@@ -58669,31 +58669,31 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
@@ -58704,37 +58704,37 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K29" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -58745,98 +58745,98 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K30" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K31" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K32" s="1">
         <x:v>2026</x:v>
@@ -58844,66 +58844,66 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K33" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -58914,37 +58914,37 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K35" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -58955,13 +58955,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
         <x:v>2547</x:v>
@@ -58970,45 +58970,45 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K36" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -59025,10 +59025,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -59037,13 +59037,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -59054,16 +59054,16 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2546</x:v>
@@ -59072,13 +59072,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -59110,7 +59110,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>120103</x:v>
@@ -59124,16 +59124,16 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2546</x:v>
@@ -59142,13 +59142,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -59159,37 +59159,37 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K42" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -59206,7 +59206,7 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2547</x:v>
@@ -59218,42 +59218,42 @@
         <x:v>2591</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K43" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -59264,31 +59264,31 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -59305,25 +59305,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -59334,31 +59334,31 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -59369,31 +59369,31 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -59404,31 +59404,31 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -59439,37 +59439,37 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K50" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -59480,31 +59480,31 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K51" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
@@ -59515,10 +59515,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>2546</x:v>
@@ -59527,13 +59527,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -59544,19 +59544,19 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2547</x:v>
@@ -59565,10 +59565,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -59579,66 +59579,66 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K54" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -59649,66 +59649,66 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K56" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -59719,31 +59719,31 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -59754,31 +59754,31 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -59789,31 +59789,31 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -59824,16 +59824,16 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2546</x:v>
@@ -59842,19 +59842,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>1705701</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -59865,10 +59865,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2546</x:v>
@@ -59877,48 +59877,48 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>215063</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -59929,37 +59929,37 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K64" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -59970,25 +59970,25 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2549</x:v>
@@ -59999,10 +59999,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2648</x:v>
@@ -60011,19 +60011,19 @@
         <x:v>2649</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>425</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>10049014</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
@@ -60040,31 +60040,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -60075,31 +60075,31 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -60116,7 +60116,7 @@
         <x:v>2653</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2547</x:v>
@@ -60128,13 +60128,13 @@
         <x:v>2611</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K69" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -60145,25 +60145,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
@@ -60174,66 +60174,66 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K71" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2549</x:v>
@@ -60244,66 +60244,66 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2549</x:v>
@@ -60314,31 +60314,31 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -60349,31 +60349,31 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2549</x:v>
@@ -60390,60 +60390,60 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2549</x:v>
@@ -60454,34 +60454,34 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K79" s="1">
         <x:v>2026</x:v>
@@ -60489,16 +60489,16 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2546</x:v>
@@ -60507,33 +60507,33 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2546</x:v>
@@ -60542,33 +60542,33 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2546</x:v>
@@ -60577,51 +60577,51 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K82" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K83" s="1">
         <x:v>2024</x:v>
@@ -60629,34 +60629,34 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K84" s="1">
         <x:v>2024</x:v>
@@ -60664,66 +60664,66 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2379</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2549</x:v>
@@ -60734,51 +60734,51 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2420</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2546</x:v>
@@ -60787,19 +60787,19 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -60810,60 +60810,60 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2420</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K89" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2549</x:v>
@@ -60874,34 +60874,34 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K91" s="1">
         <x:v>2024</x:v>
@@ -60909,34 +60909,34 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
+        <x:v>2681</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="s">
+        <x:v>2682</x:v>
+      </x:c>
+      <x:c r="E92" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F92" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="G92" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H92" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="I92" s="1">
+        <x:v>1531015</x:v>
+      </x:c>
+      <x:c r="J92" s="1" t="s">
         <x:v>2566</x:v>
-      </x:c>
-      <x:c r="B92" s="1" t="s">
-        <x:v>2567</x:v>
-      </x:c>
-      <x:c r="C92" s="1" t="s">
-        <x:v>2453</x:v>
-      </x:c>
-      <x:c r="D92" s="1" t="s">
-        <x:v>1312</x:v>
-      </x:c>
-      <x:c r="E92" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F92" s="1" t="s">
-        <x:v>2547</x:v>
-      </x:c>
-      <x:c r="G92" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H92" s="1" t="s">
-        <x:v>2683</x:v>
-      </x:c>
-      <x:c r="I92" s="1">
-        <x:v>2791716</x:v>
-      </x:c>
-      <x:c r="J92" s="1" t="s">
-        <x:v>2549</x:v>
       </x:c>
       <x:c r="K92" s="1">
         <x:v>2024</x:v>
@@ -60944,31 +60944,31 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2549</x:v>
@@ -60979,69 +60979,69 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>9866096</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="K95" s="1">
         <x:v>2026</x:v>
@@ -61049,10 +61049,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2686</x:v>
@@ -61064,19 +61064,19 @@
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>119644</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K96" s="1">
         <x:v>2026</x:v>
@@ -61090,45 +61090,45 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>106947</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="K97" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2546</x:v>
@@ -61137,13 +61137,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
@@ -61154,16 +61154,16 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2546</x:v>
@@ -61172,13 +61172,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2549</x:v>
@@ -61189,31 +61189,31 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2549</x:v>
@@ -61224,37 +61224,37 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>50875</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
@@ -61283,21 +61283,21 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>110148</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K102" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
         <x:v>2482</x:v>
@@ -61318,7 +61318,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2549</x:v>
@@ -61329,31 +61329,31 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2549</x:v>
@@ -61364,31 +61364,31 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2549</x:v>
@@ -61399,31 +61399,31 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2549</x:v>
@@ -61440,10 +61440,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
         <x:v>2546</x:v>
@@ -61455,15 +61455,50 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
       <x:c r="K107" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:11">
+      <x:c r="A108" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B108" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C108" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D108" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E108" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F108" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G108" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H108" s="1" t="s">
+        <x:v>2670</x:v>
+      </x:c>
+      <x:c r="I108" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J108" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="K108" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61483,7 +61518,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J104"/>
+  <x:dimension ref="A1:J105"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61571,25 +61606,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>1931</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>1934</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I3" s="1">
-        <x:v>3009467</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
         <x:v>2549</x:v>
@@ -61603,25 +61638,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>2554</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>1934</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>2547</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="s">
-        <x:v>2557</x:v>
-      </x:c>
       <x:c r="I4" s="1">
-        <x:v>106708</x:v>
+        <x:v>3009467</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
         <x:v>2549</x:v>
@@ -61629,31 +61664,31 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>557012</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2549</x:v>
@@ -61661,127 +61696,127 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>2078023</x:v>
+        <x:v>248811</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>1977</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>83860</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2549</x:v>
@@ -61789,10 +61824,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>1977</x:v>
@@ -61810,10 +61845,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2549</x:v>
@@ -61821,16 +61856,16 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>1977</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>2546</x:v>
@@ -61839,30 +61874,30 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1988</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2546</x:v>
@@ -61871,45 +61906,45 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2549</x:v>
@@ -61917,31 +61952,31 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2549</x:v>
@@ -61949,19 +61984,19 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>2581</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>2582</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>2583</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2547</x:v>
@@ -61970,10 +62005,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2549</x:v>
@@ -61981,31 +62016,31 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>2585</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>2704261</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2549</x:v>
@@ -62013,31 +62048,31 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2018</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>211281</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2549</x:v>
@@ -62045,31 +62080,31 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>2554</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>2555</x:v>
-      </x:c>
       <x:c r="I18" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2549</x:v>
@@ -62077,31 +62112,31 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2035</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2549</x:v>
@@ -62109,31 +62144,31 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2044</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2549</x:v>
@@ -62141,31 +62176,31 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2549</x:v>
@@ -62173,48 +62208,48 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2546</x:v>
@@ -62223,30 +62258,30 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2546</x:v>
@@ -62258,10 +62293,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2549</x:v>
@@ -62269,31 +62304,31 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2549</x:v>
@@ -62301,31 +62336,31 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2071</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2549</x:v>
@@ -62333,31 +62368,31 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2078</x:v>
+        <x:v>2071</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2549</x:v>
@@ -62365,31 +62400,31 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2090</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2549</x:v>
@@ -62397,31 +62432,31 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2549</x:v>
@@ -62435,25 +62470,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2549</x:v>
@@ -62461,95 +62496,95 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2549</x:v>
@@ -62557,31 +62592,31 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2111</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2549</x:v>
@@ -62589,31 +62624,31 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2549</x:v>
@@ -62627,13 +62662,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
         <x:v>2547</x:v>
@@ -62642,10 +62677,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2549</x:v>
@@ -62653,31 +62688,31 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2549</x:v>
@@ -62691,10 +62726,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2121</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2546</x:v>
@@ -62703,13 +62738,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2549</x:v>
@@ -62717,16 +62752,16 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2121</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2546</x:v>
@@ -62735,13 +62770,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2549</x:v>
@@ -62770,7 +62805,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>120103</x:v>
@@ -62781,16 +62816,16 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2546</x:v>
@@ -62799,13 +62834,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2549</x:v>
@@ -62813,31 +62848,31 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2163</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2549</x:v>
@@ -62845,31 +62880,31 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2171</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2549</x:v>
@@ -62877,31 +62912,31 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2171</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2549</x:v>
@@ -62915,25 +62950,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2185</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2549</x:v>
@@ -62941,31 +62976,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2185</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2549</x:v>
@@ -62973,31 +63008,31 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2549</x:v>
@@ -63005,31 +63040,31 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2200</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2549</x:v>
@@ -63037,31 +63072,31 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2549</x:v>
@@ -63075,25 +63110,25 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2211</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2549</x:v>
@@ -63107,10 +63142,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2212</x:v>
+        <x:v>2211</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2546</x:v>
@@ -63119,13 +63154,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2549</x:v>
@@ -63133,19 +63168,19 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2212</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2547</x:v>
@@ -63154,10 +63189,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2549</x:v>
@@ -63165,31 +63200,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2549</x:v>
@@ -63197,31 +63232,31 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2549</x:v>
@@ -63229,31 +63264,31 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2549</x:v>
@@ -63261,31 +63296,31 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2549</x:v>
@@ -63293,31 +63328,31 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2287</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2549</x:v>
@@ -63325,31 +63360,31 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2292</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2549</x:v>
@@ -63357,31 +63392,31 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2297</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2549</x:v>
@@ -63389,16 +63424,16 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2546</x:v>
@@ -63407,13 +63442,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>1705701</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2549</x:v>
@@ -63427,10 +63462,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2546</x:v>
@@ -63439,13 +63474,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>215063</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2549</x:v>
@@ -63453,31 +63488,31 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2549</x:v>
@@ -63485,31 +63520,31 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2549</x:v>
@@ -63517,31 +63552,31 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>10049014</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2549</x:v>
@@ -63561,16 +63596,16 @@
         <x:v>2649</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>425</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I65" s="1">
         <x:v>350000</x:v>
@@ -63587,25 +63622,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>726377</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2549</x:v>
@@ -63619,25 +63654,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2549</x:v>
@@ -63651,25 +63686,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2315</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2549</x:v>
@@ -63677,31 +63712,31 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2315</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2549</x:v>
@@ -63709,31 +63744,31 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2549</x:v>
@@ -63741,31 +63776,31 @@
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2549</x:v>
@@ -63773,31 +63808,31 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2338</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2549</x:v>
@@ -63805,31 +63840,31 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2549</x:v>
@@ -63837,31 +63872,31 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2549</x:v>
@@ -63875,25 +63910,25 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2549</x:v>
@@ -63901,31 +63936,31 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2549</x:v>
@@ -63933,48 +63968,48 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>2546</x:v>
@@ -63983,30 +64018,30 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
         <x:v>2546</x:v>
@@ -64015,30 +64050,30 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2546</x:v>
@@ -64047,109 +64082,109 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2359</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2379</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2549</x:v>
@@ -64157,31 +64192,31 @@
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2379</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2549</x:v>
@@ -64189,31 +64224,31 @@
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2402</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2549</x:v>
@@ -64221,16 +64256,16 @@
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2420</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2546</x:v>
@@ -64239,16 +64274,16 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:10">
@@ -64259,57 +64294,57 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2420</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2549</x:v>
@@ -64317,95 +64352,95 @@
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="B90" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="C90" s="1" t="s">
+        <x:v>2681</x:v>
+      </x:c>
+      <x:c r="D90" s="1" t="s">
+        <x:v>2682</x:v>
+      </x:c>
+      <x:c r="E90" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F90" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="G90" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H90" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="I90" s="1">
+        <x:v>1531015</x:v>
+      </x:c>
+      <x:c r="J90" s="1" t="s">
         <x:v>2566</x:v>
-      </x:c>
-      <x:c r="B90" s="1" t="s">
-        <x:v>2567</x:v>
-      </x:c>
-      <x:c r="C90" s="1" t="s">
-        <x:v>2453</x:v>
-      </x:c>
-      <x:c r="D90" s="1" t="s">
-        <x:v>1312</x:v>
-      </x:c>
-      <x:c r="E90" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
-      <x:c r="F90" s="1" t="s">
-        <x:v>2547</x:v>
-      </x:c>
-      <x:c r="G90" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H90" s="1" t="s">
-        <x:v>2683</x:v>
-      </x:c>
-      <x:c r="I90" s="1">
-        <x:v>2791716</x:v>
-      </x:c>
-      <x:c r="J90" s="1" t="s">
-        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2549</x:v>
@@ -64413,31 +64448,31 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2549</x:v>
@@ -64445,42 +64480,42 @@
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>9866096</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2686</x:v>
@@ -64492,19 +64527,19 @@
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>119644</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
@@ -64515,42 +64550,42 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>106947</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2546</x:v>
@@ -64559,13 +64594,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2549</x:v>
@@ -64573,16 +64608,16 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2546</x:v>
@@ -64591,13 +64626,13 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2549</x:v>
@@ -64605,31 +64640,31 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2549</x:v>
@@ -64637,31 +64672,31 @@
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>161023</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2549</x:v>
@@ -64669,10 +64704,10 @@
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2542</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2543</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2482</x:v>
@@ -64693,7 +64728,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>63084</x:v>
+        <x:v>161023</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2549</x:v>
@@ -64701,31 +64736,31 @@
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2549</x:v>
@@ -64733,31 +64768,31 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2549</x:v>
@@ -64765,31 +64800,31 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2542</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2543</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2549</x:v>
@@ -64803,10 +64838,10 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1833</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2546</x:v>
@@ -64818,12 +64853,44 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="I104" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J104" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:10">
+      <x:c r="A105" s="1" t="s">
+        <x:v>2542</x:v>
+      </x:c>
+      <x:c r="B105" s="1" t="s">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C105" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="D105" s="1" t="s">
+        <x:v>2699</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="F105" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H105" s="1" t="s">
         <x:v>2670</x:v>
       </x:c>
-      <x:c r="I104" s="1">
+      <x:c r="I105" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J104" s="1" t="s">
+      <x:c r="J105" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>
@@ -64843,7 +64910,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C99"/>
+  <x:dimension ref="A1:C100"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -64876,10 +64943,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>1934</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>3009467</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>2549</x:v>
@@ -64887,10 +64954,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>1934</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>106708</x:v>
+        <x:v>3009467</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>2549</x:v>
@@ -64898,10 +64965,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>557012</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>2549</x:v>
@@ -64909,43 +64976,43 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2078023</x:v>
+        <x:v>248811</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>666234</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>2549</x:v>
@@ -64953,32 +65020,32 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1406523</x:v>
+        <x:v>666234</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>2549</x:v>
@@ -64986,10 +65053,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2549</x:v>
@@ -64997,10 +65064,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2549</x:v>
@@ -65008,10 +65075,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2704261</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2549</x:v>
@@ -65019,10 +65086,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>211281</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2549</x:v>
@@ -65030,10 +65097,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2549</x:v>
@@ -65041,10 +65108,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2549</x:v>
@@ -65052,10 +65119,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>1700</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2549</x:v>
@@ -65063,10 +65130,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2549</x:v>
@@ -65074,32 +65141,32 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2549</x:v>
@@ -65107,10 +65174,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2549</x:v>
@@ -65118,10 +65185,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>1791</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2549</x:v>
@@ -65129,10 +65196,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2549</x:v>
@@ -65140,10 +65207,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2549</x:v>
@@ -65151,10 +65218,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2549</x:v>
@@ -65162,10 +65229,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>1321</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>2549</x:v>
@@ -65173,32 +65240,32 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2549</x:v>
@@ -65206,10 +65273,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2549</x:v>
@@ -65217,10 +65284,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2549</x:v>
@@ -65228,10 +65295,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2549</x:v>
@@ -65239,10 +65306,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2549</x:v>
@@ -65250,10 +65317,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2549</x:v>
@@ -65261,10 +65328,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2549</x:v>
@@ -65272,10 +65339,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2549</x:v>
@@ -65283,10 +65350,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2549</x:v>
@@ -65294,10 +65361,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>1391</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2549</x:v>
@@ -65305,10 +65372,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2549</x:v>
@@ -65316,10 +65383,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2549</x:v>
@@ -65327,10 +65394,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2549</x:v>
@@ -65338,10 +65405,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2549</x:v>
@@ -65349,10 +65416,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2549</x:v>
@@ -65360,10 +65427,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>1532</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2549</x:v>
@@ -65371,10 +65438,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1532</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2549</x:v>
@@ -65382,10 +65449,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>1520</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2549</x:v>
@@ -65393,10 +65460,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>1909</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2549</x:v>
@@ -65404,10 +65471,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2549</x:v>
@@ -65415,10 +65482,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2549</x:v>
@@ -65426,10 +65493,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2549</x:v>
@@ -65437,10 +65504,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2549</x:v>
@@ -65448,10 +65515,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2549</x:v>
@@ -65459,10 +65526,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>1284</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2549</x:v>
@@ -65470,10 +65537,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2549</x:v>
@@ -65481,10 +65548,10 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>1705701</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2549</x:v>
@@ -65492,10 +65559,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>1296</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>215063</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2549</x:v>
@@ -65503,10 +65570,10 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2549</x:v>
@@ -65514,10 +65581,10 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2549</x:v>
@@ -65525,10 +65592,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>10399014</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2549</x:v>
@@ -65536,10 +65603,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>726377</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2549</x:v>
@@ -65547,10 +65614,10 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2549</x:v>
@@ -65558,10 +65625,10 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2549</x:v>
@@ -65569,10 +65636,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2549</x:v>
@@ -65580,10 +65647,10 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2549</x:v>
@@ -65591,10 +65658,10 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>1891</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2549</x:v>
@@ -65602,10 +65669,10 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2549</x:v>
@@ -65613,10 +65680,10 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2549</x:v>
@@ -65624,10 +65691,10 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2549</x:v>
@@ -65635,10 +65702,10 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2549</x:v>
@@ -65646,10 +65713,10 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2549</x:v>
@@ -65657,76 +65724,76 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>1457</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2549</x:v>
@@ -65734,10 +65801,10 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>2549</x:v>
@@ -65745,10 +65812,10 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>1424</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>2549</x:v>
@@ -65756,32 +65823,32 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2549</x:v>
@@ -65789,32 +65856,32 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>1312</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>1649</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2549</x:v>
@@ -65822,10 +65889,10 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2549</x:v>
@@ -65833,32 +65900,32 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2549</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>106947</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2566</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>1664</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2549</x:v>
@@ -65866,10 +65933,10 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>2549</x:v>
@@ -65877,10 +65944,10 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2549</x:v>
@@ -65888,10 +65955,10 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>1782</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>224107</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2549</x:v>
@@ -65899,10 +65966,10 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>10000</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2549</x:v>
@@ -65910,10 +65977,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2549</x:v>
@@ -65921,10 +65988,10 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>1833</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="B98" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2549</x:v>
@@ -65932,12 +65999,23 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="1" t="s">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="B99" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:3">
+      <x:c r="A100" s="1" t="s">
         <x:v>2699</x:v>
       </x:c>
-      <x:c r="B99" s="1">
+      <x:c r="B100" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C99" s="1" t="s">
+      <x:c r="C100" s="1" t="s">
         <x:v>2549</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7869,6 +7869,15 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
     <x:t>S4AZ00139</x:t>
   </x:si>
   <x:si>
@@ -7881,9 +7890,6 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>H4TX12065</x:t>
   </x:si>
   <x:si>
@@ -7930,6 +7936,12 @@
   </x:si>
   <x:si>
     <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
     <x:t>S6IL00482</x:t>
@@ -8252,8 +8264,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K108" totalsRowShown="0">
-  <x:autoFilter ref="A1:K108"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K111" totalsRowShown="0">
+  <x:autoFilter ref="A1:K111"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8272,8 +8284,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J105" totalsRowShown="0">
-  <x:autoFilter ref="A1:J105"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J108" totalsRowShown="0">
+  <x:autoFilter ref="A1:J108"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8291,8 +8303,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C100" totalsRowShown="0">
-  <x:autoFilter ref="A1:C100"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C102" totalsRowShown="0">
+  <x:autoFilter ref="A1:C102"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57832,7 +57844,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K108"/>
+  <x:dimension ref="A1:K111"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58435,7 +58447,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>2704261</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -58971,10 +58983,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2613</x:v>
@@ -58995,7 +59007,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2553</x:v>
@@ -59006,51 +59018,51 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>10039655</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K34" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -59059,68 +59071,68 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>1012931</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K35" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>183312</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K36" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2556</x:v>
@@ -59129,13 +59141,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>725091</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -59146,66 +59158,66 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>150853</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K38" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>511329</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
@@ -59222,10 +59234,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2550</x:v>
@@ -59234,13 +59246,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>120103</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
@@ -59251,16 +59263,16 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2550</x:v>
@@ -59269,13 +59281,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -59292,10 +59304,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -59304,13 +59316,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -59321,66 +59333,66 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>836118</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K43" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>106888</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -59391,37 +59403,37 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>1836196</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K45" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -59432,10 +59444,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>2556</x:v>
@@ -59444,13 +59456,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>107353</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
@@ -59461,31 +59473,31 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>1308901</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
@@ -59496,16 +59508,16 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>2556</x:v>
@@ -59514,13 +59526,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>124736</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -59531,31 +59543,31 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>961273</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -59566,31 +59578,31 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>3025544</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -59607,60 +59619,60 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
+        <x:v>2631</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
         <x:v>2632</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>1535</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
         <x:v>2633</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>285008</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K51" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>68985</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -59677,60 +59689,60 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
         <x:v>2635</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>108546</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K53" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2636</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>1924213</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
@@ -59747,66 +59759,66 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>30183</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K55" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>350000</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K56" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
@@ -59817,10 +59829,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2556</x:v>
@@ -59829,19 +59841,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>582915</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K57" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -59852,45 +59864,45 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>2641</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>2642</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>2643</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>112913</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K58" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2556</x:v>
@@ -59899,33 +59911,33 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>34970</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K59" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2556</x:v>
@@ -59934,13 +59946,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>126626</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -59951,16 +59963,16 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2550</x:v>
@@ -59969,13 +59981,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>46160</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -59986,66 +59998,66 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>1752863</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>215063</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -60056,31 +60068,31 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>504020</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -60091,31 +60103,31 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>2648</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>2649</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F65" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H65" s="1" t="s">
         <x:v>2650</x:v>
       </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>2651</x:v>
-      </x:c>
-      <x:c r="E65" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F65" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G65" s="1" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H65" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I65" s="1">
-        <x:v>250000</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -60126,37 +60138,37 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>350000</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -60176,30 +60188,30 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2654</x:v>
@@ -60211,30 +60223,30 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>726377</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2656</x:v>
@@ -60246,16 +60258,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>161896</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -60281,22 +60293,22 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>506553</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K70" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -60307,25 +60319,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>40134929</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -60336,31 +60348,31 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>850000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
@@ -60389,48 +60401,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>282526</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>116161</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
@@ -60441,45 +60453,45 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>999284</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K75" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2664</x:v>
@@ -60488,54 +60500,54 @@
         <x:v>2665</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>209387</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K76" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>257695</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
@@ -60546,16 +60558,16 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>2556</x:v>
@@ -60564,156 +60576,156 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>558813</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1750000</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K79" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>817066</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K82" s="1">
         <x:v>2026</x:v>
@@ -60721,16 +60733,16 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2550</x:v>
@@ -60739,19 +60751,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>88256</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K83" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -60765,25 +60777,25 @@
         <x:v>2679</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>10041119</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K84" s="1">
         <x:v>2024</x:v>
@@ -60791,16 +60803,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2550</x:v>
@@ -60809,103 +60821,103 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1491280</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>350000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2550</x:v>
@@ -60914,13 +60926,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2553</x:v>
@@ -60931,34 +60943,34 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K89" s="1">
         <x:v>2026</x:v>
@@ -60966,19 +60978,19 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
         <x:v>2559</x:v>
@@ -60990,13 +61002,13 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>10046680</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -61007,10 +61019,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2550</x:v>
@@ -61019,13 +61031,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>817169</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2553</x:v>
@@ -61036,66 +61048,66 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>1531015</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2570</x:v>
       </x:c>
       <x:c r="K92" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2553</x:v>
@@ -61112,25 +61124,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2553</x:v>
@@ -61147,31 +61159,31 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K95" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -61182,74 +61194,74 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
+        <x:v>1315</x:v>
+      </x:c>
+      <x:c r="E96" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F96" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G96" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H96" s="1" t="s">
         <x:v>2691</x:v>
       </x:c>
-      <x:c r="E96" s="1" t="s">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="F96" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G96" s="1" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H96" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I96" s="1">
-        <x:v>9866096</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K96" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>119644</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K97" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2692</x:v>
@@ -61258,25 +61270,25 @@
         <x:v>2693</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>106947</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K98" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -61287,31 +61299,31 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>902176</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K99" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -61331,51 +61343,51 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>1010142</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K100" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2553</x:v>
@@ -61386,16 +61398,16 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2550</x:v>
@@ -61407,16 +61419,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>50875</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K102" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -61427,10 +61439,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2550</x:v>
@@ -61439,13 +61451,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>110148</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -61456,31 +61468,31 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>63084</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -61491,66 +61503,66 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>10000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K105" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>1306863</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -61561,16 +61573,16 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
         <x:v>2550</x:v>
@@ -61579,13 +61591,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>889852</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
@@ -61596,36 +61608,141 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="D108" s="1" t="s">
+        <x:v>2701</x:v>
+      </x:c>
+      <x:c r="E108" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F108" s="1" t="s">
         <x:v>2702</x:v>
       </x:c>
-      <x:c r="D108" s="1" t="s">
+      <x:c r="G108" s="1" t="s">
         <x:v>2703</x:v>
       </x:c>
-      <x:c r="E108" s="1" t="s">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="F108" s="1" t="s">
-        <x:v>2551</x:v>
-      </x:c>
-      <x:c r="G108" s="1" t="s">
-        <x:v>175</x:v>
-      </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>1012792</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K108" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:11">
+      <x:c r="A109" s="1" t="s">
+        <x:v>2571</x:v>
+      </x:c>
+      <x:c r="B109" s="1" t="s">
+        <x:v>2572</x:v>
+      </x:c>
+      <x:c r="C109" s="1" t="s">
+        <x:v>2704</x:v>
+      </x:c>
+      <x:c r="D109" s="1" t="s">
+        <x:v>2705</x:v>
+      </x:c>
+      <x:c r="E109" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F109" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G109" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H109" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="I109" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J109" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K109" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:11">
+      <x:c r="A110" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B110" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C110" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="D110" s="1" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="E110" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F110" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G110" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H110" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="I110" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J110" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K110" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:11">
+      <x:c r="A111" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B111" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C111" s="1" t="s">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="D111" s="1" t="s">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="E111" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F111" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G111" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H111" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="I111" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J111" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K111" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61645,7 +61762,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J105"/>
+  <x:dimension ref="A1:J108"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61951,10 +62068,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>1981</x:v>
@@ -61975,7 +62092,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2553</x:v>
@@ -61983,10 +62100,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>1981</x:v>
@@ -62007,7 +62124,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2553</x:v>
@@ -62199,7 +62316,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>2704261</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -62719,31 +62836,31 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>10039655</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2553</x:v>
@@ -62751,16 +62868,16 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -62769,13 +62886,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>1012931</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
@@ -62783,31 +62900,31 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>183312</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
@@ -62815,16 +62932,16 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2556</x:v>
@@ -62833,13 +62950,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>725091</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -62847,31 +62964,31 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>150853</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
@@ -62879,31 +62996,31 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>511329</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
@@ -62917,10 +63034,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2550</x:v>
@@ -62929,13 +63046,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>120103</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
@@ -62943,16 +63060,16 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2550</x:v>
@@ -62961,13 +63078,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -62981,10 +63098,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -62993,13 +63110,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -63007,31 +63124,31 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>943006</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
@@ -63039,16 +63156,16 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2550</x:v>
@@ -63057,13 +63174,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>1836196</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -63077,10 +63194,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2556</x:v>
@@ -63089,13 +63206,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>107353</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
@@ -63103,31 +63220,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>1308901</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
@@ -63135,16 +63252,16 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>2556</x:v>
@@ -63153,13 +63270,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>124736</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
@@ -63167,31 +63284,31 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>961273</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -63199,31 +63316,31 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>3025544</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -63237,25 +63354,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
+        <x:v>2631</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
         <x:v>2632</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>1535</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
         <x:v>2633</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>285008</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -63263,31 +63380,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>68985</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -63301,25 +63418,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
         <x:v>2635</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>108546</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -63327,31 +63444,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
         <x:v>2636</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>1924213</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
@@ -63365,25 +63482,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>30183</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
@@ -63391,31 +63508,31 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>350000</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
@@ -63429,10 +63546,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2556</x:v>
@@ -63441,13 +63558,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>582915</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
@@ -63461,25 +63578,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
+        <x:v>2641</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
         <x:v>2642</x:v>
-      </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>2643</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>112913</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
@@ -63487,16 +63604,16 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2556</x:v>
@@ -63505,13 +63622,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>34970</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
@@ -63519,16 +63636,16 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2556</x:v>
@@ -63537,13 +63654,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>126626</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
@@ -63551,16 +63668,16 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2550</x:v>
@@ -63569,13 +63686,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>46160</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -63583,31 +63700,31 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>1752863</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -63615,31 +63732,31 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>215063</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
@@ -63647,31 +63764,31 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>504020</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -63679,31 +63796,31 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
+        <x:v>2648</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>2649</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H64" s="1" t="s">
         <x:v>2650</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
-        <x:v>2651</x:v>
-      </x:c>
-      <x:c r="E64" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F64" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G64" s="1" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H64" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I64" s="1">
-        <x:v>250000</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -63711,31 +63828,31 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>350000</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -63758,16 +63875,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>10049014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
@@ -63775,10 +63892,10 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2654</x:v>
@@ -63790,16 +63907,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>726377</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
@@ -63822,16 +63939,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>668449</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -63839,16 +63956,16 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2556</x:v>
@@ -63857,13 +63974,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>40134929</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -63871,10 +63988,10 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2658</x:v>
@@ -63886,16 +64003,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>850000</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
@@ -63921,13 +64038,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>282526</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -63935,31 +64052,31 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>116161</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
@@ -63967,31 +64084,31 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>999284</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
@@ -63999,10 +64116,10 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2664</x:v>
@@ -64011,19 +64128,19 @@
         <x:v>2665</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>209387</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
@@ -64031,31 +64148,31 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>257695</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
@@ -64063,16 +64180,16 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2556</x:v>
@@ -64081,13 +64198,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>558813</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
@@ -64095,31 +64212,31 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>1750000</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
@@ -64127,63 +64244,63 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
@@ -64191,48 +64308,48 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>817066</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2550</x:v>
@@ -64241,16 +64358,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>88256</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:10">
@@ -64264,39 +64381,39 @@
         <x:v>2679</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>10041119</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2550</x:v>
@@ -64305,45 +64422,45 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>1491280</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>350000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2553</x:v>
@@ -64351,48 +64468,48 @@
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2550</x:v>
@@ -64401,13 +64518,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2553</x:v>
@@ -64415,51 +64532,51 @@
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2559</x:v>
@@ -64471,7 +64588,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>10046680</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2553</x:v>
@@ -64485,10 +64602,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2550</x:v>
@@ -64497,13 +64614,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>817169</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2553</x:v>
@@ -64511,31 +64628,31 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1531015</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2570</x:v>
@@ -64543,31 +64660,31 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2553</x:v>
@@ -64581,25 +64698,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2553</x:v>
@@ -64613,28 +64730,28 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:10">
@@ -64645,68 +64762,68 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
+        <x:v>1315</x:v>
+      </x:c>
+      <x:c r="E94" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F94" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G94" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H94" s="1" t="s">
         <x:v>2691</x:v>
       </x:c>
-      <x:c r="E94" s="1" t="s">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="F94" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G94" s="1" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H94" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I94" s="1">
-        <x:v>9866096</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>119644</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2692</x:v>
@@ -64715,19 +64832,19 @@
         <x:v>2693</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>106947</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
@@ -64735,42 +64852,42 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>902176</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2694</x:v>
@@ -64782,48 +64899,48 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1010142</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2553</x:v>
@@ -64831,16 +64948,16 @@
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2550</x:v>
@@ -64852,10 +64969,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>161023</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2553</x:v>
@@ -64863,16 +64980,16 @@
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2550</x:v>
@@ -64881,13 +64998,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>63084</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2553</x:v>
@@ -64895,31 +65012,31 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>10000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2553</x:v>
@@ -64927,31 +65044,31 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1306863</x:v>
+        <x:v>161023</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -64959,16 +65076,16 @@
     </x:row>
     <x:row r="104" spans="1:10">
       <x:c r="A104" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2550</x:v>
@@ -64977,13 +65094,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>889852</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -64991,33 +65108,129 @@
     </x:row>
     <x:row r="105" spans="1:10">
       <x:c r="A105" s="1" t="s">
+        <x:v>2596</x:v>
+      </x:c>
+      <x:c r="B105" s="1" t="s">
+        <x:v>2597</x:v>
+      </x:c>
+      <x:c r="C105" s="1" t="s">
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="D105" s="1" t="s">
+        <x:v>2701</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F105" s="1" t="s">
+        <x:v>2702</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
+        <x:v>2703</x:v>
+      </x:c>
+      <x:c r="H105" s="1" t="s">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="I105" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J105" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:10">
+      <x:c r="A106" s="1" t="s">
+        <x:v>2571</x:v>
+      </x:c>
+      <x:c r="B106" s="1" t="s">
+        <x:v>2572</x:v>
+      </x:c>
+      <x:c r="C106" s="1" t="s">
+        <x:v>2704</x:v>
+      </x:c>
+      <x:c r="D106" s="1" t="s">
+        <x:v>2705</x:v>
+      </x:c>
+      <x:c r="E106" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F106" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G106" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H106" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="I106" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J106" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:10">
+      <x:c r="A107" s="1" t="s">
         <x:v>2546</x:v>
       </x:c>
-      <x:c r="B105" s="1" t="s">
+      <x:c r="B107" s="1" t="s">
         <x:v>2547</x:v>
       </x:c>
-      <x:c r="C105" s="1" t="s">
-        <x:v>2702</x:v>
-      </x:c>
-      <x:c r="D105" s="1" t="s">
-        <x:v>2703</x:v>
-      </x:c>
-      <x:c r="E105" s="1" t="s">
+      <x:c r="C107" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="D107" s="1" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="E107" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="F105" s="1" t="s">
+      <x:c r="F107" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
-      <x:c r="G105" s="1" t="s">
+      <x:c r="G107" s="1" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="H105" s="1" t="s">
-        <x:v>2674</x:v>
-      </x:c>
-      <x:c r="I105" s="1">
+      <x:c r="H107" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="I107" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J107" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:10">
+      <x:c r="A108" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B108" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C108" s="1" t="s">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="D108" s="1" t="s">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="E108" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F108" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G108" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H108" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="I108" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J105" s="1" t="s">
+      <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>
@@ -65037,7 +65250,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C100"/>
+  <x:dimension ref="A1:C102"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -65216,7 +65429,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>2704261</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2553</x:v>
@@ -65392,7 +65605,7 @@
         <x:v>2614</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>300000</x:v>
+        <x:v>363285</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2553</x:v>
@@ -65400,10 +65613,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>10039655</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2553</x:v>
@@ -65411,10 +65624,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2553</x:v>
@@ -65422,10 +65635,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2553</x:v>
@@ -65436,7 +65649,7 @@
         <x:v>2622</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2553</x:v>
@@ -65444,10 +65657,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2553</x:v>
@@ -65455,10 +65668,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2553</x:v>
@@ -65466,10 +65679,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2553</x:v>
@@ -65477,10 +65690,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2553</x:v>
@@ -65488,10 +65701,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2553</x:v>
@@ -65499,10 +65712,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2553</x:v>
@@ -65510,10 +65723,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2553</x:v>
@@ -65521,10 +65734,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2553</x:v>
@@ -65532,10 +65745,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2553</x:v>
@@ -65543,10 +65756,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2553</x:v>
@@ -65554,10 +65767,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2553</x:v>
@@ -65565,10 +65778,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2553</x:v>
@@ -65576,10 +65789,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2553</x:v>
@@ -65587,10 +65800,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2553</x:v>
@@ -65598,10 +65811,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2553</x:v>
@@ -65609,10 +65822,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>30183</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2553</x:v>
@@ -65623,7 +65836,7 @@
         <x:v>2640</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>350000</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2553</x:v>
@@ -65631,10 +65844,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2553</x:v>
@@ -65642,10 +65855,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2553</x:v>
@@ -65653,10 +65866,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2553</x:v>
@@ -65664,10 +65877,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2553</x:v>
@@ -65675,10 +65888,10 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2553</x:v>
@@ -65686,10 +65899,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>1752863</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2553</x:v>
@@ -65697,10 +65910,10 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>215063</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2553</x:v>
@@ -65711,7 +65924,7 @@
         <x:v>2649</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>504020</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2553</x:v>
@@ -65719,10 +65932,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>250000</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2553</x:v>
@@ -65733,7 +65946,7 @@
         <x:v>2653</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>10399014</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2553</x:v>
@@ -65744,7 +65957,7 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>726377</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2553</x:v>
@@ -65755,7 +65968,7 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>668449</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2553</x:v>
@@ -65763,10 +65976,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>40134929</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2553</x:v>
@@ -65774,10 +65987,10 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>850000</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2553</x:v>
@@ -65785,10 +65998,10 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>282526</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2553</x:v>
@@ -65796,10 +66009,10 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>116161</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2553</x:v>
@@ -65807,10 +66020,10 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>999284</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2553</x:v>
@@ -65818,10 +66031,10 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>209387</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2553</x:v>
@@ -65829,10 +66042,10 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>257695</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2553</x:v>
@@ -65843,7 +66056,7 @@
         <x:v>2669</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>558813</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2553</x:v>
@@ -65854,7 +66067,7 @@
         <x:v>2671</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>1750000</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2553</x:v>
@@ -65865,18 +66078,18 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>20483</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2553</x:v>
@@ -65884,10 +66097,10 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>817066</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2570</x:v>
@@ -65895,10 +66108,10 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>88256</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>2553</x:v>
@@ -65906,10 +66119,10 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>10041119</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2570</x:v>
@@ -65917,10 +66130,10 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>1491280</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2553</x:v>
@@ -65928,21 +66141,21 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>350000</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>91847</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>2553</x:v>
@@ -65950,10 +66163,10 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>1987660</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2553</x:v>
@@ -65961,21 +66174,21 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>56045</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2553</x:v>
@@ -65983,32 +66196,32 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>817169</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>1531015</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>2791716</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2553</x:v>
@@ -66016,21 +66229,21 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>764206</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>2553</x:v>
@@ -66038,13 +66251,13 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>9985740</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
@@ -66052,7 +66265,7 @@
         <x:v>2693</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>106947</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2553</x:v>
@@ -66060,21 +66273,21 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>902176</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>1010142</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2553</x:v>
@@ -66082,10 +66295,10 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>1860445</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2553</x:v>
@@ -66093,10 +66306,10 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>224107</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2553</x:v>
@@ -66104,10 +66317,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>10000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2553</x:v>
@@ -66115,10 +66328,10 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="B98" s="1">
-        <x:v>1306863</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2553</x:v>
@@ -66126,10 +66339,10 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="B99" s="1">
-        <x:v>889852</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
         <x:v>2553</x:v>
@@ -66137,12 +66350,34 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="B100" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:3">
+      <x:c r="A101" s="1" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="B101" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:3">
+      <x:c r="A102" s="1" t="s">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="B102" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C100" s="1" t="s">
+      <x:c r="C102" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -8264,8 +8264,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K111" totalsRowShown="0">
-  <x:autoFilter ref="A1:K111"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K113" totalsRowShown="0">
+  <x:autoFilter ref="A1:K113"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8284,8 +8284,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J108" totalsRowShown="0">
-  <x:autoFilter ref="A1:J108"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J109" totalsRowShown="0">
+  <x:autoFilter ref="A1:J109"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8303,8 +8303,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C102" totalsRowShown="0">
-  <x:autoFilter ref="A1:C102"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C103" totalsRowShown="0">
+  <x:autoFilter ref="A1:C103"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -35954,10 +35954,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
         <x:v>639</x:v>
@@ -35969,7 +35969,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H208" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:8">
@@ -35980,10 +35980,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
         <x:v>639</x:v>
@@ -35995,7 +35995,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H209" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:8">
@@ -57844,7 +57844,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K111"/>
+  <x:dimension ref="A1:K113"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58027,150 +58027,150 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>106708</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K5" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>557012</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K6" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="1" t="s">
-        <x:v>2566</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2568</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K7" s="1">
-        <x:v>2022</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2566</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>2078023</x:v>
+        <x:v>248811</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
         <x:v>2570</x:v>
       </x:c>
       <x:c r="K8" s="1">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2576</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K9" s="1">
         <x:v>2024</x:v>
@@ -58178,45 +58178,45 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>1981</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>83860</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K10" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>1981</x:v>
@@ -58237,13 +58237,13 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K11" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -58254,10 +58254,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2550</x:v>
@@ -58266,16 +58266,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K12" s="1">
         <x:v>2024</x:v>
@@ -58289,10 +58289,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>1992</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2550</x:v>
@@ -58301,16 +58301,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K13" s="1">
         <x:v>2024</x:v>
@@ -58324,25 +58324,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2553</x:v>
@@ -58353,31 +58353,31 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2553</x:v>
@@ -58388,19 +58388,19 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2551</x:v>
@@ -58409,10 +58409,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2553</x:v>
@@ -58423,171 +58423,171 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>2761006</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K17" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2022</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>211281</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K18" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K19" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2039</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K20" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2048</x:v>
+        <x:v>2039</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>1703</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2553</x:v>
@@ -58598,16 +58598,16 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>2556</x:v>
@@ -58616,13 +58616,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2553</x:v>
@@ -58633,34 +58633,34 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K23" s="1">
         <x:v>2024</x:v>
@@ -58668,16 +58668,16 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2601</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2550</x:v>
@@ -58686,16 +58686,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K24" s="1">
         <x:v>2024</x:v>
@@ -58709,10 +58709,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2601</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2602</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2550</x:v>
@@ -58727,7 +58727,7 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2553</x:v>
@@ -58744,25 +58744,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2553</x:v>
@@ -58773,16 +58773,16 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2075</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2556</x:v>
@@ -58791,13 +58791,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2553</x:v>
@@ -58808,16 +58808,16 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2082</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2556</x:v>
@@ -58826,13 +58826,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2553</x:v>
@@ -58843,31 +58843,31 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2094</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2553</x:v>
@@ -58878,37 +58878,37 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K30" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
@@ -58919,10 +58919,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2100</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2556</x:v>
@@ -58931,86 +58931,86 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K31" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K32" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>63285</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K33" s="1">
         <x:v>2026</x:v>
@@ -59018,10 +59018,10 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2613</x:v>
@@ -59042,7 +59042,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2553</x:v>
@@ -59053,16 +59053,16 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -59074,10 +59074,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
@@ -59088,66 +59088,66 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>10039655</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K36" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -59158,16 +59158,16 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2556</x:v>
@@ -59176,19 +59176,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K38" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -59199,10 +59199,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2556</x:v>
@@ -59214,45 +59214,45 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K39" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
@@ -59269,10 +59269,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2550</x:v>
@@ -59281,13 +59281,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -59304,10 +59304,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -59316,13 +59316,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -59374,10 +59374,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2550</x:v>
@@ -59386,13 +59386,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -59403,37 +59403,37 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K45" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -59462,42 +59462,42 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K46" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
@@ -59508,31 +59508,31 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -59549,10 +59549,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2556</x:v>
@@ -59561,13 +59561,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -59578,16 +59578,16 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2556</x:v>
@@ -59596,13 +59596,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -59613,31 +59613,31 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -59648,31 +59648,31 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -59683,37 +59683,37 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K53" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
@@ -59724,31 +59724,31 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K54" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -59759,10 +59759,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2550</x:v>
@@ -59771,13 +59771,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
@@ -59788,19 +59788,19 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2551</x:v>
@@ -59809,10 +59809,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
@@ -59823,16 +59823,16 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2556</x:v>
@@ -59841,48 +59841,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K57" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
@@ -59893,31 +59893,31 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
@@ -59928,66 +59928,66 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K60" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -59998,31 +59998,31 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
@@ -60033,31 +60033,31 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -60074,25 +60074,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -60103,16 +60103,16 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2550</x:v>
@@ -60121,19 +60121,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>1752863</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K65" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -60144,10 +60144,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2550</x:v>
@@ -60156,48 +60156,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>215063</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
@@ -60208,37 +60208,37 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -60249,10 +60249,10 @@
         <x:v>2592</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2556</x:v>
@@ -60261,13 +60261,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -60302,7 +60302,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>10049014</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
@@ -60313,37 +60313,37 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2657</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>726377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K71" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -60354,10 +60354,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2556</x:v>
@@ -60366,19 +60366,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -60407,13 +60407,13 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -60424,25 +60424,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
@@ -60453,16 +60453,16 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2556</x:v>
@@ -60471,48 +60471,48 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K75" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
@@ -60523,37 +60523,37 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
@@ -60564,25 +60564,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
@@ -60593,31 +60593,31 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
@@ -60628,31 +60628,31 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2553</x:v>
@@ -60669,10 +60669,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2556</x:v>
@@ -60681,48 +60681,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2553</x:v>
@@ -60733,34 +60733,34 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K83" s="1">
         <x:v>2026</x:v>
@@ -60768,16 +60768,16 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2550</x:v>
@@ -60786,19 +60786,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K84" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -60809,10 +60809,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2550</x:v>
@@ -60821,19 +60821,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -60844,10 +60844,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2550</x:v>
@@ -60856,19 +60856,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -60879,28 +60879,28 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K87" s="1">
         <x:v>2024</x:v>
@@ -60908,34 +60908,34 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K88" s="1">
         <x:v>2024</x:v>
@@ -60943,51 +60943,51 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K89" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2556</x:v>
@@ -60996,13 +60996,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2553</x:v>
@@ -61013,51 +61013,51 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K91" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2550</x:v>
@@ -61066,19 +61066,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K92" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -61089,60 +61089,60 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>817169</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2553</x:v>
@@ -61159,31 +61159,31 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1531015</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K95" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -61194,25 +61194,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>2791716</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
@@ -61223,34 +61223,34 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>764206</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K97" s="1">
         <x:v>2024</x:v>
@@ -61258,16 +61258,16 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2556</x:v>
@@ -61276,19 +61276,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K98" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -61299,63 +61299,63 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>9866096</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K99" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K100" s="1">
         <x:v>2026</x:v>
@@ -61363,72 +61363,72 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>902176</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K102" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -61439,10 +61439,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2550</x:v>
@@ -61451,13 +61451,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1010142</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -61468,31 +61468,31 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>1860445</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -61509,10 +61509,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
         <x:v>2550</x:v>
@@ -61521,48 +61521,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>50875</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K105" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>110148</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -61573,10 +61573,10 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
         <x:v>2486</x:v>
@@ -61597,42 +61597,42 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>63084</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K107" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>10000</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
@@ -61649,25 +61649,25 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>1306863</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
         <x:v>2553</x:v>
@@ -61678,31 +61678,31 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>889852</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2553</x:v>
@@ -61713,36 +61713,106 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>1012792</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K111" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:11">
+      <x:c r="A112" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B112" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C112" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="D112" s="1" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="E112" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F112" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G112" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H112" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="I112" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J112" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K112" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:11">
+      <x:c r="A113" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B113" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C113" s="1" t="s">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="D113" s="1" t="s">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="E113" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F113" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G113" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H113" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="I113" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J113" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K113" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61762,7 +61832,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J108"/>
+  <x:dimension ref="A1:J109"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -61932,7 +62002,7 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2553</x:v>
@@ -62316,7 +62386,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -63820,7 +63890,7 @@
         <x:v>2650</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>1752863</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -63948,7 +64018,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>10049014</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -64692,31 +64762,31 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2553</x:v>
@@ -64724,66 +64794,66 @@
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
@@ -64794,10 +64864,10 @@
         <x:v>2572</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2556</x:v>
@@ -64806,13 +64876,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2553</x:v>
@@ -64820,16 +64890,16 @@
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2556</x:v>
@@ -64838,13 +64908,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
@@ -64852,42 +64922,42 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2694</x:v>
@@ -64908,7 +64978,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2570</x:v>
@@ -64916,48 +64986,48 @@
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2550</x:v>
@@ -64966,13 +65036,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2553</x:v>
@@ -64980,16 +65050,16 @@
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2550</x:v>
@@ -64998,13 +65068,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2553</x:v>
@@ -65012,31 +65082,31 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2553</x:v>
@@ -65044,31 +65114,31 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>161023</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -65076,10 +65146,10 @@
     </x:row>
     <x:row r="104" spans="1:10">
       <x:c r="A104" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
         <x:v>2486</x:v>
@@ -65100,7 +65170,7 @@
         <x:v>2607</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>63084</x:v>
+        <x:v>161023</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -65108,31 +65178,31 @@
     </x:row>
     <x:row r="105" spans="1:10">
       <x:c r="A105" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
@@ -65140,31 +65210,31 @@
     </x:row>
     <x:row r="106" spans="1:10">
       <x:c r="A106" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -65172,31 +65242,31 @@
     </x:row>
     <x:row r="107" spans="1:10">
       <x:c r="A107" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
@@ -65210,10 +65280,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
         <x:v>2550</x:v>
@@ -65225,12 +65295,44 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="I108" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J108" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:10">
+      <x:c r="A109" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B109" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C109" s="1" t="s">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="D109" s="1" t="s">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="E109" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F109" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G109" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H109" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="I108" s="1">
+      <x:c r="I109" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J108" s="1" t="s">
+      <x:c r="J109" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>
@@ -65250,7 +65352,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C102"/>
+  <x:dimension ref="A1:C103"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -65308,7 +65410,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>2553</x:v>
@@ -65429,7 +65531,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2553</x:v>
@@ -65924,7 +66026,7 @@
         <x:v>2649</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>1752863</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2553</x:v>
@@ -65968,7 +66070,7 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>10399014</x:v>
+        <x:v>11944100</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2553</x:v>
@@ -66218,10 +66320,10 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2553</x:v>
@@ -66229,32 +66331,32 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>2553</x:v>
@@ -66262,10 +66364,10 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2553</x:v>
@@ -66273,32 +66375,32 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>106947</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>2553</x:v>
@@ -66306,10 +66408,10 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2553</x:v>
@@ -66317,10 +66419,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2553</x:v>
@@ -66328,10 +66430,10 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="B98" s="1">
-        <x:v>224107</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2553</x:v>
@@ -66339,10 +66441,10 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="B99" s="1">
-        <x:v>10000</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
         <x:v>2553</x:v>
@@ -66350,10 +66452,10 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="B100" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2553</x:v>
@@ -66361,10 +66463,10 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="B101" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>2553</x:v>
@@ -66372,12 +66474,23 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="1" t="s">
+        <x:v>1836</x:v>
+      </x:c>
+      <x:c r="B102" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:3">
+      <x:c r="A103" s="1" t="s">
         <x:v>2707</x:v>
       </x:c>
-      <x:c r="B102" s="1">
+      <x:c r="B103" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C102" s="1" t="s">
+      <x:c r="C103" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7734,6 +7734,15 @@
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -7771,9 +7780,6 @@
   </x:si>
   <x:si>
     <x:t>CHAVEZ-DEREMER, LORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
   </x:si>
   <x:si>
     <x:t>H4AZ01202</x:t>
@@ -8264,8 +8270,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K113" totalsRowShown="0">
-  <x:autoFilter ref="A1:K113"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K114" totalsRowShown="0">
+  <x:autoFilter ref="A1:K114"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8284,8 +8290,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J109" totalsRowShown="0">
-  <x:autoFilter ref="A1:J109"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J110" totalsRowShown="0">
+  <x:autoFilter ref="A1:J110"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8303,8 +8309,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C103" totalsRowShown="0">
-  <x:autoFilter ref="A1:C103"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C104" totalsRowShown="0">
+  <x:autoFilter ref="A1:C104"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -35954,10 +35960,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
         <x:v>639</x:v>
@@ -35969,7 +35975,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H208" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:8">
@@ -35980,10 +35986,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
         <x:v>639</x:v>
@@ -35995,7 +36001,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H209" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:8">
@@ -57844,7 +57850,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K113"/>
+  <x:dimension ref="A1:K114"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58143,16 +58149,16 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>2571</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>2572</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>2573</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>2574</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>2550</x:v>
@@ -58161,27 +58167,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>2078023</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K9" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>2576</x:v>
@@ -58190,22 +58196,22 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K10" s="1">
         <x:v>2024</x:v>
@@ -58213,45 +58219,45 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>1981</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>83860</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K11" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>1981</x:v>
@@ -58269,30 +58275,30 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K12" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2550</x:v>
@@ -58301,16 +58307,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K13" s="1">
         <x:v>2024</x:v>
@@ -58318,16 +58324,16 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>1992</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>2550</x:v>
@@ -58336,16 +58342,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K14" s="1">
         <x:v>2024</x:v>
@@ -58353,31 +58359,31 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2553</x:v>
@@ -58388,10 +58394,10 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2585</x:v>
@@ -58400,19 +58406,19 @@
         <x:v>2586</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2553</x:v>
@@ -58423,10 +58429,10 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2587</x:v>
@@ -58435,7 +58441,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2551</x:v>
@@ -58444,10 +58450,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -58458,10 +58464,10 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2589</x:v>
@@ -58470,159 +58476,159 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>3343831</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K18" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2022</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>211281</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K19" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K20" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2039</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K21" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>2575</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H22" s="1" t="s">
         <x:v>2597</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>2048</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>1703</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I22" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2553</x:v>
@@ -58633,16 +58639,16 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2556</x:v>
@@ -58651,13 +58657,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2553</x:v>
@@ -58668,34 +58674,34 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K24" s="1">
         <x:v>2024</x:v>
@@ -58703,10 +58709,10 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2601</x:v>
@@ -58721,16 +58727,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K25" s="1">
         <x:v>2024</x:v>
@@ -58738,10 +58744,10 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2603</x:v>
@@ -58759,10 +58765,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2553</x:v>
@@ -58773,10 +58779,10 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2605</x:v>
@@ -58785,19 +58791,19 @@
         <x:v>2606</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2553</x:v>
@@ -58808,16 +58814,16 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2075</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2556</x:v>
@@ -58826,13 +58832,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2553</x:v>
@@ -58843,16 +58849,16 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2082</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2556</x:v>
@@ -58861,13 +58867,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2553</x:v>
@@ -58878,31 +58884,31 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2094</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2553</x:v>
@@ -58913,37 +58919,37 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K31" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -58954,10 +58960,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2100</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2556</x:v>
@@ -58966,86 +58972,86 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K32" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K33" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>2613</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>2614</x:v>
-      </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>63285</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K34" s="1">
         <x:v>2026</x:v>
@@ -59053,16 +59059,16 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -59074,10 +59080,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
@@ -59088,16 +59094,16 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>2616</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>2617</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2556</x:v>
@@ -59109,10 +59115,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
@@ -59123,66 +59129,66 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>2618</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>2619</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>814</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>10039655</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K37" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
@@ -59193,16 +59199,16 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2556</x:v>
@@ -59211,19 +59217,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K39" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -59249,45 +59255,45 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K40" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>2625</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>2626</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>2627</x:v>
-      </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -59304,10 +59310,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -59316,13 +59322,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -59333,16 +59339,16 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2550</x:v>
@@ -59351,13 +59357,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
@@ -59389,7 +59395,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>120103</x:v>
@@ -59403,16 +59409,16 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2550</x:v>
@@ -59421,13 +59427,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
@@ -59438,37 +59444,37 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K46" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -59494,45 +59500,45 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K47" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -59543,31 +59549,31 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -59584,10 +59590,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2556</x:v>
@@ -59596,13 +59602,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -59613,16 +59619,16 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2556</x:v>
@@ -59631,13 +59637,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -59648,31 +59654,31 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -59683,31 +59689,31 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
@@ -59718,37 +59724,37 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K54" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -59759,31 +59765,31 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K55" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -59794,10 +59800,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2550</x:v>
@@ -59806,13 +59812,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
@@ -59823,19 +59829,19 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2551</x:v>
@@ -59844,10 +59850,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
@@ -59858,16 +59864,16 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2556</x:v>
@@ -59876,27 +59882,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K58" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2641</x:v>
@@ -59905,19 +59911,19 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
@@ -59928,10 +59934,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2643</x:v>
@@ -59940,19 +59946,19 @@
         <x:v>2644</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -59963,66 +59969,66 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2645</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
@@ -60033,31 +60039,31 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -60068,31 +60074,31 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -60103,31 +60109,31 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -60138,16 +60144,16 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2550</x:v>
@@ -60156,19 +60162,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>2779856</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -60179,10 +60185,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>2650</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>2651</x:v>
-      </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>1299</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>2550</x:v>
@@ -60191,48 +60197,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>215063</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -60243,10 +60249,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2654</x:v>
@@ -60258,30 +60264,30 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K69" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2656</x:v>
@@ -60296,13 +60302,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>11594100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
@@ -60313,16 +60319,16 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2556</x:v>
@@ -60337,7 +60343,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>350000</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -60348,10 +60354,10 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2658</x:v>
@@ -60363,22 +60369,22 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>726377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -60401,19 +60407,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -60424,10 +60430,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2556</x:v>
@@ -60439,16 +60445,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -60459,25 +60465,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
@@ -60488,16 +60494,16 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2556</x:v>
@@ -60506,27 +60512,27 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K76" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2664</x:v>
@@ -60538,16 +60544,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
@@ -60558,66 +60564,66 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>1894</x:v>
-      </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
@@ -60628,31 +60634,31 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2553</x:v>
@@ -60663,10 +60669,10 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>2670</x:v>
@@ -60675,19 +60681,19 @@
         <x:v>2671</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2553</x:v>
@@ -60716,27 +60722,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K82" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2674</x:v>
@@ -60748,16 +60754,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2553</x:v>
@@ -60768,10 +60774,10 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2676</x:v>
@@ -60780,22 +60786,22 @@
         <x:v>2677</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K84" s="1">
         <x:v>2026</x:v>
@@ -60803,16 +60809,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
         <x:v>2679</x:v>
-      </x:c>
-      <x:c r="D85" s="1" t="s">
-        <x:v>2680</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2550</x:v>
@@ -60821,27 +60827,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2681</x:v>
@@ -60856,33 +60862,33 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2550</x:v>
@@ -60891,51 +60897,51 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K88" s="1">
         <x:v>2024</x:v>
@@ -60943,34 +60949,34 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K89" s="1">
         <x:v>2024</x:v>
@@ -60978,51 +60984,51 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2556</x:v>
@@ -61031,13 +61037,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2553</x:v>
@@ -61048,51 +61054,51 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K92" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2550</x:v>
@@ -61101,19 +61107,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -61124,133 +61130,133 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>282975</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K95" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K96" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K97" s="1">
         <x:v>2024</x:v>
@@ -61258,34 +61264,34 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K98" s="1">
         <x:v>2024</x:v>
@@ -61293,16 +61299,16 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2556</x:v>
@@ -61311,13 +61317,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2553</x:v>
@@ -61328,16 +61334,16 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2556</x:v>
@@ -61346,27 +61352,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K100" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>2694</x:v>
@@ -61375,22 +61381,22 @@
         <x:v>2695</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>9866096</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K101" s="1">
         <x:v>2026</x:v>
@@ -61404,10 +61410,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2550</x:v>
@@ -61433,10 +61439,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
         <x:v>2696</x:v>
@@ -61448,36 +61454,36 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="K103" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2550</x:v>
@@ -61486,13 +61492,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -61503,16 +61509,16 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
         <x:v>2550</x:v>
@@ -61521,13 +61527,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
@@ -61538,31 +61544,31 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -61573,37 +61579,37 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>50875</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K107" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -61629,24 +61635,24 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>110148</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K108" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
         <x:v>2486</x:v>
@@ -61664,10 +61670,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>63084</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
         <x:v>2553</x:v>
@@ -61678,31 +61684,31 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2553</x:v>
@@ -61713,31 +61719,31 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2553</x:v>
@@ -61748,31 +61754,31 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J112" s="1" t="s">
         <x:v>2553</x:v>
@@ -61789,10 +61795,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>2550</x:v>
@@ -61804,15 +61810,50 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J113" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K113" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:11">
+      <x:c r="A114" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B114" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C114" s="1" t="s">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="D114" s="1" t="s">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="E114" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F114" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G114" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H114" s="1" t="s">
+        <x:v>2680</x:v>
+      </x:c>
+      <x:c r="I114" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J114" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K114" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61832,7 +61873,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J109"/>
+  <x:dimension ref="A1:J110"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -62074,16 +62115,16 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>2571</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>2572</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>2573</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>2574</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>2550</x:v>
@@ -62092,24 +62133,24 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>2078023</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>2576</x:v>
@@ -62118,51 +62159,51 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>1981</x:v>
+        <x:v>2579</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>582374</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2553</x:v>
@@ -62170,10 +62211,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>1981</x:v>
@@ -62191,10 +62232,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2553</x:v>
@@ -62202,16 +62243,16 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2579</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2550</x:v>
@@ -62220,30 +62261,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>1406523</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>1992</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2550</x:v>
@@ -62252,45 +62293,45 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2553</x:v>
@@ -62298,10 +62339,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2585</x:v>
@@ -62310,19 +62351,19 @@
         <x:v>2586</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2553</x:v>
@@ -62330,10 +62371,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2587</x:v>
@@ -62342,7 +62383,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2551</x:v>
@@ -62351,10 +62392,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2553</x:v>
@@ -62362,10 +62403,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2589</x:v>
@@ -62374,19 +62415,19 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>3343831</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -62394,31 +62435,31 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2022</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>211281</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2553</x:v>
@@ -62426,31 +62467,31 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
@@ -62458,31 +62499,31 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2039</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
@@ -62490,31 +62531,31 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>2575</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H21" s="1" t="s">
         <x:v>2597</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>2048</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>1703</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I21" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2553</x:v>
@@ -62522,16 +62563,16 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>2556</x:v>
@@ -62540,13 +62581,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2553</x:v>
@@ -62554,42 +62595,42 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2601</x:v>
@@ -62604,24 +62645,24 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2603</x:v>
@@ -62639,10 +62680,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2553</x:v>
@@ -62650,10 +62691,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2605</x:v>
@@ -62662,19 +62703,19 @@
         <x:v>2606</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2553</x:v>
@@ -62682,16 +62723,16 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2075</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2556</x:v>
@@ -62700,13 +62741,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2553</x:v>
@@ -62714,16 +62755,16 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2082</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2556</x:v>
@@ -62732,13 +62773,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2553</x:v>
@@ -62746,31 +62787,31 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2094</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2553</x:v>
@@ -62778,31 +62819,31 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2553</x:v>
@@ -62816,10 +62857,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2100</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2556</x:v>
@@ -62828,13 +62869,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2553</x:v>
@@ -62842,80 +62883,80 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>2613</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>2614</x:v>
-      </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>2556</x:v>
@@ -62927,10 +62968,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>63285</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2553</x:v>
@@ -62944,10 +62985,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2616</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -62959,10 +63000,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>64338</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
@@ -62970,31 +63011,31 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2618</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>2619</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>814</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>10039655</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
@@ -63002,31 +63043,31 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -63034,16 +63075,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>2556</x:v>
@@ -63052,13 +63093,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
@@ -63087,10 +63128,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
@@ -63098,31 +63139,31 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>2625</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>2626</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>2627</x:v>
-      </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
@@ -63136,10 +63177,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2550</x:v>
@@ -63148,13 +63189,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -63168,10 +63209,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -63180,13 +63221,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -63194,10 +63235,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2131</x:v>
@@ -63215,10 +63256,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
@@ -63226,16 +63267,16 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2550</x:v>
@@ -63244,13 +63285,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -63258,31 +63299,31 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
@@ -63290,31 +63331,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
@@ -63322,31 +63363,31 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
@@ -63360,10 +63401,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>2556</x:v>
@@ -63372,13 +63413,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -63386,16 +63427,16 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2556</x:v>
@@ -63404,13 +63445,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -63418,31 +63459,31 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -63450,31 +63491,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -63482,31 +63523,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -63520,25 +63561,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
@@ -63552,10 +63593,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2550</x:v>
@@ -63564,13 +63605,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
@@ -63578,19 +63619,19 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
         <x:v>2551</x:v>
@@ -63599,10 +63640,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
@@ -63610,16 +63651,16 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2556</x:v>
@@ -63628,13 +63669,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
@@ -63642,10 +63683,10 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2641</x:v>
@@ -63654,19 +63695,19 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
@@ -63674,10 +63715,10 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2643</x:v>
@@ -63686,19 +63727,19 @@
         <x:v>2644</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
@@ -63706,31 +63747,31 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2645</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
@@ -63738,31 +63779,31 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -63770,31 +63811,31 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -63802,31 +63843,31 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
@@ -63834,31 +63875,31 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -63866,16 +63907,16 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2550</x:v>
@@ -63884,13 +63925,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>2779856</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -63904,10 +63945,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>2650</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>2651</x:v>
-      </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>1299</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2550</x:v>
@@ -63916,13 +63957,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>215063</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -63930,31 +63971,31 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
@@ -63962,10 +64003,10 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2654</x:v>
@@ -63977,16 +64018,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
@@ -63994,10 +64035,10 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2656</x:v>
@@ -64012,13 +64053,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>11594100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -64026,16 +64067,16 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2556</x:v>
@@ -64050,7 +64091,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>350000</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -64058,10 +64099,10 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2658</x:v>
@@ -64073,16 +64114,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>726377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
@@ -64108,13 +64149,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -64128,25 +64169,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
@@ -64154,16 +64195,16 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2556</x:v>
@@ -64172,13 +64213,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
@@ -64186,10 +64227,10 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2664</x:v>
@@ -64201,16 +64242,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
@@ -64218,31 +64259,31 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
+        <x:v>2666</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
-      <x:c r="D75" s="1" t="s">
-        <x:v>1894</x:v>
-      </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
@@ -64250,31 +64291,31 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
@@ -64282,31 +64323,31 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
@@ -64314,10 +64355,10 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>2670</x:v>
@@ -64326,19 +64367,19 @@
         <x:v>2671</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
@@ -64364,13 +64405,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
@@ -64378,10 +64419,10 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2674</x:v>
@@ -64393,16 +64434,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2553</x:v>
@@ -64410,10 +64451,10 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>2676</x:v>
@@ -64422,36 +64463,36 @@
         <x:v>2677</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
         <x:v>2679</x:v>
-      </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>2680</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2550</x:v>
@@ -64460,24 +64501,24 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2681</x:v>
@@ -64492,30 +64533,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2550</x:v>
@@ -64524,109 +64565,109 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2553</x:v>
@@ -64634,16 +64675,16 @@
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2556</x:v>
@@ -64652,13 +64693,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2553</x:v>
@@ -64666,31 +64707,31 @@
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2553</x:v>
@@ -64698,16 +64739,16 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2550</x:v>
@@ -64716,16 +64757,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:10">
@@ -64736,57 +64777,57 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>282975</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2553</x:v>
@@ -64794,31 +64835,31 @@
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2553</x:v>
@@ -64826,80 +64867,80 @@
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2556</x:v>
@@ -64908,13 +64949,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
@@ -64922,16 +64963,16 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2556</x:v>
@@ -64940,13 +64981,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2553</x:v>
@@ -64954,10 +64995,10 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2694</x:v>
@@ -64966,36 +65007,36 @@
         <x:v>2695</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2550</x:v>
@@ -65010,7 +65051,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2570</x:v>
@@ -65018,10 +65059,10 @@
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2696</x:v>
@@ -65033,33 +65074,33 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2550</x:v>
@@ -65068,13 +65109,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2553</x:v>
@@ -65082,16 +65123,16 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2550</x:v>
@@ -65100,13 +65141,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2553</x:v>
@@ -65114,31 +65155,31 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -65146,31 +65187,31 @@
     </x:row>
     <x:row r="104" spans="1:10">
       <x:c r="A104" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>161023</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -65178,10 +65219,10 @@
     </x:row>
     <x:row r="105" spans="1:10">
       <x:c r="A105" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
         <x:v>2486</x:v>
@@ -65199,10 +65240,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2607</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>63084</x:v>
+        <x:v>161023</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
@@ -65210,31 +65251,31 @@
     </x:row>
     <x:row r="106" spans="1:10">
       <x:c r="A106" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>10000</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -65242,31 +65283,31 @@
     </x:row>
     <x:row r="107" spans="1:10">
       <x:c r="A107" s="1" t="s">
-        <x:v>2571</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
@@ -65274,31 +65315,31 @@
     </x:row>
     <x:row r="108" spans="1:10">
       <x:c r="A108" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2574</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
@@ -65312,10 +65353,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
         <x:v>2550</x:v>
@@ -65327,12 +65368,44 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="I109" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J109" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:10">
+      <x:c r="A110" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B110" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C110" s="1" t="s">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="D110" s="1" t="s">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="E110" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F110" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G110" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H110" s="1" t="s">
+        <x:v>2680</x:v>
+      </x:c>
+      <x:c r="I110" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J109" s="1" t="s">
+      <x:c r="J110" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>
@@ -65352,7 +65425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C103"/>
+  <x:dimension ref="A1:C104"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -65440,13 +65513,13 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>2078023</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -65454,18 +65527,18 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>666234</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>2553</x:v>
@@ -65473,32 +65546,32 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>1406523</x:v>
+        <x:v>666234</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2553</x:v>
@@ -65509,7 +65582,7 @@
         <x:v>2586</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2553</x:v>
@@ -65520,7 +65593,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2553</x:v>
@@ -65531,7 +65604,7 @@
         <x:v>2590</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>3343831</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2553</x:v>
@@ -65539,10 +65612,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>211281</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2553</x:v>
@@ -65550,10 +65623,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2553</x:v>
@@ -65561,10 +65634,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2553</x:v>
@@ -65572,10 +65645,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>1703</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2553</x:v>
@@ -65583,10 +65656,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2553</x:v>
@@ -65594,13 +65667,13 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -65608,10 +65681,10 @@
         <x:v>2602</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -65619,7 +65692,7 @@
         <x:v>2604</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2553</x:v>
@@ -65630,7 +65703,7 @@
         <x:v>2606</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2553</x:v>
@@ -65638,10 +65711,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2553</x:v>
@@ -65649,10 +65722,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2553</x:v>
@@ -65660,10 +65733,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2553</x:v>
@@ -65671,10 +65744,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>2553</x:v>
@@ -65682,10 +65755,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>2553</x:v>
@@ -65693,32 +65766,32 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>363285</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>64338</x:v>
+        <x:v>363285</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2553</x:v>
@@ -65726,10 +65799,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>10039655</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2553</x:v>
@@ -65737,10 +65810,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B35" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>2553</x:v>
@@ -65748,10 +65821,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="B36" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>2553</x:v>
@@ -65762,7 +65835,7 @@
         <x:v>2624</x:v>
       </x:c>
       <x:c r="B37" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>2553</x:v>
@@ -65770,10 +65843,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="B38" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>2553</x:v>
@@ -65781,10 +65854,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="B39" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>2553</x:v>
@@ -65792,10 +65865,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="B40" s="1">
-        <x:v>242791</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>2553</x:v>
@@ -65803,10 +65876,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="B41" s="1">
-        <x:v>3954592</x:v>
+        <x:v>242791</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>2553</x:v>
@@ -65814,10 +65887,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="B42" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>2553</x:v>
@@ -65825,10 +65898,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B43" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>2553</x:v>
@@ -65836,10 +65909,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2553</x:v>
@@ -65847,10 +65920,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2553</x:v>
@@ -65858,10 +65931,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2553</x:v>
@@ -65869,10 +65942,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2553</x:v>
@@ -65880,10 +65953,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2553</x:v>
@@ -65891,10 +65964,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2553</x:v>
@@ -65902,10 +65975,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2553</x:v>
@@ -65913,10 +65986,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2553</x:v>
@@ -65924,10 +65997,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2553</x:v>
@@ -65935,10 +66008,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2553</x:v>
@@ -65949,7 +66022,7 @@
         <x:v>2642</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2553</x:v>
@@ -65960,7 +66033,7 @@
         <x:v>2644</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2553</x:v>
@@ -65968,10 +66041,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2553</x:v>
@@ -65979,10 +66052,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2553</x:v>
@@ -65990,10 +66063,10 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2553</x:v>
@@ -66001,10 +66074,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2553</x:v>
@@ -66012,10 +66085,10 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2553</x:v>
@@ -66023,10 +66096,10 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>2779856</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2553</x:v>
@@ -66034,10 +66107,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>215063</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2553</x:v>
@@ -66045,10 +66118,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2553</x:v>
@@ -66059,7 +66132,7 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2553</x:v>
@@ -66070,7 +66143,7 @@
         <x:v>2657</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>11944100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2553</x:v>
@@ -66081,7 +66154,7 @@
         <x:v>2659</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>726377</x:v>
+        <x:v>11944100</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2553</x:v>
@@ -66092,7 +66165,7 @@
         <x:v>2661</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2553</x:v>
@@ -66100,10 +66173,10 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2553</x:v>
@@ -66111,10 +66184,10 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2553</x:v>
@@ -66125,7 +66198,7 @@
         <x:v>2665</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>282526</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2553</x:v>
@@ -66133,10 +66206,10 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2553</x:v>
@@ -66144,10 +66217,10 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2553</x:v>
@@ -66155,10 +66228,10 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2553</x:v>
@@ -66169,7 +66242,7 @@
         <x:v>2671</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2553</x:v>
@@ -66180,7 +66253,7 @@
         <x:v>2673</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2553</x:v>
@@ -66191,7 +66264,7 @@
         <x:v>2675</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2553</x:v>
@@ -66202,21 +66275,21 @@
         <x:v>2677</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
@@ -66224,51 +66297,51 @@
         <x:v>2682</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2553</x:v>
@@ -66276,10 +66349,10 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
         <x:v>2553</x:v>
@@ -66287,10 +66360,10 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>2553</x:v>
@@ -66298,32 +66371,32 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>282975</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>2553</x:v>
@@ -66331,10 +66404,10 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2553</x:v>
@@ -66342,32 +66415,32 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2553</x:v>
@@ -66375,10 +66448,10 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>2553</x:v>
@@ -66389,10 +66462,10 @@
         <x:v>2695</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>9985740</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:3">
@@ -66400,18 +66473,18 @@
         <x:v>2697</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>106947</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2570</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2553</x:v>
@@ -66419,10 +66492,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2553</x:v>
@@ -66430,10 +66503,10 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="B98" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>2553</x:v>
@@ -66441,10 +66514,10 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="B99" s="1">
-        <x:v>224107</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
         <x:v>2553</x:v>
@@ -66452,10 +66525,10 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="B100" s="1">
-        <x:v>10000</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2553</x:v>
@@ -66463,10 +66536,10 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="B101" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>2553</x:v>
@@ -66474,10 +66547,10 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="B102" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
         <x:v>2553</x:v>
@@ -66485,12 +66558,23 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="B103" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:3">
+      <x:c r="A104" s="1" t="s">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="B104" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C103" s="1" t="s">
+      <x:c r="C104" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7704,6 +7704,15 @@
     <x:t>00</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00286</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0KY06104</x:t>
   </x:si>
   <x:si>
@@ -7798,12 +7807,6 @@
   </x:si>
   <x:si>
     <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
     <x:t>S6GA00390</x:t>
@@ -8270,8 +8273,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K114" totalsRowShown="0">
-  <x:autoFilter ref="A1:K114"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K115" totalsRowShown="0">
+  <x:autoFilter ref="A1:K115"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8290,8 +8293,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J110" totalsRowShown="0">
-  <x:autoFilter ref="A1:J110"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J111" totalsRowShown="0">
+  <x:autoFilter ref="A1:J111"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -57850,7 +57853,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K114"/>
+  <x:dimension ref="A1:K115"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58009,13 +58012,13 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>104</x:v>
@@ -58024,16 +58027,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>3590517</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2553</x:v>
@@ -58050,7 +58053,7 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>104</x:v>
@@ -58065,94 +58068,94 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>106708</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K6" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>557012</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K7" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>2566</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>2567</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>2568</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>2569</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K8" s="1">
-        <x:v>2022</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>2571</x:v>
@@ -58164,36 +58167,36 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
+        <x:v>248811</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>2573</x:v>
       </x:c>
-      <x:c r="I9" s="1">
-        <x:v>243968</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>2553</x:v>
-      </x:c>
       <x:c r="K9" s="1">
-        <x:v>2026</x:v>
+        <x:v>2022</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>2574</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>2575</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>2576</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>2577</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>2550</x:v>
@@ -58202,27 +58205,27 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>2078023</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K10" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>2579</x:v>
@@ -58231,22 +58234,22 @@
         <x:v>2580</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>2024</x:v>
@@ -58254,45 +58257,45 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1981</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>83860</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K12" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>1981</x:v>
@@ -58310,30 +58313,30 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K13" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>2550</x:v>
@@ -58342,16 +58345,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K14" s="1">
         <x:v>2024</x:v>
@@ -58359,16 +58362,16 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>1992</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>2550</x:v>
@@ -58377,16 +58380,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K15" s="1">
         <x:v>2024</x:v>
@@ -58394,31 +58397,31 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2553</x:v>
@@ -58429,31 +58432,31 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -58464,19 +58467,19 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>2551</x:v>
@@ -58485,10 +58488,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2553</x:v>
@@ -58499,171 +58502,171 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>3399876</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K19" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2022</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>211281</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K20" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K21" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2039</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K22" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
+        <x:v>2577</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>2578</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
         <x:v>2598</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>2599</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>2048</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>1703</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I23" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2553</x:v>
@@ -58674,16 +58677,16 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2556</x:v>
@@ -58692,13 +58695,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2553</x:v>
@@ -58709,34 +58712,34 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2601</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K25" s="1">
         <x:v>2024</x:v>
@@ -58744,16 +58747,16 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>2603</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>2604</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2550</x:v>
@@ -58762,16 +58765,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K26" s="1">
         <x:v>2024</x:v>
@@ -58779,16 +58782,16 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2605</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2606</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2550</x:v>
@@ -58800,10 +58803,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2553</x:v>
@@ -58814,31 +58817,31 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2607</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2608</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2553</x:v>
@@ -58849,16 +58852,16 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2075</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2556</x:v>
@@ -58867,13 +58870,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2553</x:v>
@@ -58884,16 +58887,16 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2082</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>2556</x:v>
@@ -58902,13 +58905,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2553</x:v>
@@ -58919,31 +58922,31 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2094</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2553</x:v>
@@ -58954,37 +58957,37 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K32" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -58995,10 +58998,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2100</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2556</x:v>
@@ -59007,86 +59010,86 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K33" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K34" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>63285</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K35" s="1">
         <x:v>2026</x:v>
@@ -59094,16 +59097,16 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2556</x:v>
@@ -59115,10 +59118,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>300000</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
@@ -59129,16 +59132,16 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>2556</x:v>
@@ -59150,10 +59153,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -59164,66 +59167,66 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>2619</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>2620</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="s">
         <x:v>2621</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>814</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H38" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I38" s="1">
-        <x:v>10039655</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K38" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
@@ -59234,16 +59237,16 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2556</x:v>
@@ -59252,19 +59255,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K40" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -59275,10 +59278,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>2624</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>2625</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>2626</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>2556</x:v>
@@ -59290,45 +59293,45 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K41" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -59345,10 +59348,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2550</x:v>
@@ -59357,13 +59360,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
@@ -59380,10 +59383,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2550</x:v>
@@ -59392,13 +59395,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -59409,10 +59412,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>2131</x:v>
@@ -59430,7 +59433,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>122688</x:v>
@@ -59450,10 +59453,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>2550</x:v>
@@ -59462,13 +59465,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>3954592</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
@@ -59479,37 +59482,37 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K47" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -59535,45 +59538,45 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K48" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -59584,31 +59587,31 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -59625,10 +59628,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2556</x:v>
@@ -59637,13 +59640,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -59654,16 +59657,16 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>2556</x:v>
@@ -59672,13 +59675,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -59689,31 +59692,31 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
@@ -59724,31 +59727,31 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
@@ -59759,37 +59762,37 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K55" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -59800,31 +59803,31 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
         <x:v>2638</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K56" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
@@ -59835,10 +59838,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2550</x:v>
@@ -59847,13 +59850,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
         <x:v>2639</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
@@ -59864,19 +59867,19 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
         <x:v>2551</x:v>
@@ -59888,7 +59891,7 @@
         <x:v>2640</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
@@ -59899,16 +59902,16 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2556</x:v>
@@ -59917,48 +59920,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K59" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
+        <x:v>2642</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
         <x:v>2643</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>2644</x:v>
-      </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>30183</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -59969,31 +59972,31 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
+        <x:v>2644</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
         <x:v>2645</x:v>
       </x:c>
-      <x:c r="D61" s="1" t="s">
-        <x:v>2646</x:v>
-      </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -60004,66 +60007,66 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
+        <x:v>2646</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
         <x:v>2647</x:v>
-      </x:c>
-      <x:c r="D62" s="1" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K62" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2648</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -60074,31 +60077,31 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -60109,31 +60112,31 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -60144,31 +60147,31 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
@@ -60179,16 +60182,16 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>2550</x:v>
@@ -60197,19 +60200,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>2779856</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -60220,10 +60223,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2550</x:v>
@@ -60232,48 +60235,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>215063</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2654</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -60284,51 +60287,51 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
+        <x:v>2655</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
         <x:v>2656</x:v>
-      </x:c>
-      <x:c r="D70" s="1" t="s">
-        <x:v>2657</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K70" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>2657</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>2658</x:v>
-      </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>2659</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2556</x:v>
@@ -60337,13 +60340,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>11594100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -60354,16 +60357,16 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2556</x:v>
@@ -60378,7 +60381,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>350000</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
@@ -60389,37 +60392,37 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
+        <x:v>2659</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
         <x:v>2660</x:v>
-      </x:c>
-      <x:c r="D73" s="1" t="s">
-        <x:v>2661</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>726377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K73" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -60430,10 +60433,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
+        <x:v>2661</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
         <x:v>2662</x:v>
-      </x:c>
-      <x:c r="D74" s="1" t="s">
-        <x:v>2663</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2556</x:v>
@@ -60442,19 +60445,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>161896</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -60465,10 +60468,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2556</x:v>
@@ -60480,16 +60483,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>506553</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K75" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -60500,25 +60503,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>40134929</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
@@ -60529,16 +60532,16 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2556</x:v>
@@ -60547,48 +60550,48 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>2665</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>2666</x:v>
-      </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>2667</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>282526</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
@@ -60599,66 +60602,66 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K79" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2553</x:v>
@@ -60669,31 +60672,31 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2553</x:v>
@@ -60704,31 +60707,31 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
+        <x:v>2671</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
         <x:v>2672</x:v>
       </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>2673</x:v>
-      </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2553</x:v>
@@ -60745,10 +60748,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
+        <x:v>2673</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
         <x:v>2674</x:v>
-      </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>2675</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2556</x:v>
@@ -60757,48 +60760,48 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K83" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>2675</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>2676</x:v>
-      </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>2677</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2553</x:v>
@@ -60809,34 +60812,34 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
+        <x:v>2677</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="D85" s="1" t="s">
-        <x:v>2679</x:v>
-      </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K85" s="1">
         <x:v>2026</x:v>
@@ -60844,16 +60847,16 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2550</x:v>
@@ -60862,33 +60865,33 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
+        <x:v>2682</x:v>
+      </x:c>
+      <x:c r="D87" s="1" t="s">
         <x:v>2683</x:v>
-      </x:c>
-      <x:c r="D87" s="1" t="s">
-        <x:v>2684</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2550</x:v>
@@ -60897,33 +60900,33 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
         <x:v>2550</x:v>
@@ -60932,51 +60935,51 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K89" s="1">
         <x:v>2024</x:v>
@@ -60984,34 +60987,34 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>2686</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K90" s="1">
         <x:v>2024</x:v>
@@ -61019,51 +61022,51 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K91" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2556</x:v>
@@ -61072,13 +61075,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2553</x:v>
@@ -61089,51 +61092,51 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2550</x:v>
@@ -61142,19 +61145,19 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -61165,133 +61168,133 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K95" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>282975</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K96" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K97" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K98" s="1">
         <x:v>2024</x:v>
@@ -61299,34 +61302,34 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K99" s="1">
         <x:v>2024</x:v>
@@ -61334,16 +61337,16 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2556</x:v>
@@ -61352,13 +61355,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2553</x:v>
@@ -61369,16 +61372,16 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2556</x:v>
@@ -61387,51 +61390,51 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="D102" s="1" t="s">
         <x:v>2696</x:v>
       </x:c>
-      <x:c r="D102" s="1" t="s">
-        <x:v>2697</x:v>
-      </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="K102" s="1">
         <x:v>2026</x:v>
@@ -61439,16 +61442,16 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2550</x:v>
@@ -61466,7 +61469,7 @@
         <x:v>9866096</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K103" s="1">
         <x:v>2026</x:v>
@@ -61480,45 +61483,45 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
+        <x:v>2697</x:v>
+      </x:c>
+      <x:c r="D104" s="1" t="s">
         <x:v>2698</x:v>
-      </x:c>
-      <x:c r="D104" s="1" t="s">
-        <x:v>2699</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>106947</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="K104" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
         <x:v>2550</x:v>
@@ -61527,13 +61530,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
@@ -61544,16 +61547,16 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
         <x:v>2550</x:v>
@@ -61562,13 +61565,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2553</x:v>
@@ -61579,31 +61582,31 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
@@ -61614,37 +61617,37 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>50875</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K108" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -61670,24 +61673,24 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>110148</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K109" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
         <x:v>2486</x:v>
@@ -61705,7 +61708,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I110" s="1">
         <x:v>63084</x:v>
@@ -61719,31 +61722,31 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>10000</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2553</x:v>
@@ -61754,31 +61757,31 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J112" s="1" t="s">
         <x:v>2553</x:v>
@@ -61789,31 +61792,31 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2708</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J113" s="1" t="s">
         <x:v>2553</x:v>
@@ -61830,10 +61833,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
         <x:v>2550</x:v>
@@ -61845,15 +61848,50 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H114" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I114" s="1">
-        <x:v>1012792</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="J114" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="K114" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:11">
+      <x:c r="A115" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B115" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C115" s="1" t="s">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="D115" s="1" t="s">
+        <x:v>2710</x:v>
+      </x:c>
+      <x:c r="E115" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F115" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G115" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H115" s="1" t="s">
+        <x:v>2681</x:v>
+      </x:c>
+      <x:c r="I115" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J115" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="K115" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -61873,7 +61911,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J110"/>
+  <x:dimension ref="A1:J111"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -62019,13 +62057,13 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>104</x:v>
@@ -62034,16 +62072,16 @@
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>3697225</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
         <x:v>2553</x:v>
@@ -62051,31 +62089,31 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
         <x:v>2565</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>557012</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2553</x:v>
@@ -62083,42 +62121,42 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>2566</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>2567</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>2568</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>2569</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>248811</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2569</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>2571</x:v>
@@ -62130,33 +62168,33 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
+        <x:v>2560</x:v>
+      </x:c>
+      <x:c r="I8" s="1">
+        <x:v>248811</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="s">
         <x:v>2573</x:v>
-      </x:c>
-      <x:c r="I8" s="1">
-        <x:v>243968</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>2574</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>2575</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>2576</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>2577</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>2550</x:v>
@@ -62165,24 +62203,24 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>2078023</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>2579</x:v>
@@ -62191,51 +62229,51 @@
         <x:v>2580</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>530840</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>1981</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>1397</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>582374</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2553</x:v>
@@ -62264,7 +62302,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>83860</x:v>
@@ -62275,16 +62313,16 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2550</x:v>
@@ -62293,30 +62331,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>1406523</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>1992</x:v>
+        <x:v>2585</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>2550</x:v>
@@ -62325,45 +62363,45 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>2270929</x:v>
+        <x:v>1406523</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2585</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>1514370</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2553</x:v>
@@ -62371,31 +62409,31 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2587</x:v>
+        <x:v>2588</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>415283</x:v>
+        <x:v>1514370</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2553</x:v>
@@ -62403,19 +62441,19 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2590</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>2551</x:v>
@@ -62424,10 +62462,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>1625297</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2553</x:v>
@@ -62435,31 +62473,31 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2591</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>3399876</x:v>
+        <x:v>1625297</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2553</x:v>
@@ -62467,31 +62505,31 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2022</x:v>
+        <x:v>2594</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>211281</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
@@ -62499,31 +62537,31 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2595</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>350000</x:v>
+        <x:v>211281</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
@@ -62531,31 +62569,31 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>2039</x:v>
+        <x:v>2596</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>973501</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2553</x:v>
@@ -62563,31 +62601,31 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
+        <x:v>2577</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>2578</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H22" s="1" t="s">
         <x:v>2598</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>2599</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>2048</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>1703</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>2556</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I22" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2553</x:v>
@@ -62595,16 +62633,16 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2600</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2556</x:v>
@@ -62613,13 +62651,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2553</x:v>
@@ -62627,48 +62665,48 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2601</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>2603</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>2604</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2550</x:v>
@@ -62677,30 +62715,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>2605</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>2606</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2550</x:v>
@@ -62712,10 +62750,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2553</x:v>
@@ -62723,31 +62761,31 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2607</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2608</x:v>
-      </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>813215</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2553</x:v>
@@ -62755,16 +62793,16 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>2075</x:v>
+        <x:v>2608</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1794</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2556</x:v>
@@ -62773,13 +62811,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2553</x:v>
@@ -62787,16 +62825,16 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2082</x:v>
+        <x:v>2075</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2556</x:v>
@@ -62805,13 +62843,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2553</x:v>
@@ -62819,31 +62857,31 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2094</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2553</x:v>
@@ -62851,31 +62889,31 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2610</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2553</x:v>
@@ -62889,10 +62927,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2100</x:v>
+        <x:v>2611</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1324</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2556</x:v>
@@ -62901,13 +62939,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2553</x:v>
@@ -62915,80 +62953,80 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2612</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2613</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2556</x:v>
@@ -63000,10 +63038,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>63285</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2553</x:v>
@@ -63017,10 +63055,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2556</x:v>
@@ -63032,10 +63070,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>64338</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2553</x:v>
@@ -63043,31 +63081,31 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>2619</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>2620</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>2556</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="s">
         <x:v>2621</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>814</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>2559</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H37" s="1" t="s">
-        <x:v>2560</x:v>
-      </x:c>
       <x:c r="I37" s="1">
-        <x:v>10039655</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
         <x:v>2553</x:v>
@@ -63075,31 +63113,31 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2115</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1327</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
         <x:v>2553</x:v>
@@ -63107,16 +63145,16 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2556</x:v>
@@ -63125,13 +63163,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I39" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
         <x:v>2553</x:v>
@@ -63145,10 +63183,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>2624</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>2625</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>2626</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2556</x:v>
@@ -63160,10 +63198,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2553</x:v>
@@ -63171,31 +63209,31 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H41" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2628</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2553</x:v>
@@ -63209,10 +63247,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2125</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>2550</x:v>
@@ -63221,13 +63259,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2630</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2553</x:v>
@@ -63241,10 +63279,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2131</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2550</x:v>
@@ -63253,13 +63291,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>120103</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2553</x:v>
@@ -63267,10 +63305,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>2131</x:v>
@@ -63288,10 +63326,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2553</x:v>
@@ -63299,16 +63337,16 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2131</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>2550</x:v>
@@ -63317,13 +63355,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>3954592</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2553</x:v>
@@ -63331,31 +63369,31 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2167</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2553</x:v>
@@ -63363,31 +63401,31 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2175</x:v>
+        <x:v>2167</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1394</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2553</x:v>
@@ -63395,31 +63433,31 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2181</x:v>
+        <x:v>2175</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
         <x:v>2557</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2553</x:v>
@@ -63433,10 +63471,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2189</x:v>
+        <x:v>2181</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2556</x:v>
@@ -63445,13 +63483,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2553</x:v>
@@ -63459,16 +63497,16 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2195</x:v>
+        <x:v>2189</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2556</x:v>
@@ -63477,13 +63515,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2553</x:v>
@@ -63491,31 +63529,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>2195</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2635</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2553</x:v>
@@ -63523,31 +63561,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2204</x:v>
+        <x:v>2634</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2553</x:v>
@@ -63555,31 +63593,31 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2204</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1535</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2553</x:v>
@@ -63593,25 +63631,25 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2215</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2638</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2553</x:v>
@@ -63625,10 +63663,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2216</x:v>
+        <x:v>2215</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1523</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2550</x:v>
@@ -63637,13 +63675,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
         <x:v>2639</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2553</x:v>
@@ -63651,19 +63689,19 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2220</x:v>
+        <x:v>2216</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1912</x:v>
+        <x:v>1523</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
         <x:v>2551</x:v>
@@ -63675,7 +63713,7 @@
         <x:v>2640</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2553</x:v>
@@ -63683,16 +63721,16 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2220</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2556</x:v>
@@ -63701,13 +63739,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>54935</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2553</x:v>
@@ -63715,31 +63753,31 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>2642</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>2643</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>2644</x:v>
-      </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>30183</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2553</x:v>
@@ -63747,31 +63785,31 @@
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>2644</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>2645</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>2646</x:v>
-      </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2553</x:v>
@@ -63779,31 +63817,31 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
+        <x:v>2646</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
         <x:v>2647</x:v>
-      </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2553</x:v>
@@ -63811,31 +63849,31 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2648</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>112913</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2553</x:v>
@@ -63843,31 +63881,31 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2291</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>34970</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2553</x:v>
@@ -63875,31 +63913,31 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2296</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>1287</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>126626</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2553</x:v>
@@ -63907,31 +63945,31 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2301</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2573</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>46160</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2553</x:v>
@@ -63939,16 +63977,16 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2550</x:v>
@@ -63957,13 +63995,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2576</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>2779856</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2553</x:v>
@@ -63977,10 +64015,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>1299</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2550</x:v>
@@ -63989,13 +64027,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>215063</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
@@ -64003,31 +64041,31 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2654</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>504020</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2553</x:v>
@@ -64035,31 +64073,31 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
+        <x:v>2655</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
         <x:v>2656</x:v>
-      </x:c>
-      <x:c r="D68" s="1" t="s">
-        <x:v>2657</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>250000</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -64067,16 +64105,16 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
+        <x:v>2657</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
         <x:v>2658</x:v>
-      </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>2659</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2556</x:v>
@@ -64085,13 +64123,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>11594100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2553</x:v>
@@ -64099,16 +64137,16 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2658</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>2556</x:v>
@@ -64123,7 +64161,7 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>350000</x:v>
+        <x:v>11594100</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2553</x:v>
@@ -64131,31 +64169,31 @@
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>2659</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>2660</x:v>
-      </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>2661</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>726377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2553</x:v>
@@ -64169,10 +64207,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
+        <x:v>2661</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
         <x:v>2662</x:v>
-      </x:c>
-      <x:c r="D72" s="1" t="s">
-        <x:v>2663</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>2556</x:v>
@@ -64181,13 +64219,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2553</x:v>
@@ -64201,25 +64239,25 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2319</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>40134929</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2553</x:v>
@@ -64227,16 +64265,16 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2319</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>2556</x:v>
@@ -64245,13 +64283,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>850000</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2553</x:v>
@@ -64259,31 +64297,31 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
+        <x:v>2665</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
         <x:v>2666</x:v>
-      </x:c>
-      <x:c r="D75" s="1" t="s">
-        <x:v>2667</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>282526</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2553</x:v>
@@ -64291,31 +64329,31 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2669</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>1894</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>116161</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2553</x:v>
@@ -64323,31 +64361,31 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2342</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>1894</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>999284</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2553</x:v>
@@ -64355,31 +64393,31 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>2342</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>209387</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2553</x:v>
@@ -64387,31 +64425,31 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
+        <x:v>2671</x:v>
+      </x:c>
+      <x:c r="D79" s="1" t="s">
         <x:v>2672</x:v>
       </x:c>
-      <x:c r="D79" s="1" t="s">
-        <x:v>2673</x:v>
-      </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>257695</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2553</x:v>
@@ -64425,10 +64463,10 @@
         <x:v>2555</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
+        <x:v>2673</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
         <x:v>2674</x:v>
-      </x:c>
-      <x:c r="D80" s="1" t="s">
-        <x:v>2675</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2556</x:v>
@@ -64437,13 +64475,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>558813</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2553</x:v>
@@ -64451,31 +64489,31 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
+        <x:v>2675</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
         <x:v>2676</x:v>
-      </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>2677</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2553</x:v>
@@ -64483,48 +64521,48 @@
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
+        <x:v>2677</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>2679</x:v>
-      </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>20483</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2681</x:v>
+        <x:v>2679</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2550</x:v>
@@ -64533,30 +64571,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>1927706</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>2682</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>2683</x:v>
-      </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>2684</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2550</x:v>
@@ -64565,30 +64603,30 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2597</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>817066</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2363</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2550</x:v>
@@ -64597,109 +64635,109 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2598</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>88256</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:10">
       <x:c r="A86" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>10041119</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2686</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>1491280</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2593</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2594</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2383</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1460</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2565</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>350000</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2553</x:v>
@@ -64707,16 +64745,16 @@
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2383</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2556</x:v>
@@ -64725,13 +64763,13 @@
         <x:v>2559</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2553</x:v>
@@ -64739,31 +64777,31 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2406</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>1427</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>1987660</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2553</x:v>
@@ -64771,16 +64809,16 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2406</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2550</x:v>
@@ -64789,16 +64827,16 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>56045</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:10">
@@ -64809,57 +64847,57 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>10046680</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>282975</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2553</x:v>
@@ -64867,31 +64905,31 @@
     </x:row>
     <x:row r="94" spans="1:10">
       <x:c r="A94" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>817169</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2553</x:v>
@@ -64899,80 +64937,80 @@
     </x:row>
     <x:row r="95" spans="1:10">
       <x:c r="A95" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2449</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1531015</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1315</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>2791716</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>1652</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>2556</x:v>
@@ -64981,13 +65019,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2584</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>764206</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2553</x:v>
@@ -64995,16 +65033,16 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>1652</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2556</x:v>
@@ -65013,13 +65051,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2565</x:v>
+        <x:v>2587</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2553</x:v>
@@ -65027,48 +65065,48 @@
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="D99" s="1" t="s">
         <x:v>2696</x:v>
       </x:c>
-      <x:c r="D99" s="1" t="s">
-        <x:v>2697</x:v>
-      </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>119644</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2553</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:10">
       <x:c r="A100" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2550</x:v>
@@ -65083,56 +65121,56 @@
         <x:v>2560</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>9866096</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
+        <x:v>2697</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
         <x:v>2698</x:v>
-      </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>2699</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>106947</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1667</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2550</x:v>
@@ -65141,13 +65179,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2553</x:v>
@@ -65155,16 +65193,16 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2550</x:v>
@@ -65173,13 +65211,13 @@
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2581</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1010142</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2553</x:v>
@@ -65187,31 +65225,31 @@
     </x:row>
     <x:row r="104" spans="1:10">
       <x:c r="A104" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>1897</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2584</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>1860445</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2553</x:v>
@@ -65219,31 +65257,31 @@
     </x:row>
     <x:row r="105" spans="1:10">
       <x:c r="A105" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>1785</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>161023</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2553</x:v>
@@ -65251,10 +65289,10 @@
     </x:row>
     <x:row r="106" spans="1:10">
       <x:c r="A106" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
         <x:v>2486</x:v>
@@ -65272,7 +65310,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2609</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I106" s="1">
         <x:v>63084</x:v>
@@ -65283,31 +65321,31 @@
     </x:row>
     <x:row r="107" spans="1:10">
       <x:c r="A107" s="1" t="s">
-        <x:v>2598</x:v>
+        <x:v>2546</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2599</x:v>
+        <x:v>2547</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2551</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2560</x:v>
+        <x:v>2610</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>10000</x:v>
+        <x:v>211898</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2553</x:v>
@@ -65315,31 +65353,31 @@
     </x:row>
     <x:row r="108" spans="1:10">
       <x:c r="A108" s="1" t="s">
-        <x:v>2574</x:v>
+        <x:v>2599</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
         <x:v>2556</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>2551</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2560</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>1306863</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2553</x:v>
@@ -65347,31 +65385,31 @@
     </x:row>
     <x:row r="109" spans="1:10">
       <x:c r="A109" s="1" t="s">
-        <x:v>2546</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>2547</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>1836</x:v>
+        <x:v>2708</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>2550</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>2551</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2614</x:v>
+        <x:v>2669</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>889852</x:v>
+        <x:v>1306863</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
         <x:v>2553</x:v>
@@ -65385,10 +65423,10 @@
         <x:v>2547</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
         <x:v>2550</x:v>
@@ -65400,12 +65438,44 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="I110" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J110" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:10">
+      <x:c r="A111" s="1" t="s">
+        <x:v>2546</x:v>
+      </x:c>
+      <x:c r="B111" s="1" t="s">
+        <x:v>2547</x:v>
+      </x:c>
+      <x:c r="C111" s="1" t="s">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="D111" s="1" t="s">
+        <x:v>2710</x:v>
+      </x:c>
+      <x:c r="E111" s="1" t="s">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="F111" s="1" t="s">
+        <x:v>2551</x:v>
+      </x:c>
+      <x:c r="G111" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H111" s="1" t="s">
+        <x:v>2681</x:v>
+      </x:c>
+      <x:c r="I111" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J110" s="1" t="s">
+      <x:c r="J111" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
     </x:row>
@@ -65483,7 +65553,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>3697225</x:v>
+        <x:v>4325822</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>2553</x:v>
@@ -65491,7 +65561,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>557012</x:v>
@@ -65502,18 +65572,18 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>2569</x:v>
+        <x:v>2572</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>248811</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>2572</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>243968</x:v>
@@ -65524,18 +65594,18 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>2577</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2078023</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>2580</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>530840</x:v>
@@ -65557,13 +65627,13 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2586</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1406523</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -65579,7 +65649,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>2586</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1514370</x:v>
@@ -65590,7 +65660,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>2588</x:v>
+        <x:v>2591</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>415283</x:v>
@@ -65601,7 +65671,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>2590</x:v>
+        <x:v>2593</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1625297</x:v>
@@ -65612,7 +65682,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>3399876</x:v>
@@ -65634,7 +65704,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>2596</x:v>
+        <x:v>2597</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>350000</x:v>
@@ -65678,18 +65748,18 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>2602</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>238154</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>20000</x:v>
@@ -65700,7 +65770,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2607</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2260606</x:v>
@@ -65711,7 +65781,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>2609</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>813215</x:v>
@@ -65755,7 +65825,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>2611</x:v>
+        <x:v>2612</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>1673736</x:v>
@@ -65777,21 +65847,21 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>2613</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>363285</x:v>
+        <x:v>628576</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>2553</x:v>
@@ -65799,10 +65869,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2553</x:v>
@@ -65832,7 +65902,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="B37" s="1">
         <x:v>183312</x:v>
@@ -65843,7 +65913,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="B38" s="1">
         <x:v>725091</x:v>
@@ -65854,7 +65924,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="B39" s="1">
         <x:v>150853</x:v>
@@ -65887,7 +65957,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2633</x:v>
       </x:c>
       <x:c r="B42" s="1">
         <x:v>3954592</x:v>
@@ -65953,7 +66023,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>2634</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="B48" s="1">
         <x:v>961273</x:v>
@@ -66019,10 +66089,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2553</x:v>
@@ -66030,7 +66100,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="B55" s="1">
         <x:v>30183</x:v>
@@ -66041,7 +66111,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="B56" s="1">
         <x:v>350000</x:v>
@@ -66063,7 +66133,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="B58" s="1">
         <x:v>112913</x:v>
@@ -66107,10 +66177,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>2779856</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2553</x:v>
@@ -66129,7 +66199,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="B64" s="1">
         <x:v>504020</x:v>
@@ -66140,7 +66210,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="B65" s="1">
         <x:v>250000</x:v>
@@ -66151,7 +66221,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="B66" s="1">
         <x:v>11944100</x:v>
@@ -66162,7 +66232,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>2662</x:v>
       </x:c>
       <x:c r="B67" s="1">
         <x:v>726377</x:v>
@@ -66173,7 +66243,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="B68" s="1">
         <x:v>668449</x:v>
@@ -66195,10 +66265,10 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>850000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2553</x:v>
@@ -66206,7 +66276,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="B71" s="1">
         <x:v>282526</x:v>
@@ -66239,7 +66309,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="B74" s="1">
         <x:v>209387</x:v>
@@ -66250,7 +66320,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="B75" s="1">
         <x:v>257695</x:v>
@@ -66261,7 +66331,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="B76" s="1">
         <x:v>558813</x:v>
@@ -66272,7 +66342,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="B77" s="1">
         <x:v>1750000</x:v>
@@ -66283,18 +66353,18 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>2679</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="B78" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="B79" s="1">
         <x:v>1927706</x:v>
@@ -66305,13 +66375,13 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="B80" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:3">
@@ -66333,12 +66403,12 @@
         <x:v>10041119</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="B83" s="1">
         <x:v>1491280</x:v>
@@ -66360,7 +66430,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="B85" s="1">
         <x:v>91847</x:v>
@@ -66388,7 +66458,7 @@
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:3">
@@ -66426,13 +66496,13 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="B91" s="1">
         <x:v>1531015</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:3">
@@ -66459,7 +66529,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="B94" s="1">
         <x:v>1543316</x:v>
@@ -66470,18 +66540,18 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="B95" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="B96" s="1">
         <x:v>106947</x:v>
@@ -66503,7 +66573,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="B98" s="1">
         <x:v>1010142</x:v>
@@ -66528,7 +66598,7 @@
         <x:v>1785</x:v>
       </x:c>
       <x:c r="B100" s="1">
-        <x:v>224107</x:v>
+        <x:v>274982</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2553</x:v>
@@ -66536,7 +66606,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="B101" s="1">
         <x:v>10000</x:v>
@@ -66547,7 +66617,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2708</x:v>
       </x:c>
       <x:c r="B102" s="1">
         <x:v>1306863</x:v>
@@ -66569,7 +66639,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>2710</x:v>
       </x:c>
       <x:c r="B104" s="1">
         <x:v>1012792</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -35963,10 +35963,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D208" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
         <x:v>639</x:v>
@@ -35978,7 +35978,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H208" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:8">
@@ -35989,10 +35989,10 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
         <x:v>639</x:v>
@@ -36004,7 +36004,7 @@
         <x:v>2082</x:v>
       </x:c>
       <x:c r="H209" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:8">
@@ -58561,7 +58561,7 @@
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2553</x:v>
@@ -60241,7 +60241,7 @@
         <x:v>2653</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2553</x:v>
@@ -62529,7 +62529,7 @@
         <x:v>2584</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2553</x:v>
@@ -64033,7 +64033,7 @@
         <x:v>2653</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2553</x:v>
@@ -65685,7 +65685,7 @@
         <x:v>2595</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2553</x:v>
@@ -66180,7 +66180,7 @@
         <x:v>2652</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2553</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -50650,7 +50650,7 @@
         <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -51850,7 +51850,7 @@
         <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -52553,7 +52553,7 @@
         <x:v>2473</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2426</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -50230,7 +50230,7 @@
         <x:v>2443</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
         <x:v>2426</x:v>
@@ -50335,7 +50335,7 @@
         <x:v>2456</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>328576</x:v>
+        <x:v>391861</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2426</x:v>
@@ -50405,7 +50405,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -50545,7 +50545,7 @@
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -50755,7 +50755,7 @@
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>6576247</x:v>
+        <x:v>6774919</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -51175,7 +51175,7 @@
         <x:v>2497</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2426</x:v>
@@ -51466,7 +51466,7 @@
         <x:v>2443</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
         <x:v>2426</x:v>
@@ -51562,7 +51562,7 @@
         <x:v>2456</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>328576</x:v>
+        <x:v>391861</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2426</x:v>
@@ -51626,7 +51626,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -51754,7 +51754,7 @@
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -51946,7 +51946,7 @@
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>6576247</x:v>
+        <x:v>6774919</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -52330,7 +52330,7 @@
         <x:v>2497</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2426</x:v>
@@ -52432,7 +52432,7 @@
         <x:v>2445</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>2426</x:v>
@@ -52465,7 +52465,7 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>628576</x:v>
+        <x:v>691861</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>2426</x:v>
@@ -52476,7 +52476,7 @@
         <x:v>2458</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>2426</x:v>
@@ -52520,7 +52520,7 @@
         <x:v>2466</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2426</x:v>
@@ -52575,7 +52575,7 @@
         <x:v>2478</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>6926247</x:v>
+        <x:v>7124919</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2426</x:v>
@@ -52696,7 +52696,7 @@
         <x:v>1702</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>2426</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -50055,7 +50055,7 @@
         <x:v>2428</x:v>
       </x:c>
       <x:c r="I3" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
         <x:v>2426</x:v>
@@ -50160,7 +50160,7 @@
         <x:v>2442</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2426</x:v>
@@ -50335,7 +50335,7 @@
         <x:v>2456</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>391861</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2426</x:v>
@@ -50405,7 +50405,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -50545,7 +50545,7 @@
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -50650,7 +50650,7 @@
         <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -50755,7 +50755,7 @@
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>6774919</x:v>
+        <x:v>7217154</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -51306,7 +51306,7 @@
         <x:v>2428</x:v>
       </x:c>
       <x:c r="I3" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
         <x:v>2426</x:v>
@@ -51402,7 +51402,7 @@
         <x:v>2442</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2426</x:v>
@@ -51562,7 +51562,7 @@
         <x:v>2456</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>391861</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2426</x:v>
@@ -51626,7 +51626,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -51754,7 +51754,7 @@
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -51850,7 +51850,7 @@
         <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -51946,7 +51946,7 @@
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>6774919</x:v>
+        <x:v>7217154</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -52388,7 +52388,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>4219114</x:v>
+        <x:v>7798735</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>2426</x:v>
@@ -52410,7 +52410,7 @@
         <x:v>2441</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>2426</x:v>
@@ -52465,7 +52465,7 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>691861</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>2426</x:v>
@@ -52476,7 +52476,7 @@
         <x:v>2458</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>2426</x:v>
@@ -52520,7 +52520,7 @@
         <x:v>2466</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2426</x:v>
@@ -52553,7 +52553,7 @@
         <x:v>2473</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2426</x:v>
@@ -52575,7 +52575,7 @@
         <x:v>2478</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>7124919</x:v>
+        <x:v>7567154</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2426</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7350,6 +7350,15 @@
     <x:t>05</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX02244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
     <x:t>13</x:t>
   </x:si>
   <x:si>
@@ -7446,6 +7455,9 @@
     <x:t>18</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NJ08232</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6LA00540</x:t>
   </x:si>
   <x:si>
@@ -7495,6 +7507,15 @@
   </x:si>
   <x:si>
     <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX19206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>03</x:t>
@@ -7634,8 +7655,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K35" totalsRowShown="0">
-  <x:autoFilter ref="A1:K35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K39" totalsRowShown="0">
+  <x:autoFilter ref="A1:K39"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -7654,8 +7675,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J35" totalsRowShown="0">
-  <x:autoFilter ref="A1:J35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J39" totalsRowShown="0">
+  <x:autoFilter ref="A1:J39"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -7673,8 +7694,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C31" totalsRowShown="0">
-  <x:autoFilter ref="A1:C31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C35" totalsRowShown="0">
+  <x:autoFilter ref="A1:C35"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -49942,7 +49963,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K35"/>
+  <x:dimension ref="A1:K39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -50160,7 +50181,7 @@
         <x:v>2442</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2426</x:v>
@@ -50171,31 +50192,31 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>1882</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>1320</x:v>
+        <x:v>2444</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>83860</x:v>
+        <x:v>42720</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
         <x:v>2426</x:v>
@@ -50212,10 +50233,10 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2444</x:v>
+        <x:v>1882</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>2438</x:v>
@@ -50224,13 +50245,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
         <x:v>2426</x:v>
@@ -50241,31 +50262,31 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2446</x:v>
+        <x:v>2447</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>2447</x:v>
+        <x:v>2448</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>350000</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2426</x:v>
@@ -50276,34 +50297,34 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>2430</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>2449</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>2450</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>2451</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K10" s="1">
         <x:v>2026</x:v>
@@ -50311,34 +50332,34 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>2453</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>2454</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>2455</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
+        <x:v>2455</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="s">
         <x:v>2456</x:v>
-      </x:c>
-      <x:c r="I11" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>2426</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>2026</x:v>
@@ -50346,16 +50367,16 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2454</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2458</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2423</x:v>
@@ -50367,10 +50388,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
         <x:v>2426</x:v>
@@ -50381,10 +50402,10 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2457</x:v>
@@ -50405,7 +50426,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -50434,13 +50455,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2426</x:v>
@@ -50457,10 +50478,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2060</x:v>
+        <x:v>2463</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2464</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>2423</x:v>
@@ -50469,13 +50490,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
         <x:v>2462</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2426</x:v>
@@ -50486,31 +50507,31 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2463</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2464</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2426</x:v>
@@ -50521,31 +50542,31 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -50556,10 +50577,10 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2468</x:v>
@@ -50568,19 +50589,19 @@
         <x:v>2469</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2464</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2426</x:v>
@@ -50591,31 +50612,31 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2471</x:v>
+        <x:v>2472</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2426</x:v>
@@ -50626,31 +50647,31 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2472</x:v>
+        <x:v>2473</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2473</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3490086</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -50661,10 +50682,10 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2475</x:v>
@@ -50673,19 +50694,19 @@
         <x:v>2476</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2477</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2426</x:v>
@@ -50696,31 +50717,31 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>350000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2426</x:v>
@@ -50731,16 +50752,16 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2479</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2423</x:v>
@@ -50749,13 +50770,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>7217154</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -50766,31 +50787,31 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2479</x:v>
+        <x:v>2481</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2426</x:v>
@@ -50801,10 +50822,10 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2481</x:v>
@@ -50819,13 +50840,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>221403</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2426</x:v>
@@ -50854,13 +50875,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2485</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2426</x:v>
@@ -50877,10 +50898,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2485</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2486</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2487</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2423</x:v>
@@ -50889,13 +50910,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2426</x:v>
@@ -50906,34 +50927,34 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2487</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2488</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2489</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2462</x:v>
+        <x:v>2489</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K28" s="1">
         <x:v>2026</x:v>
@@ -50959,13 +50980,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2426</x:v>
@@ -50976,16 +50997,16 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2307</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2493</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>2438</x:v>
@@ -50994,16 +51015,16 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2456</x:v>
       </x:c>
       <x:c r="K30" s="1">
         <x:v>2026</x:v>
@@ -51011,31 +51032,31 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2325</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2426</x:v>
@@ -51046,34 +51067,34 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2494</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2456</x:v>
       </x:c>
       <x:c r="K32" s="1">
         <x:v>2026</x:v>
@@ -51081,34 +51102,34 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2495</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>2497</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2498</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>9866096</x:v>
+        <x:v>54372</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K33" s="1">
         <x:v>2026</x:v>
@@ -51116,34 +51137,34 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2495</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>119644</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K34" s="1">
         <x:v>2026</x:v>
@@ -51151,36 +51172,176 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2367</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>1702</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2497</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>144600</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
       <x:c r="K35" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:11">
+      <x:c r="A36" s="1" t="s">
+        <x:v>2451</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>2452</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I36" s="1">
+        <x:v>9866096</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+      <x:c r="K36" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:11">
+      <x:c r="A37" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I37" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="J37" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+      <x:c r="K37" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>2359</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="s">
+        <x:v>2425</x:v>
+      </x:c>
+      <x:c r="I38" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="J38" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+      <x:c r="K38" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:11">
+      <x:c r="A39" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>2367</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="s">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>144600</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+      <x:c r="K39" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -51200,7 +51361,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J35"/>
+  <x:dimension ref="A1:J39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -51402,7 +51563,7 @@
         <x:v>2442</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
         <x:v>2426</x:v>
@@ -51410,31 +51571,31 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>1882</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>1320</x:v>
+        <x:v>2444</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>83860</x:v>
+        <x:v>42720</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
         <x:v>2426</x:v>
@@ -51448,10 +51609,10 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>2444</x:v>
+        <x:v>1882</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>2438</x:v>
@@ -51460,13 +51621,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
         <x:v>2426</x:v>
@@ -51474,31 +51635,31 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2446</x:v>
+        <x:v>2447</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>2447</x:v>
+        <x:v>2448</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>350000</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2426</x:v>
@@ -51506,80 +51667,80 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>2430</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>2449</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>2450</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>2451</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>2453</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>2454</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>2455</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
+        <x:v>2455</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="s">
         <x:v>2456</x:v>
-      </x:c>
-      <x:c r="I11" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>2454</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2458</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>2423</x:v>
@@ -51591,10 +51752,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="I12" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
         <x:v>2426</x:v>
@@ -51602,10 +51763,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2457</x:v>
@@ -51626,7 +51787,7 @@
         <x:v>2459</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -51652,13 +51813,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2426</x:v>
@@ -51672,10 +51833,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2060</x:v>
+        <x:v>2463</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2464</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>2423</x:v>
@@ -51684,13 +51845,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
         <x:v>2462</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2426</x:v>
@@ -51698,31 +51859,31 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2463</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>2464</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2426</x:v>
@@ -51730,31 +51891,31 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
         <x:v>2467</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
         <x:v>2426</x:v>
@@ -51762,10 +51923,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2468</x:v>
@@ -51774,19 +51935,19 @@
         <x:v>2469</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2464</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2426</x:v>
@@ -51794,31 +51955,31 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2471</x:v>
+        <x:v>2472</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2426</x:v>
@@ -51826,31 +51987,31 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>2472</x:v>
+        <x:v>2473</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>2473</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>3490086</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -51858,10 +52019,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2475</x:v>
@@ -51870,19 +52031,19 @@
         <x:v>2476</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2477</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2426</x:v>
@@ -51890,31 +52051,31 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>350000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2426</x:v>
@@ -51922,16 +52083,16 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2479</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2423</x:v>
@@ -51940,13 +52101,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>7217154</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -51954,31 +52115,31 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2479</x:v>
+        <x:v>2481</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2426</x:v>
@@ -51986,10 +52147,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2481</x:v>
@@ -52004,13 +52165,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>221403</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2426</x:v>
@@ -52036,13 +52197,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2485</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2426</x:v>
@@ -52056,10 +52217,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2485</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2486</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2487</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2423</x:v>
@@ -52068,13 +52229,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2426</x:v>
@@ -52082,34 +52243,34 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2487</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2488</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2489</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2462</x:v>
+        <x:v>2489</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -52132,13 +52293,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2426</x:v>
@@ -52146,16 +52307,16 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2307</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2493</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>2438</x:v>
@@ -52164,45 +52325,45 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2443</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2456</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2325</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2426</x:v>
@@ -52210,129 +52371,257 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>2494</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2456</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2448</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2449</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2495</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>2497</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2498</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>9866096</x:v>
+        <x:v>54372</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2495</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2499</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>119644</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2367</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>1702</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H35" s="1" t="s">
+        <x:v>2439</x:v>
+      </x:c>
+      <x:c r="I35" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
+      <x:c r="A36" s="1" t="s">
+        <x:v>2451</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>2452</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I36" s="1">
+        <x:v>9866096</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
+      <x:c r="A37" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H37" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I37" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="J37" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
+      <x:c r="A38" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>2359</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="H38" s="1" t="s">
+        <x:v>2425</x:v>
+      </x:c>
+      <x:c r="I38" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="J38" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
+      <x:c r="A39" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>2367</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H35" s="1" t="s">
-        <x:v>2497</x:v>
-      </x:c>
-      <x:c r="I35" s="1">
+      <x:c r="H39" s="1" t="s">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="J35" s="1" t="s">
+      <x:c r="J39" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
     </x:row>
@@ -52352,7 +52641,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C31"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -52410,7 +52699,7 @@
         <x:v>2441</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>2426</x:v>
@@ -52418,10 +52707,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>1320</x:v>
+        <x:v>2444</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>83860</x:v>
+        <x:v>42720</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>2426</x:v>
@@ -52429,10 +52718,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>4210393</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>2426</x:v>
@@ -52440,10 +52729,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>2447</x:v>
+        <x:v>2448</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>350000</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>2426</x:v>
@@ -52451,24 +52740,24 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2450</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>2475788</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>755146</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2456</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -52476,7 +52765,7 @@
         <x:v>2458</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>708827</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>2426</x:v>
@@ -52487,7 +52776,7 @@
         <x:v>2461</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>2426</x:v>
@@ -52495,10 +52784,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2464</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2426</x:v>
@@ -52506,10 +52795,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2426</x:v>
@@ -52517,10 +52806,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>2426</x:v>
@@ -52531,7 +52820,7 @@
         <x:v>2469</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2426</x:v>
@@ -52539,10 +52828,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>2471</x:v>
+        <x:v>2472</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2426</x:v>
@@ -52550,10 +52839,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>2473</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>3490086</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2426</x:v>
@@ -52564,7 +52853,7 @@
         <x:v>2476</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2426</x:v>
@@ -52572,10 +52861,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>2478</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>7567154</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2426</x:v>
@@ -52586,7 +52875,7 @@
         <x:v>2480</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2426</x:v>
@@ -52597,7 +52886,7 @@
         <x:v>2482</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>221403</x:v>
+        <x:v>7765826</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2426</x:v>
@@ -52608,7 +52897,7 @@
         <x:v>2484</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2426</x:v>
@@ -52616,10 +52905,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>2487</x:v>
+        <x:v>2486</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2426</x:v>
@@ -52627,13 +52916,13 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>2489</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -52641,7 +52930,7 @@
         <x:v>2491</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2426</x:v>
@@ -52649,21 +52938,21 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2493</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2456</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2426</x:v>
@@ -52671,34 +52960,78 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>2494</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2456</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>2497</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>9985740</x:v>
+        <x:v>54372</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2453</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B31" s="1">
+        <x:v>282975</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="1" t="s">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="B32" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="1" t="s">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="B33" s="1">
+        <x:v>9985740</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="B34" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="1" t="s">
         <x:v>1702</x:v>
       </x:c>
-      <x:c r="B31" s="1">
+      <x:c r="B35" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="C35" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7374,6 +7374,15 @@
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX35087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -7416,6 +7425,9 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
@@ -7450,9 +7462,6 @@
   </x:si>
   <x:si>
     <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>H2NJ08232</x:t>
@@ -7655,8 +7664,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K39" totalsRowShown="0">
-  <x:autoFilter ref="A1:K39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K41" totalsRowShown="0">
+  <x:autoFilter ref="A1:K41"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -7675,8 +7684,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J39" totalsRowShown="0">
-  <x:autoFilter ref="A1:J39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J41" totalsRowShown="0">
+  <x:autoFilter ref="A1:J41"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -7694,8 +7703,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C35" totalsRowShown="0">
-  <x:autoFilter ref="A1:C35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C37" totalsRowShown="0">
+  <x:autoFilter ref="A1:C37"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -49963,7 +49972,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K39"/>
+  <x:dimension ref="A1:K41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -50216,7 +50225,7 @@
         <x:v>2445</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>42720</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
         <x:v>2426</x:v>
@@ -50332,34 +50341,34 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>2451</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>2452</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>2453</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>2454</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>2475788</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>2026</x:v>
@@ -50367,34 +50376,34 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>2457</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>2458</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
+        <x:v>2458</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
         <x:v>2459</x:v>
-      </x:c>
-      <x:c r="I12" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
-        <x:v>2426</x:v>
       </x:c>
       <x:c r="K12" s="1">
         <x:v>2026</x:v>
@@ -50402,16 +50411,16 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2460</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2458</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2423</x:v>
@@ -50423,10 +50432,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -50437,10 +50446,10 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2460</x:v>
@@ -50461,7 +50470,7 @@
         <x:v>2462</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2426</x:v>
@@ -50490,13 +50499,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2462</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2426</x:v>
@@ -50513,10 +50522,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2060</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>2423</x:v>
@@ -50525,13 +50534,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
         <x:v>2465</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2426</x:v>
@@ -50548,28 +50557,28 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2468</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>285008</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="K17" s="1">
         <x:v>2026</x:v>
@@ -50583,10 +50592,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2468</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2469</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>2423</x:v>
@@ -50595,13 +50604,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2469</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2426</x:v>
@@ -50618,10 +50627,10 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2471</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2472</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2438</x:v>
@@ -50633,10 +50642,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2426</x:v>
@@ -50647,31 +50656,31 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>2472</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>2473</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>2474</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -50697,16 +50706,16 @@
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>4345153</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2426</x:v>
@@ -50717,31 +50726,31 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>2477</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>2478</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>1228</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>64395</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2426</x:v>
@@ -50752,10 +50761,10 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2479</x:v>
@@ -50764,19 +50773,19 @@
         <x:v>2480</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2468</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -50787,31 +50796,31 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2481</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>350000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2426</x:v>
@@ -50822,16 +50831,16 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2481</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2483</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2423</x:v>
@@ -50840,13 +50849,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>7415826</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2426</x:v>
@@ -50863,25 +50872,25 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2483</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2485</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>80948</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2426</x:v>
@@ -50898,10 +50907,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2484</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2485</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2486</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2423</x:v>
@@ -50910,13 +50919,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2426</x:v>
@@ -50933,10 +50942,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2486</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2487</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2488</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2423</x:v>
@@ -50945,13 +50954,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2489</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2426</x:v>
@@ -50968,10 +50977,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2490</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2491</x:v>
+        <x:v>2489</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2423</x:v>
@@ -50980,13 +50989,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2426</x:v>
@@ -50997,34 +51006,34 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2491</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K30" s="1">
         <x:v>2026</x:v>
@@ -51038,10 +51047,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>2493</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>2494</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>2495</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2423</x:v>
@@ -51050,13 +51059,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2426</x:v>
@@ -51067,16 +51076,16 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2307</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2438</x:v>
@@ -51085,16 +51094,16 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2446</x:v>
+        <x:v>2469</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="K32" s="1">
         <x:v>2026</x:v>
@@ -51102,31 +51111,31 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>2497</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2497</x:v>
+        <x:v>2498</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2498</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>54372</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2426</x:v>
@@ -51137,34 +51146,34 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2325</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="K34" s="1">
         <x:v>2026</x:v>
@@ -51178,10 +51187,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2500</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2501</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2423</x:v>
@@ -51193,10 +51202,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>771658</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2426</x:v>
@@ -51207,34 +51216,34 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2325</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
         <x:v>2502</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>2503</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>2438</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>2432</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H36" s="1" t="s">
-        <x:v>2433</x:v>
-      </x:c>
       <x:c r="I36" s="1">
-        <x:v>9866096</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K36" s="1">
         <x:v>2026</x:v>
@@ -51242,34 +51251,34 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2502</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2504</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="K37" s="1">
         <x:v>2026</x:v>
@@ -51277,34 +51286,34 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2505</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1802</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>706</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2425</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>56118</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="K38" s="1">
         <x:v>2026</x:v>
@@ -51318,30 +51327,100 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2367</x:v>
+        <x:v>2505</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1702</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>2459</x:v>
+      </x:c>
+      <x:c r="K39" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:11">
+      <x:c r="A40" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>2359</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
+      <x:c r="G40" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="s">
+        <x:v>2425</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+      <x:c r="K40" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>2367</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H39" s="1" t="s">
-        <x:v>2504</x:v>
-      </x:c>
-      <x:c r="I39" s="1">
+      <x:c r="H41" s="1" t="s">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="I41" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="J39" s="1" t="s">
+      <x:c r="J41" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
-      <x:c r="K39" s="1">
+      <x:c r="K41" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -51361,7 +51440,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J39"/>
+  <x:dimension ref="A1:J41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -51595,7 +51674,7 @@
         <x:v>2445</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>42720</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
         <x:v>2426</x:v>
@@ -51699,80 +51778,80 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>2451</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>2452</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>2453</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>2454</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>2455</x:v>
+        <x:v>2453</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>2475788</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>2456</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>2457</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>2458</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
+        <x:v>2458</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
         <x:v>2459</x:v>
-      </x:c>
-      <x:c r="I12" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
-        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>2457</x:v>
+        <x:v>2460</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>2458</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>2423</x:v>
@@ -51784,10 +51863,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2426</x:v>
@@ -51795,10 +51874,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2460</x:v>
@@ -51819,7 +51898,7 @@
         <x:v>2462</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2426</x:v>
@@ -51845,13 +51924,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>2462</x:v>
+        <x:v>2465</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
         <x:v>2426</x:v>
@@ -51865,10 +51944,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>2060</x:v>
+        <x:v>2466</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>2423</x:v>
@@ -51877,13 +51956,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
         <x:v>2465</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
         <x:v>2426</x:v>
@@ -51897,28 +51976,28 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>2466</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2468</x:v>
       </x:c>
       <x:c r="I17" s="1">
-        <x:v>285008</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
@@ -51929,10 +52008,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2468</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2469</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>2423</x:v>
@@ -51941,13 +52020,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>2470</x:v>
+        <x:v>2469</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
         <x:v>2426</x:v>
@@ -51961,10 +52040,10 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>2471</x:v>
+        <x:v>2470</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>2472</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>2438</x:v>
@@ -51976,10 +52055,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
         <x:v>2426</x:v>
@@ -51987,31 +52066,31 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>2472</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>2473</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>2474</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2474</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
         <x:v>2426</x:v>
@@ -52034,16 +52113,16 @@
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>2477</x:v>
+        <x:v>2471</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>4345153</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
         <x:v>2426</x:v>
@@ -52051,31 +52130,31 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>2477</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>2478</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>1228</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I22" s="1">
-        <x:v>64395</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
         <x:v>2426</x:v>
@@ -52083,10 +52162,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2479</x:v>
@@ -52095,19 +52174,19 @@
         <x:v>2480</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2468</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2426</x:v>
@@ -52115,31 +52194,31 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>2429</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2430</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2481</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>350000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2426</x:v>
@@ -52147,16 +52226,16 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2481</x:v>
+        <x:v>2482</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>2483</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>2423</x:v>
@@ -52165,13 +52244,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>7415826</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2426</x:v>
@@ -52185,25 +52264,25 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2483</x:v>
+        <x:v>2484</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2485</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>80948</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2426</x:v>
@@ -52217,10 +52296,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>2484</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>2485</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>2486</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>2423</x:v>
@@ -52229,13 +52308,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
         <x:v>2426</x:v>
@@ -52249,10 +52328,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2486</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2487</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2488</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2423</x:v>
@@ -52261,13 +52340,13 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2489</x:v>
+        <x:v>2462</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
         <x:v>2426</x:v>
@@ -52281,10 +52360,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2490</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>2491</x:v>
+        <x:v>2489</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2423</x:v>
@@ -52293,13 +52372,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2426</x:v>
@@ -52307,34 +52386,34 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>2492</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2491</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2465</x:v>
+        <x:v>2492</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
@@ -52345,10 +52424,10 @@
         <x:v>2430</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>2493</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>2494</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>2495</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2423</x:v>
@@ -52357,13 +52436,13 @@
         <x:v>2432</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
         <x:v>2433</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2426</x:v>
@@ -52371,16 +52450,16 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2307</x:v>
+        <x:v>2495</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2438</x:v>
@@ -52389,45 +52468,45 @@
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2446</x:v>
+        <x:v>2469</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2429</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2430</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2496</x:v>
+        <x:v>2497</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>2497</x:v>
+        <x:v>2498</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2423</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2498</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>54372</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2426</x:v>
@@ -52435,34 +52514,34 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2434</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2435</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2325</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2499</x:v>
+        <x:v>2446</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
@@ -52473,10 +52552,10 @@
         <x:v>2422</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>2499</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>2500</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>2501</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>2423</x:v>
@@ -52488,10 +52567,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2439</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>771658</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2426</x:v>
@@ -52499,98 +52578,98 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>2452</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>2325</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H36" s="1" t="s">
         <x:v>2502</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>2503</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>2438</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>2432</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H36" s="1" t="s">
-        <x:v>2433</x:v>
-      </x:c>
       <x:c r="I36" s="1">
-        <x:v>9866096</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>2434</x:v>
+        <x:v>2421</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2435</x:v>
+        <x:v>2422</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2502</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>2504</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2438</x:v>
+        <x:v>2423</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>2432</x:v>
+        <x:v>2424</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2433</x:v>
+        <x:v>2439</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>2421</x:v>
+        <x:v>2454</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2422</x:v>
+        <x:v>2455</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2359</x:v>
+        <x:v>2505</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1802</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2423</x:v>
+        <x:v>2438</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>2424</x:v>
+        <x:v>2432</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>706</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2425</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>56118</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
@@ -52601,27 +52680,91 @@
         <x:v>2435</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2367</x:v>
+        <x:v>2505</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1702</x:v>
+        <x:v>2506</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2438</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
+        <x:v>2432</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H39" s="1" t="s">
+        <x:v>2433</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>2459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" s="1" t="s">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>2359</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>2423</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
         <x:v>2424</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
+      <x:c r="G40" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="s">
+        <x:v>2425</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="1" t="s">
+        <x:v>2434</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>2435</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>2367</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>1702</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>2438</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>2424</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H39" s="1" t="s">
-        <x:v>2504</x:v>
-      </x:c>
-      <x:c r="I39" s="1">
+      <x:c r="H41" s="1" t="s">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="I41" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="J39" s="1" t="s">
+      <x:c r="J41" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
     </x:row>
@@ -52641,7 +52784,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -52710,7 +52853,7 @@
         <x:v>2444</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>42720</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>2426</x:v>
@@ -52751,24 +52894,24 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>2454</x:v>
+        <x:v>2452</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>2458</x:v>
+        <x:v>2457</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>755146</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -52776,7 +52919,7 @@
         <x:v>2461</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>708827</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>2426</x:v>
@@ -52787,7 +52930,7 @@
         <x:v>2464</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>2426</x:v>
@@ -52795,10 +52938,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>2426</x:v>
@@ -52806,21 +52949,21 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>1455</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>285008</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>2469</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>2426</x:v>
@@ -52828,10 +52971,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>2472</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>2426</x:v>
@@ -52839,10 +52982,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>2474</x:v>
+        <x:v>2473</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>2426</x:v>
@@ -52853,7 +52996,7 @@
         <x:v>2476</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>4345153</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>2426</x:v>
@@ -52861,10 +53004,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>1228</x:v>
+        <x:v>2478</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>64395</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>2426</x:v>
@@ -52875,7 +53018,7 @@
         <x:v>2480</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>2426</x:v>
@@ -52883,10 +53026,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>2482</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>7765826</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>2426</x:v>
@@ -52894,10 +53037,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>2484</x:v>
+        <x:v>2483</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>2426</x:v>
@@ -52905,10 +53048,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>2486</x:v>
+        <x:v>2485</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>221403</x:v>
+        <x:v>7765826</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>2426</x:v>
@@ -52916,10 +53059,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2487</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>2426</x:v>
@@ -52927,10 +53070,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>2491</x:v>
+        <x:v>2489</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>2426</x:v>
@@ -52938,21 +53081,21 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>2493</x:v>
+        <x:v>2491</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>2495</x:v>
+        <x:v>2494</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>2426</x:v>
@@ -52960,21 +53103,21 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>2497</x:v>
+        <x:v>2498</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>54372</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>2426</x:v>
@@ -52982,21 +53125,21 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B31" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2459</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>2501</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="B32" s="1">
-        <x:v>771658</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>2426</x:v>
@@ -53004,21 +53147,21 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>2503</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="1">
-        <x:v>9985740</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2456</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>1802</x:v>
+        <x:v>2504</x:v>
       </x:c>
       <x:c r="B34" s="1">
-        <x:v>56118</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>2426</x:v>
@@ -53026,12 +53169,34 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="B35" s="1">
+        <x:v>9985740</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>2459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="1" t="s">
+        <x:v>1802</x:v>
+      </x:c>
+      <x:c r="B36" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>2426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="1" t="s">
         <x:v>1702</x:v>
       </x:c>
-      <x:c r="B35" s="1">
+      <x:c r="B37" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
+      <x:c r="C37" s="1" t="s">
         <x:v>2426</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7980,6 +7980,12 @@
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6IL00482</x:t>
   </x:si>
   <x:si>
@@ -8001,6 +8007,15 @@
     <x:t>MCBRIDE, SARAH ELIZABETH</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX09140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX18232</x:t>
   </x:si>
   <x:si>
@@ -8008,6 +8023,9 @@
   </x:si>
   <x:si>
     <x:t>H2NJ08232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NJ13075</x:t>
   </x:si>
   <x:si>
     <x:t>H4IN08249</x:t>
@@ -8306,8 +8324,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K121" totalsRowShown="0">
-  <x:autoFilter ref="A1:K121"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K125" totalsRowShown="0">
+  <x:autoFilter ref="A1:K125"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8326,8 +8344,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J115" totalsRowShown="0">
-  <x:autoFilter ref="A1:J115"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J119" totalsRowShown="0">
+  <x:autoFilter ref="A1:J119"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8345,8 +8363,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C108" totalsRowShown="0">
-  <x:autoFilter ref="A1:C108"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C111" totalsRowShown="0">
+  <x:autoFilter ref="A1:C111"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57938,7 +57956,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K121"/>
+  <x:dimension ref="A1:K125"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58996,7 +59014,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>35211</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2555</x:v>
@@ -59567,10 +59585,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2133</x:v>
@@ -59591,7 +59609,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2555</x:v>
@@ -59602,10 +59620,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2133</x:v>
@@ -59626,7 +59644,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2555</x:v>
@@ -59637,34 +59655,34 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2141</x:v>
+        <x:v>2134</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1696</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K49" s="1">
         <x:v>2026</x:v>
@@ -59678,10 +59696,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2141</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>2552</x:v>
@@ -59690,54 +59708,54 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>3954592</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K50" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2169</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K51" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
@@ -59766,42 +59784,42 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K52" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2169</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1396</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2555</x:v>
@@ -59812,31 +59830,31 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2183</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2555</x:v>
@@ -59853,10 +59871,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2183</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>2558</x:v>
@@ -59865,13 +59883,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2555</x:v>
@@ -59882,16 +59900,16 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2197</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2558</x:v>
@@ -59900,13 +59918,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2555</x:v>
@@ -59917,31 +59935,31 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2197</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2555</x:v>
@@ -59952,31 +59970,31 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2206</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2555</x:v>
@@ -59987,37 +60005,37 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2206</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1537</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K59" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -60028,31 +60046,31 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2217</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K60" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -60063,10 +60081,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2218</x:v>
+        <x:v>2217</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>1525</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2552</x:v>
@@ -60075,13 +60093,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2555</x:v>
@@ -60092,19 +60110,19 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2222</x:v>
+        <x:v>2218</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>1914</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
         <x:v>2553</x:v>
@@ -60113,10 +60131,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2555</x:v>
@@ -60127,16 +60145,16 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2222</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2558</x:v>
@@ -60145,48 +60163,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>430866</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K63" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2555</x:v>
@@ -60197,31 +60215,31 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2555</x:v>
@@ -60232,101 +60250,101 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K66" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>2657</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>2658</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>2659</x:v>
-      </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K67" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2293</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2555</x:v>
@@ -60337,31 +60355,31 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2298</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>1289</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2555</x:v>
@@ -60372,31 +60390,31 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2303</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2555</x:v>
@@ -60407,66 +60425,66 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>4345153</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K71" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2662</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>64395</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2555</x:v>
@@ -60477,16 +60495,16 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2662</x:v>
+        <x:v>2303</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>2552</x:v>
@@ -60495,13 +60513,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>215063</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2555</x:v>
@@ -60512,66 +60530,66 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>504020</x:v>
+        <x:v>5650160</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2667</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>250000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2555</x:v>
@@ -60582,31 +60600,31 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>12433679</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2555</x:v>
@@ -60617,37 +60635,37 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>350000</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
@@ -60670,13 +60688,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2555</x:v>
@@ -60687,10 +60705,10 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2671</x:v>
@@ -60702,16 +60720,16 @@
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>161896</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2555</x:v>
@@ -60722,37 +60740,37 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>506553</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
@@ -60763,10 +60781,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2321</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2558</x:v>
@@ -60775,54 +60793,54 @@
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>40134929</x:v>
+        <x:v>12433679</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>221403</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K82" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
@@ -60833,10 +60851,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
         <x:v>2558</x:v>
@@ -60845,13 +60863,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>282526</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2555</x:v>
@@ -60862,19 +60880,19 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>2677</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>1896</x:v>
-      </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
         <x:v>2553</x:v>
@@ -60883,10 +60901,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>116161</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2555</x:v>
@@ -60897,31 +60915,31 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2344</x:v>
+        <x:v>2321</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>999284</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2555</x:v>
@@ -60932,10 +60950,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>2679</x:v>
@@ -60944,25 +60962,25 @@
         <x:v>2680</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>209387</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -60985,89 +61003,89 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>257695</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K87" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>1896</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>558813</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K88" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2344</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1750000</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K89" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
@@ -61078,10 +61096,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2552</x:v>
@@ -61090,48 +61108,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>20483</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1927706</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2555</x:v>
@@ -61142,34 +61160,34 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>817066</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K92" s="1">
         <x:v>2026</x:v>
@@ -61177,86 +61195,86 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2365</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>88256</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
+        <x:v>2693</x:v>
+      </x:c>
+      <x:c r="D94" s="1" t="s">
         <x:v>2694</x:v>
-      </x:c>
-      <x:c r="D94" s="1" t="s">
-        <x:v>1082</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>10041119</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
         <x:v>2575</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2552</x:v>
@@ -61265,13 +61283,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1491280</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2555</x:v>
@@ -61282,34 +61300,34 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2385</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>1462</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K96" s="1">
         <x:v>2026</x:v>
@@ -61317,37 +61335,37 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2365</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>91847</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K97" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -61358,28 +61376,28 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2408</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1429</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>1987660</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K98" s="1">
         <x:v>2024</x:v>
@@ -61393,10 +61411,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2552</x:v>
@@ -61405,48 +61423,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>56045</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K99" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>2385</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>108744</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2555</x:v>
@@ -61457,19 +61475,19 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
         <x:v>2561</x:v>
@@ -61481,62 +61499,62 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>10046680</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2408</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>282975</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K102" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2552</x:v>
@@ -61545,19 +61563,19 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>817169</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K103" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -61568,60 +61586,60 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>1531015</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K104" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2708</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>1317</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2555</x:v>
@@ -61632,16 +61650,16 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>1654</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
         <x:v>2558</x:v>
@@ -61650,89 +61668,89 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>764206</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K106" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>1543316</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K107" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2709</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>2710</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>119644</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
         <x:v>2575</x:v>
       </x:c>
       <x:c r="K108" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -61743,60 +61761,60 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2711</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>9866096</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K109" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2710</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>2711</x:v>
+        <x:v>1654</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>106947</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2555</x:v>
@@ -61807,37 +61825,37 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2712</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>902176</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K111" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -61848,63 +61866,63 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>2712</x:v>
+        <x:v>2714</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>2713</x:v>
+        <x:v>2715</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>1010142</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J112" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K112" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2714</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2715</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>56118</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J113" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K113" s="1">
         <x:v>2026</x:v>
@@ -61912,31 +61930,31 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2716</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2717</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H114" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I114" s="1">
-        <x:v>1860445</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J114" s="1" t="s">
         <x:v>2555</x:v>
@@ -61947,16 +61965,16 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
         <x:v>2552</x:v>
@@ -61968,30 +61986,30 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H115" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I115" s="1">
-        <x:v>187450</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J115" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K115" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2718</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>2719</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
         <x:v>2552</x:v>
@@ -62000,13 +62018,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H116" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I116" s="1">
-        <x:v>63084</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J116" s="1" t="s">
         <x:v>2555</x:v>
@@ -62017,66 +62035,66 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H117" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I117" s="1">
-        <x:v>110148</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="J117" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K117" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>2714</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>2715</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
-        <x:v>2716</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
-        <x:v>2717</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H118" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I118" s="1">
-        <x:v>10000</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J118" s="1" t="s">
         <x:v>2555</x:v>
@@ -62087,37 +62105,37 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>2718</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>2719</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H119" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I119" s="1">
-        <x:v>1306863</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="J119" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K119" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -62128,10 +62146,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>2505</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>1838</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
         <x:v>2552</x:v>
@@ -62140,13 +62158,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G120" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H120" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I120" s="1">
-        <x:v>889852</x:v>
+        <x:v>110148</x:v>
       </x:c>
       <x:c r="J120" s="1" t="s">
         <x:v>2555</x:v>
@@ -62157,16 +62175,16 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>2720</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>2721</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
         <x:v>2552</x:v>
@@ -62175,18 +62193,158 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H121" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I121" s="1">
-        <x:v>1012792</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J121" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K121" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:11">
+      <x:c r="A122" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B122" s="1" t="s">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C122" s="1" t="s">
+        <x:v>2720</x:v>
+      </x:c>
+      <x:c r="D122" s="1" t="s">
+        <x:v>2721</x:v>
+      </x:c>
+      <x:c r="E122" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F122" s="1" t="s">
+        <x:v>2722</x:v>
+      </x:c>
+      <x:c r="G122" s="1" t="s">
+        <x:v>2723</x:v>
+      </x:c>
+      <x:c r="H122" s="1" t="s">
+        <x:v>2562</x:v>
+      </x:c>
+      <x:c r="I122" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J122" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K122" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:11">
+      <x:c r="A123" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B123" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C123" s="1" t="s">
+        <x:v>2724</x:v>
+      </x:c>
+      <x:c r="D123" s="1" t="s">
+        <x:v>2725</x:v>
+      </x:c>
+      <x:c r="E123" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F123" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G123" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H123" s="1" t="s">
+        <x:v>2683</x:v>
+      </x:c>
+      <x:c r="I123" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J123" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K123" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:11">
+      <x:c r="A124" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B124" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C124" s="1" t="s">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="D124" s="1" t="s">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="E124" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F124" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G124" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H124" s="1" t="s">
+        <x:v>2623</x:v>
+      </x:c>
+      <x:c r="I124" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J124" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K124" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:11">
+      <x:c r="A125" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B125" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C125" s="1" t="s">
+        <x:v>2726</x:v>
+      </x:c>
+      <x:c r="D125" s="1" t="s">
+        <x:v>2727</x:v>
+      </x:c>
+      <x:c r="E125" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F125" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G125" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H125" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="I125" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J125" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K125" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -62206,7 +62364,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J115"/>
+  <x:dimension ref="A1:J119"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -63144,7 +63302,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>35211</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2555</x:v>
@@ -63664,10 +63822,10 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2133</x:v>
@@ -63688,7 +63846,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>122688</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2555</x:v>
@@ -63696,10 +63854,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2133</x:v>
@@ -63720,7 +63878,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2555</x:v>
@@ -63728,34 +63886,34 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>2141</x:v>
+        <x:v>2134</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1696</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H48" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
@@ -63766,10 +63924,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2141</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>2552</x:v>
@@ -63778,45 +63936,45 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>3954592</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2169</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
         <x:v>2555</x:v>
@@ -63824,31 +63982,31 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2169</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1396</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
         <x:v>2555</x:v>
@@ -63856,31 +64014,31 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2183</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2555</x:v>
@@ -63894,10 +64052,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2183</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>2558</x:v>
@@ -63906,13 +64064,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2555</x:v>
@@ -63920,16 +64078,16 @@
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2197</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>2558</x:v>
@@ -63938,13 +64096,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2555</x:v>
@@ -63952,31 +64110,31 @@
     </x:row>
     <x:row r="55" spans="1:10">
       <x:c r="A55" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2197</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2555</x:v>
@@ -63984,31 +64142,31 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2206</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2555</x:v>
@@ -64016,31 +64174,31 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2206</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1537</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2555</x:v>
@@ -64054,25 +64212,25 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2217</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2648</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2555</x:v>
@@ -64086,10 +64244,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2218</x:v>
+        <x:v>2217</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1525</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>2552</x:v>
@@ -64098,13 +64256,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2555</x:v>
@@ -64112,19 +64270,19 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2222</x:v>
+        <x:v>2218</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>1914</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2553</x:v>
@@ -64133,10 +64291,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2650</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2555</x:v>
@@ -64144,16 +64302,16 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2222</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2558</x:v>
@@ -64162,13 +64320,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>430866</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2555</x:v>
@@ -64176,31 +64334,31 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2653</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2555</x:v>
@@ -64208,31 +64366,31 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2655</x:v>
+        <x:v>2653</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2555</x:v>
@@ -64240,31 +64398,31 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2657</x:v>
+        <x:v>2655</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2555</x:v>
@@ -64272,31 +64430,31 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>2657</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>2658</x:v>
       </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>2659</x:v>
-      </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J65" s="1" t="s">
         <x:v>2555</x:v>
@@ -64304,31 +64462,31 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>2293</x:v>
+        <x:v>2659</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2555</x:v>
@@ -64336,31 +64494,31 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>2298</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>1289</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2555</x:v>
@@ -64368,31 +64526,31 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>2303</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2555</x:v>
@@ -64400,31 +64558,31 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>4345153</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2555</x:v>
@@ -64432,31 +64590,31 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2662</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>279458</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2555</x:v>
@@ -64464,31 +64622,31 @@
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2663</x:v>
+        <x:v>2303</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>504020</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2555</x:v>
@@ -64496,10 +64654,10 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2665</x:v>
@@ -64508,19 +64666,19 @@
         <x:v>2666</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>250000</x:v>
+        <x:v>5650160</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2555</x:v>
@@ -64528,31 +64686,31 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2667</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>350000</x:v>
+        <x:v>279458</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2555</x:v>
@@ -64560,31 +64718,31 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>12433679</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2555</x:v>
@@ -64610,13 +64768,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2555</x:v>
@@ -64624,10 +64782,10 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2671</x:v>
@@ -64639,16 +64797,16 @@
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>668449</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2555</x:v>
@@ -64656,16 +64814,16 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>2321</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2558</x:v>
@@ -64674,13 +64832,13 @@
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>40134929</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2555</x:v>
@@ -64688,10 +64846,10 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>2673</x:v>
@@ -64706,13 +64864,13 @@
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>221403</x:v>
+        <x:v>12433679</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2555</x:v>
@@ -64738,13 +64896,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>282526</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2555</x:v>
@@ -64752,19 +64910,19 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
+        <x:v>2677</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
         <x:v>2678</x:v>
       </x:c>
-      <x:c r="D80" s="1" t="s">
-        <x:v>1896</x:v>
-      </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>2553</x:v>
@@ -64773,10 +64931,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>116161</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2555</x:v>
@@ -64784,31 +64942,31 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2344</x:v>
+        <x:v>2321</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>999284</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2555</x:v>
@@ -64816,10 +64974,10 @@
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>2679</x:v>
@@ -64828,19 +64986,19 @@
         <x:v>2680</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>209387</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2555</x:v>
@@ -64866,13 +65024,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>257695</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2555</x:v>
@@ -64880,31 +65038,31 @@
     </x:row>
     <x:row r="84" spans="1:10">
       <x:c r="A84" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>1896</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>558813</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2555</x:v>
@@ -64912,31 +65070,31 @@
     </x:row>
     <x:row r="85" spans="1:10">
       <x:c r="A85" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2344</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>1750000</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2555</x:v>
@@ -64950,10 +65108,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2552</x:v>
@@ -64962,45 +65120,45 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>20483</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:10">
       <x:c r="A87" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>1927706</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2555</x:v>
@@ -65008,63 +65166,63 @@
     </x:row>
     <x:row r="88" spans="1:10">
       <x:c r="A88" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>817066</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:10">
       <x:c r="A89" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2365</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>88256</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2555</x:v>
@@ -65072,31 +65230,31 @@
     </x:row>
     <x:row r="90" spans="1:10">
       <x:c r="A90" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
+        <x:v>2693</x:v>
+      </x:c>
+      <x:c r="D90" s="1" t="s">
         <x:v>2694</x:v>
-      </x:c>
-      <x:c r="D90" s="1" t="s">
-        <x:v>1082</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>10041119</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2575</x:v>
@@ -65104,16 +65262,16 @@
     </x:row>
     <x:row r="91" spans="1:10">
       <x:c r="A91" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2552</x:v>
@@ -65122,13 +65280,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>1491280</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2555</x:v>
@@ -65136,63 +65294,63 @@
     </x:row>
     <x:row r="92" spans="1:10">
       <x:c r="A92" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2385</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>1462</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2603</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:10">
       <x:c r="A93" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2365</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>91847</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2555</x:v>
@@ -65206,28 +65364,28 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2408</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>1429</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>1987660</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:10">
@@ -65238,10 +65396,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>2552</x:v>
@@ -65250,45 +65408,45 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>56045</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:10">
       <x:c r="A96" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>2385</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>108744</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
         <x:v>2555</x:v>
@@ -65296,19 +65454,19 @@
     </x:row>
     <x:row r="97" spans="1:10">
       <x:c r="A97" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
         <x:v>2561</x:v>
@@ -65320,7 +65478,7 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>10046680</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2555</x:v>
@@ -65328,31 +65486,31 @@
     </x:row>
     <x:row r="98" spans="1:10">
       <x:c r="A98" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2408</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>282975</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2555</x:v>
@@ -65360,16 +65518,16 @@
     </x:row>
     <x:row r="99" spans="1:10">
       <x:c r="A99" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2552</x:v>
@@ -65378,16 +65536,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>817169</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:10">
@@ -65398,57 +65556,57 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>1531015</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:10">
       <x:c r="A101" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2708</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>1317</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>2791716</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2555</x:v>
@@ -65456,16 +65614,16 @@
     </x:row>
     <x:row r="102" spans="1:10">
       <x:c r="A102" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1654</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2558</x:v>
@@ -65474,13 +65632,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>764206</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
         <x:v>2555</x:v>
@@ -65488,31 +65646,31 @@
     </x:row>
     <x:row r="103" spans="1:10">
       <x:c r="A103" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>1543316</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
         <x:v>2555</x:v>
@@ -65520,31 +65678,31 @@
     </x:row>
     <x:row r="104" spans="1:10">
       <x:c r="A104" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2709</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>2710</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>9866096</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2575</x:v>
@@ -65552,63 +65710,63 @@
     </x:row>
     <x:row r="105" spans="1:10">
       <x:c r="A105" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2711</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>119644</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:10">
       <x:c r="A106" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2710</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>2711</x:v>
+        <x:v>1654</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>106947</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2555</x:v>
@@ -65616,31 +65774,31 @@
     </x:row>
     <x:row r="107" spans="1:10">
       <x:c r="A107" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2712</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>902176</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
         <x:v>2555</x:v>
@@ -65648,66 +65806,66 @@
     </x:row>
     <x:row r="108" spans="1:10">
       <x:c r="A108" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>2712</x:v>
+        <x:v>2714</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>2713</x:v>
+        <x:v>2715</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>1010142</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:10">
       <x:c r="A109" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2714</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2715</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>1916563</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:10">
@@ -65718,10 +65876,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2716</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>2717</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
         <x:v>2552</x:v>
@@ -65730,13 +65888,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2629</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>297598</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2555</x:v>
@@ -65750,10 +65908,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
         <x:v>2552</x:v>
@@ -65765,10 +65923,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>63084</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2555</x:v>
@@ -65776,31 +65934,31 @@
     </x:row>
     <x:row r="112" spans="1:10">
       <x:c r="A112" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>2714</x:v>
+        <x:v>2718</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>2715</x:v>
+        <x:v>2719</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>2716</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>2717</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>10000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J112" s="1" t="s">
         <x:v>2555</x:v>
@@ -65808,16 +65966,16 @@
     </x:row>
     <x:row r="113" spans="1:10">
       <x:c r="A113" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>2718</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>2719</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>2558</x:v>
@@ -65826,13 +65984,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1916563</x:v>
       </x:c>
       <x:c r="J113" s="1" t="s">
         <x:v>2555</x:v>
@@ -65846,10 +66004,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>2505</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>1838</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
         <x:v>2552</x:v>
@@ -65858,13 +66016,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H114" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="I114" s="1">
-        <x:v>889852</x:v>
+        <x:v>297598</x:v>
       </x:c>
       <x:c r="J114" s="1" t="s">
         <x:v>2555</x:v>
@@ -65872,16 +66030,16 @@
     </x:row>
     <x:row r="115" spans="1:10">
       <x:c r="A115" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>2720</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>2721</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
         <x:v>2552</x:v>
@@ -65890,15 +66048,143 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H115" s="1" t="s">
+        <x:v>2618</x:v>
+      </x:c>
+      <x:c r="I115" s="1">
+        <x:v>63084</x:v>
+      </x:c>
+      <x:c r="J115" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:10">
+      <x:c r="A116" s="1" t="s">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B116" s="1" t="s">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C116" s="1" t="s">
+        <x:v>2720</x:v>
+      </x:c>
+      <x:c r="D116" s="1" t="s">
+        <x:v>2721</x:v>
+      </x:c>
+      <x:c r="E116" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F116" s="1" t="s">
+        <x:v>2722</x:v>
+      </x:c>
+      <x:c r="G116" s="1" t="s">
+        <x:v>2723</x:v>
+      </x:c>
+      <x:c r="H116" s="1" t="s">
+        <x:v>2562</x:v>
+      </x:c>
+      <x:c r="I116" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J116" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:10">
+      <x:c r="A117" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B117" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C117" s="1" t="s">
+        <x:v>2724</x:v>
+      </x:c>
+      <x:c r="D117" s="1" t="s">
+        <x:v>2725</x:v>
+      </x:c>
+      <x:c r="E117" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F117" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G117" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H117" s="1" t="s">
+        <x:v>2683</x:v>
+      </x:c>
+      <x:c r="I117" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J117" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:10">
+      <x:c r="A118" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B118" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C118" s="1" t="s">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="D118" s="1" t="s">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="E118" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F118" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G118" s="1" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H115" s="1" t="s">
-        <x:v>2689</x:v>
-      </x:c>
-      <x:c r="I115" s="1">
+      <x:c r="H118" s="1" t="s">
+        <x:v>2623</x:v>
+      </x:c>
+      <x:c r="I118" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J118" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:10">
+      <x:c r="A119" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B119" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C119" s="1" t="s">
+        <x:v>2726</x:v>
+      </x:c>
+      <x:c r="D119" s="1" t="s">
+        <x:v>2727</x:v>
+      </x:c>
+      <x:c r="E119" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F119" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G119" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H119" s="1" t="s">
+        <x:v>2695</x:v>
+      </x:c>
+      <x:c r="I119" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="J115" s="1" t="s">
+      <x:c r="J119" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
     </x:row>
@@ -65918,7 +66204,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C108"/>
+  <x:dimension ref="A1:C111"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -66218,7 +66504,7 @@
         <x:v>2614</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>35211</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2555</x:v>
@@ -66402,32 +66688,32 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1696</x:v>
       </x:c>
       <x:c r="B44" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="B45" s="1">
-        <x:v>3954592</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="B46" s="1">
-        <x:v>943006</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>2555</x:v>
@@ -66435,10 +66721,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>1396</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B47" s="1">
-        <x:v>1836196</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>2555</x:v>
@@ -66446,10 +66732,10 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="B48" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2555</x:v>
@@ -66457,10 +66743,10 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="B49" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>2555</x:v>
@@ -66468,10 +66754,10 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B50" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>2555</x:v>
@@ -66479,10 +66765,10 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B51" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>2555</x:v>
@@ -66490,10 +66776,10 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="B52" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>2555</x:v>
@@ -66501,10 +66787,10 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="1" t="s">
-        <x:v>1537</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="B53" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>2555</x:v>
@@ -66512,10 +66798,10 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="B54" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>2555</x:v>
@@ -66523,10 +66809,10 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="1" t="s">
-        <x:v>1525</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="B55" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>2555</x:v>
@@ -66534,10 +66820,10 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="1" t="s">
-        <x:v>1914</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="B56" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>2555</x:v>
@@ -66545,10 +66831,10 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="B57" s="1">
-        <x:v>430866</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>2555</x:v>
@@ -66556,10 +66842,10 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="1" t="s">
-        <x:v>2654</x:v>
+        <x:v>2652</x:v>
       </x:c>
       <x:c r="B58" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>2555</x:v>
@@ -66567,10 +66853,10 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="1" t="s">
-        <x:v>2656</x:v>
+        <x:v>2654</x:v>
       </x:c>
       <x:c r="B59" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>2555</x:v>
@@ -66578,10 +66864,10 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>2656</x:v>
       </x:c>
       <x:c r="B60" s="1">
-        <x:v>582915</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>2555</x:v>
@@ -66589,10 +66875,10 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="1" t="s">
-        <x:v>2659</x:v>
+        <x:v>2658</x:v>
       </x:c>
       <x:c r="B61" s="1">
-        <x:v>112913</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>2555</x:v>
@@ -66600,10 +66886,10 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B62" s="1">
-        <x:v>34970</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>2555</x:v>
@@ -66611,10 +66897,10 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="1" t="s">
-        <x:v>1289</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="B63" s="1">
-        <x:v>126626</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>2555</x:v>
@@ -66622,10 +66908,10 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B64" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>2555</x:v>
@@ -66633,10 +66919,10 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B65" s="1">
-        <x:v>4345153</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>2555</x:v>
@@ -66644,10 +66930,10 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>2663</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>279458</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2555</x:v>
@@ -66655,10 +66941,10 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="B67" s="1">
-        <x:v>504020</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>2555</x:v>
@@ -66669,7 +66955,7 @@
         <x:v>2666</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>250000</x:v>
+        <x:v>5650160</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2555</x:v>
@@ -66677,10 +66963,10 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="B69" s="1">
-        <x:v>12783679</x:v>
+        <x:v>314348</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>2555</x:v>
@@ -66691,7 +66977,7 @@
         <x:v>2670</x:v>
       </x:c>
       <x:c r="B70" s="1">
-        <x:v>726377</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>2555</x:v>
@@ -66702,7 +66988,7 @@
         <x:v>2672</x:v>
       </x:c>
       <x:c r="B71" s="1">
-        <x:v>668449</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>2555</x:v>
@@ -66710,10 +66996,10 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="B72" s="1">
-        <x:v>40134929</x:v>
+        <x:v>12783679</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2555</x:v>
@@ -66721,10 +67007,10 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="B73" s="1">
-        <x:v>221403</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>2555</x:v>
@@ -66732,10 +67018,10 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2678</x:v>
       </x:c>
       <x:c r="B74" s="1">
-        <x:v>282526</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>2555</x:v>
@@ -66743,10 +67029,10 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="1" t="s">
-        <x:v>1896</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B75" s="1">
-        <x:v>116161</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>2555</x:v>
@@ -66754,10 +67040,10 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="B76" s="1">
-        <x:v>999284</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>2555</x:v>
@@ -66765,10 +67051,10 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="1" t="s">
-        <x:v>2680</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="B77" s="1">
-        <x:v>209387</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>2555</x:v>
@@ -66776,10 +67062,10 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="1" t="s">
-        <x:v>2682</x:v>
+        <x:v>1896</x:v>
       </x:c>
       <x:c r="B78" s="1">
-        <x:v>257695</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>2555</x:v>
@@ -66787,10 +67073,10 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="B79" s="1">
-        <x:v>558813</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>2555</x:v>
@@ -66801,7 +67087,7 @@
         <x:v>2686</x:v>
       </x:c>
       <x:c r="B80" s="1">
-        <x:v>1750000</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>2555</x:v>
@@ -66812,18 +67098,18 @@
         <x:v>2688</x:v>
       </x:c>
       <x:c r="B81" s="1">
-        <x:v>20483</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="B82" s="1">
-        <x:v>1927706</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>2555</x:v>
@@ -66831,54 +67117,54 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>817066</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="B84" s="1">
-        <x:v>88256</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="1" t="s">
-        <x:v>1082</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="B85" s="1">
-        <x:v>10041119</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="B86" s="1">
-        <x:v>1491280</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="1" t="s">
-        <x:v>1462</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B87" s="1">
-        <x:v>350000</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>2555</x:v>
@@ -66886,21 +67172,21 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="B88" s="1">
-        <x:v>91847</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="1" t="s">
-        <x:v>1429</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="B89" s="1">
-        <x:v>1987660</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>2555</x:v>
@@ -66908,21 +67194,21 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="B90" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="B91" s="1">
-        <x:v>108744</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>2555</x:v>
@@ -66930,10 +67216,10 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="B92" s="1">
-        <x:v>10046680</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>2555</x:v>
@@ -66941,21 +67227,21 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B93" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>817169</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2555</x:v>
@@ -66963,21 +67249,21 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B95" s="1">
-        <x:v>1531015</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="1" t="s">
-        <x:v>1317</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B96" s="1">
-        <x:v>2791716</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>2555</x:v>
@@ -66985,10 +67271,10 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="1" t="s">
-        <x:v>1654</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="B97" s="1">
-        <x:v>764206</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>2555</x:v>
@@ -66996,32 +67282,32 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2710</x:v>
       </x:c>
       <x:c r="B98" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="1" t="s">
-        <x:v>2709</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="B99" s="1">
-        <x:v>9985740</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="1" t="s">
-        <x:v>2711</x:v>
+        <x:v>1654</x:v>
       </x:c>
       <x:c r="B100" s="1">
-        <x:v>106947</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>2555</x:v>
@@ -67029,10 +67315,10 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="B101" s="1">
-        <x:v>902176</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>2555</x:v>
@@ -67040,21 +67326,21 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="1" t="s">
-        <x:v>2713</x:v>
+        <x:v>2715</x:v>
       </x:c>
       <x:c r="B102" s="1">
-        <x:v>1010142</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2717</x:v>
       </x:c>
       <x:c r="B103" s="1">
-        <x:v>1916563</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
         <x:v>2555</x:v>
@@ -67062,10 +67348,10 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="B104" s="1">
-        <x:v>360682</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
         <x:v>2555</x:v>
@@ -67073,10 +67359,10 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="1" t="s">
-        <x:v>2715</x:v>
+        <x:v>2719</x:v>
       </x:c>
       <x:c r="B105" s="1">
-        <x:v>10000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
         <x:v>2555</x:v>
@@ -67084,10 +67370,10 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="1" t="s">
-        <x:v>2719</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="B106" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1916563</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
         <x:v>2555</x:v>
@@ -67095,10 +67381,10 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="1" t="s">
-        <x:v>1838</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="B107" s="1">
-        <x:v>889852</x:v>
+        <x:v>360682</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
         <x:v>2555</x:v>
@@ -67109,9 +67395,42 @@
         <x:v>2721</x:v>
       </x:c>
       <x:c r="B108" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="C108" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:3">
+      <x:c r="A109" s="1" t="s">
+        <x:v>2725</x:v>
+      </x:c>
+      <x:c r="B109" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="C109" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:3">
+      <x:c r="A110" s="1" t="s">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="B110" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="C110" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:3">
+      <x:c r="A111" s="1" t="s">
+        <x:v>2727</x:v>
+      </x:c>
+      <x:c r="B111" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C108" s="1" t="s">
+      <x:c r="C111" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -36066,10 +36066,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D209" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
         <x:v>638</x:v>
@@ -36081,7 +36081,7 @@
         <x:v>2084</x:v>
       </x:c>
       <x:c r="H209" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:8">
@@ -36092,10 +36092,10 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D210" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="E210" s="1" t="s">
         <x:v>638</x:v>
@@ -36107,7 +36107,7 @@
         <x:v>2084</x:v>
       </x:c>
       <x:c r="H210" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:8">
@@ -58314,7 +58314,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2555</x:v>
@@ -58349,7 +58349,7 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
         <x:v>2555</x:v>
@@ -59014,7 +59014,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2555</x:v>
@@ -60484,7 +60484,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2555</x:v>
@@ -60554,7 +60554,7 @@
         <x:v>2640</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2555</x:v>
@@ -61219,7 +61219,7 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2555</x:v>
@@ -61604,7 +61604,7 @@
         <x:v>2707</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2555</x:v>
@@ -62662,7 +62662,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
         <x:v>2555</x:v>
@@ -62694,7 +62694,7 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
         <x:v>2555</x:v>
@@ -63302,7 +63302,7 @@
         <x:v>2615</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2555</x:v>
@@ -64614,7 +64614,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2555</x:v>
@@ -64678,7 +64678,7 @@
         <x:v>2640</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2555</x:v>
@@ -65222,7 +65222,7 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2555</x:v>
@@ -65574,7 +65574,7 @@
         <x:v>2707</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
         <x:v>2555</x:v>
@@ -66295,7 +66295,7 @@
         <x:v>2577</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>2555</x:v>
@@ -66306,7 +66306,7 @@
         <x:v>2580</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>2555</x:v>
@@ -66504,7 +66504,7 @@
         <x:v>2614</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2555</x:v>
@@ -66933,7 +66933,7 @@
         <x:v>2663</x:v>
       </x:c>
       <x:c r="B66" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>2555</x:v>
@@ -66955,7 +66955,7 @@
         <x:v>2666</x:v>
       </x:c>
       <x:c r="B68" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>2555</x:v>
@@ -67120,7 +67120,7 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B83" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
         <x:v>2555</x:v>
@@ -67241,7 +67241,7 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B94" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>2555</x:v>

--- a/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-disbursement-report.xlsx
@@ -7830,6 +7830,9 @@
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
@@ -7998,6 +8001,9 @@
     <x:t>LETLOW, JULIA</x:t>
   </x:si>
   <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
     <x:t>H4AZ08124</x:t>
   </x:si>
   <x:si>
@@ -8022,12 +8028,12 @@
     <x:t>MENEFEE, CHRISTIAN</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NJ13075</x:t>
+  </x:si>
+  <x:si>
     <x:t>H2NJ08232</x:t>
   </x:si>
   <x:si>
-    <x:t>H2NJ13075</x:t>
-  </x:si>
-  <x:si>
     <x:t>H4IN08249</x:t>
   </x:si>
   <x:si>
@@ -8040,6 +8046,9 @@
     <x:t>MIGUEZ, BLAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6AL00476</x:t>
   </x:si>
   <x:si>
@@ -8143,6 +8152,12 @@
   </x:si>
   <x:si>
     <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA12154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
   </x:si>
   <x:si>
     <x:t>S4MI00470</x:t>
@@ -8324,8 +8339,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K125" totalsRowShown="0">
-  <x:autoFilter ref="A1:K125"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K130" totalsRowShown="0">
+  <x:autoFilter ref="A1:K130"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8344,8 +8359,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J119" totalsRowShown="0">
-  <x:autoFilter ref="A1:J119"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J124" totalsRowShown="0">
+  <x:autoFilter ref="A1:J124"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -8363,8 +8378,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C111" totalsRowShown="0">
-  <x:autoFilter ref="A1:C111"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C116" totalsRowShown="0">
+  <x:autoFilter ref="A1:C116"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -57956,7 +57971,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K125"/>
+  <x:dimension ref="A1:K130"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="12" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -58780,16 +58795,16 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>2041</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>2552</x:v>
@@ -58798,48 +58813,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>973501</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K24" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H25" s="1" t="s">
         <x:v>2604</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>2605</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>2050</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>1705</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>2558</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>2561</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>2562</x:v>
-      </x:c>
       <x:c r="I25" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
         <x:v>2555</x:v>
@@ -58850,16 +58865,16 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>2606</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>1018</x:v>
+        <x:v>1705</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>2558</x:v>
@@ -58868,13 +58883,13 @@
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I26" s="1">
-        <x:v>1945951</x:v>
+        <x:v>29970</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
         <x:v>2555</x:v>
@@ -58885,34 +58900,34 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>2607</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>2608</x:v>
+        <x:v>1018</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I27" s="1">
-        <x:v>238154</x:v>
+        <x:v>1945951</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K27" s="1">
         <x:v>2024</x:v>
@@ -58920,16 +58935,16 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>2609</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>2610</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>2552</x:v>
@@ -58938,16 +58953,16 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I28" s="1">
-        <x:v>20000</x:v>
+        <x:v>238154</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K28" s="1">
         <x:v>2024</x:v>
@@ -58961,10 +58976,10 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>2611</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>2612</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>2552</x:v>
@@ -58979,7 +58994,7 @@
         <x:v>2592</x:v>
       </x:c>
       <x:c r="I29" s="1">
-        <x:v>2260606</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
         <x:v>2555</x:v>
@@ -58990,51 +59005,51 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>2613</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>2614</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>2615</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I30" s="1">
-        <x:v>581175</x:v>
+        <x:v>2260606</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K30" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2616</x:v>
+        <x:v>2614</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>2617</x:v>
+        <x:v>2615</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>2558</x:v>
@@ -59046,30 +59061,30 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H31" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2616</x:v>
       </x:c>
       <x:c r="I31" s="1">
-        <x:v>813215</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K31" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>2077</x:v>
+        <x:v>2617</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1796</x:v>
+        <x:v>2618</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>2558</x:v>
@@ -59078,13 +59093,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>871</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I32" s="1">
-        <x:v>509959</x:v>
+        <x:v>813215</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
         <x:v>2555</x:v>
@@ -59095,16 +59110,16 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2084</x:v>
+        <x:v>2077</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>1796</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>2558</x:v>
@@ -59113,13 +59128,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I33" s="1">
-        <x:v>118034</x:v>
+        <x:v>509959</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
         <x:v>2555</x:v>
@@ -59130,31 +59145,31 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>2096</x:v>
+        <x:v>2084</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>2408433</x:v>
+        <x:v>118034</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
         <x:v>2555</x:v>
@@ -59165,37 +59180,37 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>2619</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>2620</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H35" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I35" s="1">
-        <x:v>1673736</x:v>
+        <x:v>2408433</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K35" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -59206,10 +59221,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>2102</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>1326</x:v>
+        <x:v>2621</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>2558</x:v>
@@ -59218,86 +59233,86 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>126740</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K36" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2621</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>2622</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H37" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>2475786</x:v>
+        <x:v>126740</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K37" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2622</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="I38" s="1">
-        <x:v>300000</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K38" s="1">
         <x:v>2026</x:v>
@@ -59311,10 +59326,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>2624</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>2625</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>2558</x:v>
@@ -59326,7 +59341,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H39" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>455146</x:v>
@@ -59340,16 +59355,16 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>2627</x:v>
+        <x:v>2625</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>2628</x:v>
+        <x:v>2626</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>2558</x:v>
@@ -59361,10 +59376,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
         <x:v>2555</x:v>
@@ -59375,66 +59390,66 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>2628</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>2629</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H41" s="1" t="s">
         <x:v>2630</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>816</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>2552</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>2561</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H41" s="1" t="s">
-        <x:v>2562</x:v>
-      </x:c>
       <x:c r="I41" s="1">
-        <x:v>10039655</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K41" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>2117</x:v>
+        <x:v>2631</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1329</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>2631</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I42" s="1">
-        <x:v>1012931</x:v>
+        <x:v>10039655</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
         <x:v>2555</x:v>
@@ -59445,16 +59460,16 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>2632</x:v>
+        <x:v>2117</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>2633</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>2558</x:v>
@@ -59463,19 +59478,19 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H43" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2632</x:v>
       </x:c>
       <x:c r="I43" s="1">
-        <x:v>183312</x:v>
+        <x:v>1012931</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K43" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -59486,10 +59501,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>2633</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>2634</x:v>
-      </x:c>
-      <x:c r="D44" s="1" t="s">
-        <x:v>2635</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>2558</x:v>
@@ -59501,45 +59516,45 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>2636</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I44" s="1">
-        <x:v>725091</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K44" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>2637</x:v>
+        <x:v>2635</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>2638</x:v>
+        <x:v>2636</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H45" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I45" s="1">
-        <x:v>150853</x:v>
+        <x:v>725091</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
         <x:v>2555</x:v>
@@ -59556,10 +59571,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>2127</x:v>
+        <x:v>2638</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>994</x:v>
+        <x:v>2639</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>2552</x:v>
@@ -59568,13 +59583,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H46" s="1" t="s">
-        <x:v>2639</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I46" s="1">
-        <x:v>511329</x:v>
+        <x:v>150853</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
         <x:v>2555</x:v>
@@ -59585,16 +59600,16 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>2133</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1040</x:v>
+        <x:v>994</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>2552</x:v>
@@ -59603,13 +59618,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H47" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I47" s="1">
-        <x:v>122688</x:v>
+        <x:v>511329</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
         <x:v>2555</x:v>
@@ -59620,10 +59635,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>2133</x:v>
@@ -59644,7 +59659,7 @@
         <x:v>2578</x:v>
       </x:c>
       <x:c r="I48" s="1">
-        <x:v>120103</x:v>
+        <x:v>122688</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
         <x:v>2555</x:v>
@@ -59655,69 +59670,69 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>2134</x:v>
+        <x:v>2133</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1696</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H49" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I49" s="1">
-        <x:v>550000</x:v>
+        <x:v>120103</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K49" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>2141</x:v>
+        <x:v>2134</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1696</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H50" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I50" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K50" s="1">
         <x:v>2026</x:v>
@@ -59731,10 +59746,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>2641</x:v>
+        <x:v>2141</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>2642</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>2552</x:v>
@@ -59743,54 +59758,54 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H51" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I51" s="1">
-        <x:v>3954592</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K51" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>2169</x:v>
+        <x:v>2642</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>2643</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H52" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>836118</x:v>
+        <x:v>3954592</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K52" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
@@ -59816,45 +59831,45 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H53" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I53" s="1">
-        <x:v>106888</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K53" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>2177</x:v>
+        <x:v>2169</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1396</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I54" s="1">
-        <x:v>1836196</x:v>
+        <x:v>106888</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
         <x:v>2555</x:v>
@@ -59865,31 +59880,31 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>2183</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H55" s="1" t="s">
         <x:v>2559</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>107353</x:v>
+        <x:v>1836196</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
         <x:v>2555</x:v>
@@ -59906,10 +59921,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>2191</x:v>
+        <x:v>2183</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>2558</x:v>
@@ -59918,13 +59933,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I56" s="1">
-        <x:v>1308901</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
         <x:v>2555</x:v>
@@ -59935,16 +59950,16 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>2197</x:v>
+        <x:v>2191</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>2558</x:v>
@@ -59953,13 +59968,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>124736</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
         <x:v>2555</x:v>
@@ -59970,31 +59985,31 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>2643</x:v>
+        <x:v>2197</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>2644</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
-        <x:v>2645</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>961273</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
         <x:v>2555</x:v>
@@ -60005,31 +60020,31 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>2206</x:v>
+        <x:v>2644</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>2645</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2646</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>3025544</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
         <x:v>2555</x:v>
@@ -60040,37 +60055,37 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>2646</x:v>
+        <x:v>2206</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>1537</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>285008</x:v>
+        <x:v>3025544</x:v>
       </x:c>
       <x:c r="J60" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K60" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -60081,31 +60096,31 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>2217</x:v>
+        <x:v>2647</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
         <x:v>2648</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>68985</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K61" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -60116,10 +60131,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>2218</x:v>
+        <x:v>2217</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>1525</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>2552</x:v>
@@ -60128,13 +60143,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
         <x:v>2649</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>108546</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="J62" s="1" t="s">
         <x:v>2555</x:v>
@@ -60145,19 +60160,19 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>2222</x:v>
+        <x:v>2218</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>1914</x:v>
+        <x:v>1525</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
         <x:v>2553</x:v>
@@ -60169,7 +60184,7 @@
         <x:v>2650</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>1924213</x:v>
+        <x:v>108546</x:v>
       </x:c>
       <x:c r="J63" s="1" t="s">
         <x:v>2555</x:v>
@@ -60180,16 +60195,16 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>2651</x:v>
+        <x:v>2222</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>2652</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>2558</x:v>
@@ -60198,19 +60213,19 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>430866</x:v>
+        <x:v>1924213</x:v>
       </x:c>
       <x:c r="J64" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K64" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -60221,10 +60236,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>2652</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>2653</x:v>
-      </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>2654</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>2558</x:v>
@@ -60250,31 +60265,31 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
+        <x:v>2654</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
         <x:v>2655</x:v>
       </x:c>
-      <x:c r="D66" s="1" t="s">
-        <x:v>2656</x:v>
-      </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>2647</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I66" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="J66" s="1" t="s">
         <x:v>2555</x:v>
@@ -60285,31 +60300,31 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>2656</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>2657</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>2658</x:v>
-      </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2648</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="J67" s="1" t="s">
         <x:v>2555</x:v>
@@ -60320,37 +60335,37 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
+        <x:v>2658</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
         <x:v>2659</x:v>
-      </x:c>
-      <x:c r="D68" s="1" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>582915</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J68" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K68" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -60361,10 +60376,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>2660</x:v>
+        <x:v>2256</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>2661</x:v>
+        <x:v>1711</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>2552</x:v>
@@ -60373,68 +60388,68 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2660</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>112913</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="J69" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K69" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>2293</x:v>
+        <x:v>2259</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>34970</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="J70" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K70" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>2298</x:v>
+        <x:v>2661</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>1289</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>2558</x:v>
@@ -60443,13 +60458,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>126626</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="J71" s="1" t="s">
         <x:v>2555</x:v>
@@ -60460,10 +60475,10 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>2662</x:v>
@@ -60472,54 +60487,54 @@
         <x:v>2663</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
-        <x:v>2664</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>436280</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="J72" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K72" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2605</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2606</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>2303</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>2578</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>46160</x:v>
+        <x:v>34970</x:v>
       </x:c>
       <x:c r="J73" s="1" t="s">
         <x:v>2555</x:v>
@@ -60530,66 +60545,66 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>2665</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>2666</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I74" s="1">
-        <x:v>5667720</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="J74" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K74" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>2667</x:v>
+        <x:v>2664</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>2665</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2666</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>64395</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="J75" s="1" t="s">
         <x:v>2555</x:v>
@@ -60600,16 +60615,16 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>2668</x:v>
+        <x:v>2303</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>2552</x:v>
@@ -60618,19 +60633,19 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2578</x:v>
       </x:c>
       <x:c r="I76" s="1">
-        <x:v>34890</x:v>
+        <x:v>46160</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K76" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -60644,7 +60659,7 @@
         <x:v>2667</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>1301</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>2552</x:v>
@@ -60653,83 +60668,83 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I77" s="1">
-        <x:v>215063</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="J77" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K77" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>2669</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>2670</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>2570</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>504020</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K78" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>2671</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>2672</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>250000</x:v>
+        <x:v>128790</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
         <x:v>2555</x:v>
@@ -60740,37 +60755,37 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>350000</x:v>
+        <x:v>215063</x:v>
       </x:c>
       <x:c r="J80" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K80" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
@@ -60781,95 +60796,95 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>2673</x:v>
+        <x:v>2671</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>2674</x:v>
+        <x:v>2672</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I81" s="1">
-        <x:v>12433679</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K81" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>2675</x:v>
+        <x:v>2673</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>2676</x:v>
+        <x:v>2674</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I82" s="1">
-        <x:v>726377</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="J82" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K82" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>2677</x:v>
+        <x:v>2311</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>2678</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2675</x:v>
       </x:c>
       <x:c r="I83" s="1">
-        <x:v>161896</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="J83" s="1" t="s">
         <x:v>2555</x:v>
@@ -60886,45 +60901,45 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>2676</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>2677</x:v>
-      </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>2678</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>2626</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I84" s="1">
-        <x:v>506553</x:v>
+        <x:v>12433679</x:v>
       </x:c>
       <x:c r="J84" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K84" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>2321</x:v>
+        <x:v>2676</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>2677</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>2558</x:v>
@@ -60933,54 +60948,54 @@
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I85" s="1">
-        <x:v>40134929</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J85" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K85" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
+        <x:v>2678</x:v>
+      </x:c>
+      <x:c r="D86" s="1" t="s">
         <x:v>2679</x:v>
-      </x:c>
-      <x:c r="D86" s="1" t="s">
-        <x:v>2680</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I86" s="1">
-        <x:v>221403</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="J86" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K86" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -60991,10 +61006,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
+        <x:v>2680</x:v>
+      </x:c>
+      <x:c r="D87" s="1" t="s">
         <x:v>2681</x:v>
-      </x:c>
-      <x:c r="D87" s="1" t="s">
-        <x:v>2682</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>2558</x:v>
@@ -61003,13 +61018,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>282526</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="J87" s="1" t="s">
         <x:v>2555</x:v>
@@ -61020,19 +61035,19 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>2684</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>1896</x:v>
+        <x:v>2681</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>2553</x:v>
@@ -61041,10 +61056,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2627</x:v>
       </x:c>
       <x:c r="I88" s="1">
-        <x:v>116161</x:v>
+        <x:v>506553</x:v>
       </x:c>
       <x:c r="J88" s="1" t="s">
         <x:v>2555</x:v>
@@ -61055,31 +61070,31 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>2344</x:v>
+        <x:v>2321</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>999284</x:v>
+        <x:v>40134929</x:v>
       </x:c>
       <x:c r="J89" s="1" t="s">
         <x:v>2555</x:v>
@@ -61090,37 +61105,37 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>2685</x:v>
+        <x:v>2682</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>2686</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I90" s="1">
-        <x:v>209387</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="J90" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K90" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -61131,10 +61146,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>2687</x:v>
+        <x:v>2684</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>2688</x:v>
+        <x:v>2685</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
         <x:v>2558</x:v>
@@ -61143,89 +61158,89 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2686</x:v>
       </x:c>
       <x:c r="I91" s="1">
-        <x:v>257695</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="J91" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K91" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>2689</x:v>
+        <x:v>2687</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>2690</x:v>
+        <x:v>1896</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I92" s="1">
-        <x:v>558813</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="J92" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K92" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>2691</x:v>
+        <x:v>2344</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>2692</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I93" s="1">
-        <x:v>2250000</x:v>
+        <x:v>999284</x:v>
       </x:c>
       <x:c r="J93" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K93" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -61236,10 +61251,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>2693</x:v>
+        <x:v>2688</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>2694</x:v>
+        <x:v>2689</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
         <x:v>2552</x:v>
@@ -61248,48 +61263,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I94" s="1">
-        <x:v>20483</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="J94" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K94" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>2696</x:v>
+        <x:v>2690</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>2697</x:v>
+        <x:v>2691</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>1927706</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="J95" s="1" t="s">
         <x:v>2555</x:v>
@@ -61300,34 +61315,34 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>2698</x:v>
+        <x:v>2692</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>2699</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>2603</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I96" s="1">
-        <x:v>817066</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="J96" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K96" s="1">
         <x:v>2026</x:v>
@@ -61335,86 +61350,86 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>2365</x:v>
+        <x:v>2694</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>2695</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>88256</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="J97" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K97" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>2700</x:v>
+        <x:v>2696</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>1082</x:v>
+        <x:v>2697</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2698</x:v>
       </x:c>
       <x:c r="I98" s="1">
-        <x:v>10041119</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="J98" s="1" t="s">
         <x:v>2575</x:v>
       </x:c>
       <x:c r="K98" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>2701</x:v>
+        <x:v>2699</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>2702</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
         <x:v>2552</x:v>
@@ -61423,13 +61438,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
-        <x:v>2567</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I99" s="1">
-        <x:v>1491280</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="J99" s="1" t="s">
         <x:v>2555</x:v>
@@ -61440,34 +61455,34 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="1" t="s">
-        <x:v>2563</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>2564</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>2385</x:v>
+        <x:v>2701</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>1462</x:v>
+        <x:v>2702</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2604</x:v>
       </x:c>
       <x:c r="I100" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="J100" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K100" s="1">
         <x:v>2026</x:v>
@@ -61475,37 +61490,37 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>2703</x:v>
+        <x:v>2365</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>2704</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2624</x:v>
       </x:c>
       <x:c r="I101" s="1">
-        <x:v>91847</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="J101" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K101" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
@@ -61516,28 +61531,28 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>2408</x:v>
+        <x:v>2703</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>1429</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
-        <x:v>2640</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I102" s="1">
-        <x:v>1987660</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="J102" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K102" s="1">
         <x:v>2024</x:v>
@@ -61551,10 +61566,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>2426</x:v>
+        <x:v>2704</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>2705</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
         <x:v>2552</x:v>
@@ -61563,48 +61578,48 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2567</x:v>
       </x:c>
       <x:c r="I103" s="1">
-        <x:v>56045</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="J103" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K103" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2563</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2564</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>2705</x:v>
+        <x:v>2385</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>2706</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
-        <x:v>2707</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>426280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="J104" s="1" t="s">
         <x:v>2555</x:v>
@@ -61615,19 +61630,19 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>2708</x:v>
+        <x:v>2706</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>2707</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>2561</x:v>
@@ -61639,62 +61654,62 @@
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>10046680</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="J105" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K105" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>2445</x:v>
+        <x:v>2408</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>282975</x:v>
+        <x:v>1987660</x:v>
       </x:c>
       <x:c r="J106" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K106" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>2451</x:v>
+        <x:v>2426</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
         <x:v>2552</x:v>
@@ -61703,19 +61718,19 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
-        <x:v>2649</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>817169</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="J107" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K107" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -61726,48 +61741,48 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="D108" s="1" t="s">
         <x:v>2709</x:v>
-      </x:c>
-      <x:c r="D108" s="1" t="s">
-        <x:v>2710</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2710</x:v>
       </x:c>
       <x:c r="I108" s="1">
-        <x:v>1531015</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="J108" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K108" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>2459</x:v>
+        <x:v>2711</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>1317</x:v>
+        <x:v>2712</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>2553</x:v>
@@ -61776,45 +61791,45 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
-        <x:v>2711</x:v>
+        <x:v>2637</x:v>
       </x:c>
       <x:c r="I109" s="1">
-        <x:v>2791716</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="J109" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K109" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>2461</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>1654</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
-        <x:v>2592</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>764206</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="J110" s="1" t="s">
         <x:v>2555</x:v>
@@ -61831,10 +61846,10 @@
         <x:v>2557</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>2712</x:v>
+        <x:v>2445</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>2713</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
         <x:v>2558</x:v>
@@ -61843,13 +61858,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
-        <x:v>2570</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>1543316</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="J111" s="1" t="s">
         <x:v>2555</x:v>
@@ -61860,45 +61875,45 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>2714</x:v>
+        <x:v>2451</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>2715</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
         <x:v>2552</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>2561</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2650</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>119644</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="J112" s="1" t="s">
-        <x:v>2575</x:v>
+        <x:v>2555</x:v>
       </x:c>
       <x:c r="K112" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>2714</x:v>
@@ -61907,54 +61922,54 @@
         <x:v>2715</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
         <x:v>2561</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
         <x:v>2562</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>9866096</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="J113" s="1" t="s">
         <x:v>2575</x:v>
       </x:c>
       <x:c r="K113" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>2716</x:v>
+        <x:v>2459</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>2717</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H114" s="1" t="s">
-        <x:v>2629</x:v>
+        <x:v>2716</x:v>
       </x:c>
       <x:c r="I114" s="1">
-        <x:v>106947</x:v>
+        <x:v>2791716</x:v>
       </x:c>
       <x:c r="J114" s="1" t="s">
         <x:v>2555</x:v>
@@ -61971,25 +61986,25 @@
         <x:v>2583</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>2467</x:v>
+        <x:v>2461</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>1669</x:v>
+        <x:v>1654</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G115" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="H115" s="1" t="s">
-        <x:v>2554</x:v>
+        <x:v>2592</x:v>
       </x:c>
       <x:c r="I115" s="1">
-        <x:v>902176</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="J115" s="1" t="s">
         <x:v>2555</x:v>
@@ -62000,69 +62015,69 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
+        <x:v>2717</x:v>
+      </x:c>
+      <x:c r="D116" s="1" t="s">
         <x:v>2718</x:v>
       </x:c>
-      <x:c r="D116" s="1" t="s">
-        <x:v>2719</x:v>
-      </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>2552</x:v>
+        <x:v>2558</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G116" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H116" s="1" t="s">
-        <x:v>2589</x:v>
+        <x:v>2570</x:v>
       </x:c>
       <x:c r="I116" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="J116" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K116" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B117" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2719</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G117" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H117" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I117" s="1">
-        <x:v>56118</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="J117" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K117" s="1">
         <x:v>2026</x:v>
@@ -62070,37 +62085,37 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="1" t="s">
-        <x:v>2556</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>2557</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>2480</x:v>
+        <x:v>2719</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>1899</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>2558</x:v>
+        <x:v>2552</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
-        <x:v>2553</x:v>
+        <x:v>2561</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H118" s="1" t="s">
-        <x:v>2559</x:v>
+        <x:v>2562</x:v>
       </x:c>
       <x:c r="I118" s="1">
-        <x:v>1860445</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="J118" s="1" t="s">
-        <x:v>2555</x:v>
+        <x:v>2575</x:v>
       </x:c>
       <x:c r="K118" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
@@ -62111,10 +62126,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2721</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>2722</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
         <x:v>2552</x:v>
@@ -62123,33 +62138,33 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H119" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2630</x:v>
       </x:c>
       <x:c r="I119" s="1">
-        <x:v>187450</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="J119" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K119" s="1">
-        <x:v>2026</x:v>
+        <x:v>2024</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2467</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
         <x:v>2552</x:v>
@@ -62161,10 +62176,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H120" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="I120" s="1">
-        <x:v>110148</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="J120" s="1" t="s">
         <x:v>2555</x:v>
@@ -62175,16 +62190,16 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>2488</x:v>
+        <x:v>2723</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>1787</x:v>
+        <x:v>2724</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
         <x:v>2552</x:v>
@@ -62193,13 +62208,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G121" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H121" s="1" t="s">
-        <x:v>2618</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="I121" s="1">
-        <x:v>63084</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="J121" s="1" t="s">
         <x:v>2555</x:v>
@@ -62210,51 +62225,51 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="1" t="s">
-        <x:v>2604</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>2605</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>2720</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>2721</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
         <x:v>2558</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
-        <x:v>2722</x:v>
+        <x:v>2553</x:v>
       </x:c>
       <x:c r="G122" s="1" t="s">
-        <x:v>2723</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H122" s="1" t="s">
-        <x:v>2562</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I122" s="1">
-        <x:v>10000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="J122" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K122" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2556</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2557</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>2724</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>2725</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
         <x:v>2558</x:v>
@@ -62263,13 +62278,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G123" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="H123" s="1" t="s">
-        <x:v>2683</x:v>
+        <x:v>2559</x:v>
       </x:c>
       <x:c r="I123" s="1">
-        <x:v>1306863</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="J123" s="1" t="s">
         <x:v>2555</x:v>
@@ -62286,10 +62301,10 @@
         <x:v>2549</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>2505</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>1838</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
         <x:v>2552</x:v>
@@ -62298,33 +62313,33 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G124" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H124" s="1" t="s">
-        <x:v>2623</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I124" s="1">
-        <x:v>889852</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="J124" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K124" s="1">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>2726</x:v>
+        <x:v>2488</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>2727</x:v>
+        <x:v>1787</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
         <x:v>2552</x:v>
@@ -62333,18 +62348,193 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G125" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H125" s="1" t="s">
-        <x:v>2695</x:v>
+        <x:v>2619</x:v>
       </x:c>
       <x:c r="I125" s="1">
-        <x:v>1012792</x:v>
+        <x:v>63084</x:v>
       </x:c>
       <x:c r="J125" s="1" t="s">
         <x:v>2555</x:v>
       </x:c>
       <x:c r="K125" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:11">
+      <x:c r="A126" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B126" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C126" s="1" t="s">
+        <x:v>2488</x:v>
+      </x:c>
+      <x:c r="D126" s="1" t="s">
+        <x:v>1787</x:v>
+      </x:c>
+      <x:c r="E126" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F126" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G126" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H126" s="1" t="s">
+        <x:v>2619</x:v>
+      </x:c>
+      <x:c r="I126" s="1">
+        <x:v>110148</x:v>
+      </x:c>
+      <x:c r="J126" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K126" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:11">
+      <x:c r="A127" s="1" t="s">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="B127" s="1" t="s">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="C127" s="1" t="s">
+        <x:v>2725</x:v>
+      </x:c>
+      <x:c r="D127" s="1" t="s">
+        <x:v>2726</x:v>
+      </x:c>
+      <x:c r="E127" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F127" s="1" t="s">
+        <x:v>2727</x:v>
+      </x:c>
+      <x:c r="G127" s="1" t="s">
+        <x:v>2728</x:v>
+      </x:c>
+      <x:c r="H127" s="1" t="s">
+        <x:v>2562</x:v>
+      </x:c>
+      <x:c r="I127" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J127" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K127" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:11">
+      <x:c r="A128" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B128" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C128" s="1" t="s">
+        <x:v>2729</x:v>
+      </x:c>
+      <x:c r="D128" s="1" t="s">
+        <x:v>2730</x:v>
+      </x:c>
+      <x:c r="E128" s="1" t="s">
+        <x:v>2558</x:v>
+      </x:c>
+      <x:c r="F128" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G128" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H128" s="1" t="s">
+        <x:v>2686</x:v>
+      </x:c>
+      <x:c r="I128" s="1">
+        <x:v>1306863</x:v>
+      </x:c>
+      <x:c r="J128" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K128" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:11">
+      <x:c r="A129" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B129" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C129" s="1" t="s">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="D129" s="1" t="s">
+        <x:v>1838</x:v>
+      </x:c>
+      <x:c r="E129" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F129" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G129" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H129" s="1" t="s">
+        <x:v>2624</x:v>
+      </x:c>
+      <x:c r="I129" s="1">
+        <x:v>889852</x:v>
+      </x:c>
+      <x:c r="J129" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K129" s="1">
+        <x:v>2024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:11">
+      <x:c r="A130" s="1" t="s">
+        <x:v>2548</x:v>
+      </x:c>
+      <x:c r="B130" s="1" t="s">
+        <x:v>2549</x:v>
+      </x:c>
+      <x:c r="C130" s="1" t="s">
+        <x:v>2731</x:v>
+      </x:c>
+      <x:c r="D130" s="1" t="s">
+        <x:v>2732</x:v>
+      </x:c>
+      <x:c r="E130" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F130" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G130" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H130" s="1" t="s">
+        <x:v>2698</x:v>
+      </x:c>
+      <x:c r="I130" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="J130" s="1" t="s">
+        <x:v>2555</x:v>
+      </x:c>
+      <x:c r="K130" s="1">
         <x:v>2026</x:v>
       </x:c>
     </x:row>
@@ -62364,7 +62554,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J119"/>
+  <x:dimension ref="A1:J124"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -62766,10 +62956,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>2548</x:v>
+        <x:v>2582</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2549</x:v>
+        <x:v>2583</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>1983</x:v>
@@ -62790,7 +62980,7 @@
         <x:v>2589</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>83860</x:v>
+        <x:v>582374</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
         <x:v>2555</x:v>
@@ -62798,10 +62988,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>1983</x:v>
@@ -62822,7 +63012,7 @@
         <x:v>2589</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>582374</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
         <x:v>2555</x:v>
@@ -63086,16 +63276,16 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>2582</x:v>
+        <x:v>2548</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>2583</x:v>
+        <x:v>2549</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>2041</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>2552</x:v>
@@ -63104,13 +63294,13 @@
         <x:v>2553</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>2603</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>973501</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
         <x:v>2555</x:v>
@@ -63118,31 +63308,31 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
+        <x:v>2582</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>2583</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>2553</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H24" s="1" t="s">
         <x:v>2604</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>2605</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>2050</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>1705</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>2558</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>2561</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>2562</x:v>
-      </x:c>
       <x:c r="I24" s="1">
-        <x:v>29970</x:v>
+        <x:v>973501</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>2555</x:v>
@@ -63150,16 +63340,16 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>2556</